--- a/extraction/meredith.xlsx
+++ b/extraction/meredith.xlsx
@@ -24,10 +24,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="MM/DD/YYYY"/>
-    <numFmt numFmtId="166" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -70,9 +69,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,23 +440,23 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
-    <col width="55" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
@@ -590,13 +586,13 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
+          <t>Moelis &amp; Company LLC (Moelis)</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -615,12 +611,12 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Board discussed sale of four select stations (St. Louis, Mobile-Pensacola, Flint-Saginaw-Bay City, Springfield) or all of LMG; afterwards engaged Moelis to prepare station marketing after Labor Day 2020, keeping an LMG sale open as an option. Segment/asset sale, not yet a whole-company sale.</t>
+          <t>Target's financial adviser. Moelis attended the May 2020 board meeting on selling select stations or all of LMG, was formally engaged afterwards, and in February 2021 amended its engagement letter to add an LMG sale fee.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>“to discuss strategic options for our LMG business segment, including the potential sale of select broadcast stations and a potential sale of all of LMG” (p. 58)</t>
+          <t>“Members of our senior management and representatives of Moelis also participated in the meeting. The select station group” (p. 58)</t>
         </is>
       </c>
       <c r="R2" s="2" t="n"/>
@@ -641,18 +637,18 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>after the May 2020 board meeting; by July 2020</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Moelis &amp; Company LLC</t>
+          <t>Meredith</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -671,24 +667,24 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Target financial adviser (only one named). First seen acting at May 2020 board meeting; formally engaged after it; engagement letter amended Feb 2021 to add LMG-sale fee (p. 62); fairness opinion 05/03/2021.</t>
+          <t>Qualified decision: engaged Moelis to prepare to market four select stations after Labor Day 2020, while preparing an LMG sale and NMG spin-off as an option. On 08/24/2020 the board postponed marketing until after the November 2020 shareholder meeting.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>“Members of our senior management and representatives of Moelis also participated in the meeting.” (p. 58)</t>
+          <t>“Subsequent to the May 2020 Board meeting, the Company formally engaged Moelis to begin preparations for marketing the select station group after Labor Day 2020 depending on market conditions.” (p. 59)</t>
         </is>
       </c>
       <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="n"/>
       <c r="T3" s="3" t="n">
-        <v>43967</v>
+        <v>43997</v>
       </c>
       <c r="U3" s="3" t="n">
         <v>43952</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>43982</v>
+        <v>44043</v>
       </c>
     </row>
     <row r="4">
@@ -697,12 +693,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>after May 2020 meeting; by July 2020</t>
+          <t>after the May 2020 board meeting; by July 2020</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Cooley LLP</t>
+          <t>Cooley LLP (Cooley)</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
@@ -727,12 +723,12 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Target primary outside legal counsel. First seen acting in LMG divestiture/NMG spin-off preparations after the May 2020 meeting; attended July 2020 board meeting.</t>
+          <t>Target's primary outside legal counsel. Cooley was first shown acting after the May 2020 meeting, preparing the LMG divestiture and NMG spin-off, and attended the July 2020 board meeting. Deloitte Tax LLP later acted as the target's tax adviser.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>“the Company’s primary outside legal counsel Cooley LLP (“Cooley”) also continued analysis and preparations for a potential divestiture of LMG and a spin-off of NMG” (p. 59)</t>
+          <t>“the Company’s primary outside legal counsel Cooley LLP” (p. 59)</t>
         </is>
       </c>
       <c r="R4" s="2" t="n"/>
@@ -753,7 +749,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>08/24/2020</t>
+          <t>after the 11/10/2020 board meeting</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -764,7 +760,7 @@
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -783,24 +779,28 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Board defers: will seek the articles amendment at the 11/11/2020 annual meeting before any strategic transaction, so station marketing waits until after that meeting.</t>
+          <t>Board authorized management and advisers to market the select station sales (St. Louis, Mobile-Pensacola, Flint-Saginaw-Bay City, Springfield-Holyoke), begin buyer outreach and solicit initial indications of interest. The scope was assets only; an LMG sale was not yet decided.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>“determined to wait to commence marketing the select station sale until after the November annual shareholders meeting” (p. 59)</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="n"/>
+          <t>“our Board authorized our senior management and advisors to move forward with the marketing of the select station sales, to commence buyer outreach and solicit initial indications of interest.” (p. 60)</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S5" s="2" t="n"/>
       <c r="T5" s="3" t="n">
-        <v>44067</v>
+        <v>44148</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>44067</v>
+        <v>44145</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>44067</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="6">
@@ -809,7 +809,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>after 11/10/2020 meeting</t>
+          <t>11/16/2020</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -820,14 +820,14 @@
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
@@ -839,21 +839,25 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Board authorizes marketing of the four select stations: buyer outreach and initial indications of interest. Station (asset) sale; LMG sale still only an option. Undated; bounded by the 11/10 meeting and outreach start 11/16.</t>
+          <t>Moelis outreach for the four select stations. NDA counterparties could review preliminary financial and diligence information, with preliminary indications of interest due 12/17/2020. Interest in all of LMG came up within this outreach.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>“our Board authorized our senior management and advisors to move forward with the marketing of the select station sales, to commence buyer outreach and solicit initial indications of interest” (p. 60)</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="n"/>
+          <t>“Commencing November 16, 2020 and over the next several weeks, representatives of Moelis contacted 20 parties (including Gray)” (p. 60)</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="3" t="n">
-        <v>44148</v>
+        <v>44151</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>44145</v>
+        <v>44151</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>44151</v>
@@ -865,18 +869,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>11/16/2020</t>
+          <t>commencing 11/16/2020 and over the next several weeks</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n"/>
+          <t>20 parties contacted by Moelis (incl. Gray)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -890,24 +898,22 @@
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n"/>
+      <c r="M7" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Moelis begins outreach for the four select stations; NDA signers get preliminary financial and diligence information; preliminary indications due 12/17/2020 (communication date of due date not given).</t>
+          <t>Target-initiated contacts: all publicly traded broadcasters (incl. Gray), plus other broadcasters and broadcast investors seen as most likely to be interested. Several showed interest in some or all four stations. Types are not split.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>“Commencing November 16, 2020 and over the next several weeks, representatives of Moelis contacted 20 parties (including Gray)” (p. 60)</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“The contacted parties included all of the publicly-traded broadcasters (including Gray) as well as other broadcasters and broadcast investors considered most likely to have potential interest.” (p. 60)</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="n"/>
       <c r="T7" s="3" t="n">
         <v>44151</v>
@@ -916,7 +922,7 @@
         <v>44151</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>44151</v>
+        <v>44186</v>
       </c>
     </row>
     <row r="8">
@@ -925,12 +931,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>from 11/16/2020, over several weeks</t>
+          <t>between 11/16/2020 and 12/21/2020</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>20 parties contacted by Moelis (incl. Gray, Parties A–D)</t>
+          <t>17 NDA signers (incl. Gray)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -940,7 +946,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -955,18 +961,18 @@
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated. All publicly-traded broadcasters (incl. Gray; so also Party E, later named as one) plus other broadcasters and broadcast investors; strategic/financial split not given. Several expressed interest; 17 signed NDAs (#8, #9).</t>
+          <t>Confidentiality agreements with customary standstill and fall-away provisions. The filing names only Gray among the 17. Parties A–D are presumably members, since only counterparties were invited to bid, but this is not stated (Q). About 3 contacted parties did not sign.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>“The contacted parties included all of the publicly-traded broadcasters (including Gray) as well as other broadcasters and broadcast investors considered most likely to have potential interest.” (p. 60)</t>
+          <t>“The Company entered into confidentiality agreements with 17 parties (including Gray) who had expressed interest in a transaction with the Company.” (p. 60)</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -976,7 +982,7 @@
       </c>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="3" t="n">
-        <v>44151</v>
+        <v>44168</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>44151</v>
@@ -991,12 +997,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/17/2020</t>
+          <t>by 12/21/2020 (due 12/17/2020)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc.</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,7 +1012,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -1017,9 +1023,21 @@
       </c>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="n">
         <v>1</v>
       </c>
@@ -1027,28 +1045,28 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Confidentiality agreement with customary standstill and fall-away; date from merger agreement summary (p. 114). Gray is a television broadcast company (p. 43).</t>
+          <t>Conditions: the filing states none for the station bids. First-round bid for all four select stations; its own price is not disclosed. The four station bids together showed a group value of $511–631 million, not per share.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>“the confidentiality agreement between the Company and Gray, dated November 17, 2020” (p. 114)</t>
+          <t>“Two parties bid for all four stations: a strategic party referred to as Party A, and a private equity sponsor” (p. 60)</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="3" t="n">
-        <v>44152</v>
+        <v>44182</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>44152</v>
+        <v>44151</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>44152</v>
+        <v>44186</v>
       </c>
     </row>
     <row r="10">
@@ -1057,22 +1075,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Nov–Dec 2020, by 12/17/2020</t>
+          <t>by 12/21/2020 (due 12/17/2020)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>16 other NDA signers (incl. Parties A–D)</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -1083,38 +1101,50 @@
       </c>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Filing total: 17 parties incl. Gray (#8); residual 16. Parties A–D taken as members: the IOI invitation went to NDA counterparties. Split by type not given.</t>
+          <t>Conditions: the filing states none for the station bids. Private equity sponsor that owned a station group and had talked with Meredith in Fall 2019. First-round bid for all four stations; its price is not disclosed (group range $511–631 million).</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>“The Company entered into confidentiality agreements with 17 parties (including Gray) who had expressed interest in a transaction with the Company.” (p. 60)</t>
+          <t>“a private equity sponsor which had acquired a station group and spoken with the Company in Fall 2019, referred to as Party B” (p. 60)</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="3" t="n">
-        <v>44166</v>
+        <v>44182</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>44151</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>44182</v>
+        <v>44186</v>
       </c>
     </row>
     <row r="11">
@@ -1123,18 +1153,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>12/17/2020</t>
+          <t>by 12/21/2020 (due 12/17/2020)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -1145,20 +1179,34 @@
       </c>
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Preliminary station indications due. Four station bids (#11–#14) and LMG indications from Gray, A, B (#15–#17); arrival days not reported (reported at 12/21 meeting). Four station bids totalled $511–631m for the four-station group.</t>
+          <t>Conditions: the filing states none for the station bids. First-round bid for the Flint-Saginaw-Bay City station only; its price is not disclosed.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>“submit preliminary indications of interest by December 17, 2020” (p. 60)</t>
+          <t>“Another strategic party, referred to as Party C, bid on the Flint-Saginaw-Bay City station only.” (p. 60)</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -1171,10 +1219,10 @@
         <v>44182</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>44182</v>
+        <v>44151</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>44182</v>
+        <v>44186</v>
       </c>
     </row>
     <row r="12">
@@ -1188,12 +1236,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1231,17 +1279,17 @@
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Preliminary, all four select stations; own price not disclosed (group range $511–631m, #10). Conditions: filing’s “non-binding, diligence, debt financing” sentence sits in the LMG paragraph; its reach to station bids unclear.</t>
+          <t>Conditions: the filing states none for the station bids. Investment firm whose portfolio company owned a small station group. First-round bid for the Mobile-Pensacola and Flint-Saginaw-Bay City stations; its price is not disclosed.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>“Two parties bid for all four stations: a strategic party referred to as Party A, and a private equity sponsor” (p. 60)</t>
+          <t>“An investment firm with a portfolio company that currently owned a small station group, referred to as Party D, bid on the Mobile- Pensacola and Flint-Saginaw-Bay City stations.” (p. 60)</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S12" s="2" t="n"/>
@@ -1266,17 +1314,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Gray Television, Inc. (Gray)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -1289,7 +1337,7 @@
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1299,7 +1347,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
@@ -1309,17 +1357,17 @@
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Preliminary, all four select stations; price not disclosed. PE sponsor that had acquired a station group and spoke with Meredith in Fall 2019.</t>
+          <t>Heavy: subject to third-party debt financing and customary diligence; non-binding. Indicated interest in LMG after a simultaneous NMG spin-off, at an enterprise value of $2.5–2.7 billion all cash (not per share). Gray made no bid for the station group alone.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>“a private equity sponsor which had acquired a station group and spoken with the Company in Fall 2019, referred to as Party B” (p. 60)</t>
+          <t>“Gray indicated a value range of $2.5-$2.7 billion in an all cash transaction.” (p. 60)</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S13" s="2" t="n"/>
@@ -1344,7 +1392,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1354,7 +1402,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1377,7 +1425,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
@@ -1387,17 +1435,17 @@
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Preliminary, Flint-Saginaw-Bay City station only; price not disclosed.</t>
+          <t>Heavy: subject to third-party debt financing and customary diligence; non-binding. Indicated interest in LMG after an NMG spin-off at an enterprise value of $2.6–2.8 billion (not per share); the form of consideration is not stated. Made alongside its station bid.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>“Another strategic party, referred to as Party C, bid on the Flint-Saginaw-Bay City station only.” (p. 60)</t>
+          <t>“Party A indicated a value range of $2.6-$2.8 billion.” (p. 60)</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S14" s="2" t="n"/>
@@ -1422,7 +1470,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1432,7 +1480,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -1445,7 +1493,7 @@
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1455,7 +1503,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
@@ -1465,17 +1513,17 @@
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Preliminary, Mobile-Pensacola and Flint-Saginaw-Bay City stations; price not disclosed. Investment firm whose portfolio company owns a small station group.</t>
+          <t>Heavy: subject to third-party debt financing and customary diligence; non-binding. Indicated interest in LMG after an NMG spin-off at an enterprise value of $2.5–2.75 billion (not per share), in cash and stock in proportions to be determined.</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>“An investment firm with a portfolio company that currently owned a small station group, referred to as Party D, bid on the Mobile- Pensacola and Flint-Saginaw-Bay City stations.” (p. 60)</t>
+          <t>“Party B indicated a value range of $2.5-$2.75 billion in a combination of cash and stock to be determined.” (p. 60)</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S15" s="2" t="n"/>
@@ -1495,22 +1543,18 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>by 12/21/2020 (due 12/17/2020)</t>
+          <t>12/17/2020</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Meredith</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -1521,39 +1565,25 @@
       </c>
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Non-binding; subject to diligence and third-party debt financing. LMG after NMG spin-off, EV $2.5–2.7bn all cash; not per share. Gray made no bid for the four stations alone.</t>
+          <t>Due date for preliminary indications of interest on the four select stations. The board reviewed the results on 12/21/2020: 4 of the 20 contacted parties had bid on stations, and Gray, Party A and Party B had indicated interest in LMG.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>“Gray indicated a value range of $2.5-$2.7 billion in an all cash transaction.” (p. 60)</t>
+          <t>“submit preliminary indications of interest by December 17, 2020.” (p. 60)</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>Q4; Q5</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S16" s="2" t="n"/>
@@ -1561,10 +1591,10 @@
         <v>44182</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>44151</v>
+        <v>44182</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>44186</v>
+        <v>44182</v>
       </c>
     </row>
     <row r="17">
@@ -1573,22 +1603,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>by 12/21/2020 (due 12/17/2020)</t>
+          <t>by 12/17/2020</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>NDA signers that made no first-round proposal</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -1599,39 +1629,33 @@
       </c>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="n"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Non-binding; subject to diligence and third-party debt financing. LMG after NMG spin-off, EV $2.6–2.8bn; consideration form not stated; not per share.</t>
+          <t>Count: 12–16. The count is 17 signers minus Gray minus those of Parties A–D who were signers: 12 if all four were (likely, since only counterparties were invited), up to 16 if none were. None was invited to round 2.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>“Party A indicated a value range of $2.6-$2.8 billion.” (p. 60)</t>
+          <t>“Representatives of Moelis reported to our Board that, of the 20 parties contacted, four submitted first round bids.” (p. 60)</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>Q4; Q5</t>
+          <t>Q2; Q4</t>
         </is>
       </c>
       <c r="S17" s="2" t="n"/>
@@ -1642,7 +1666,7 @@
         <v>44151</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>44186</v>
+        <v>44182</v>
       </c>
     </row>
     <row r="18">
@@ -1651,76 +1675,58 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>by 12/21/2020 (due 12/17/2020)</t>
+          <t>after the 12/21/2020 board meeting</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Non-binding; subject to diligence and third-party debt financing. LMG after NMG spin-off, EV $2.5–2.75bn, cash and stock mix to be determined; not per share.</t>
+          <t>Board invited the four first-round station bidders (Parties A–D) to a second round with full data room access and LMG management diligence calls. Gray was added by the 01/12/2021 invitation. No due date was set until 01/12/2021.</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>“Party B indicated a value range of $2.5-$2.75 billion in a combination of cash and stock to be determined.” (p. 60)</t>
+          <t>“Each of the parties that submitted first round proposals for the select stations was invited to participate in the second round and granted full data room access.” (p. 60)</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>Q4; Q5</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="3" t="n">
-        <v>44182</v>
+        <v>44186</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>44151</v>
+        <v>44186</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>44186</v>
+        <v>44208</v>
       </c>
     </row>
     <row r="19">
@@ -1729,70 +1735,58 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>by 12/17/2020</t>
+          <t>after the 12/21/2020 board meeting</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12 other NDA signers</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+          <t>Meredith</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17 NDA signers − 5 submitters (Gray, A, B, C, D) = 12. Filing: of 20 contacted, four submitted station bids; Gray gave only an LMG indication. None invited to round 2 (#19).</t>
+          <t>Information access differs: the board had select, value-driving LMG information given only to the parties interested in LMG (Gray, Party A, Party B). Parties C and D got station information only.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>“Representatives of Moelis reported to our Board that, of the 20 parties contacted, four submitted first round bids.” (p. 60)</t>
+          <t>“our Board instructed our senior management and advisors to provide select, value-driving information to parties who expressed interest in a LMG transaction” (p. 60)</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="3" t="n">
-        <v>44182</v>
-      </c>
-      <c r="U19" s="2" t="n"/>
+        <v>44186</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>44186</v>
+      </c>
       <c r="V19" s="3" t="n">
-        <v>44182</v>
+        <v>44208</v>
       </c>
     </row>
     <row r="20">
@@ -1801,7 +1795,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>after 12/21/2020 meeting</t>
+          <t>01/12/2021</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1812,7 +1806,7 @@
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -1831,12 +1825,12 @@
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Board advanced all four station bidders (A, B, C, D) to second round with full data room access; Gray continued on LMG (invited to final station offers 01/12, #21). Undated consequence of 12/21 meeting.</t>
+          <t>Moelis invited Gray and Parties A–D to submit final offers for the select station group by 01/25/2021, with markups of an asset purchase agreement. Gray, A and B were also invited to submit LMG proposals by that date; these were not called final.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>“Each of the parties that submitted first round proposals for the select stations was invited to participate in the second round and granted full data room access.” (p. 60)</t>
+          <t>“representatives of Moelis invited Gray, Party A, Party B, Party C and Party D to submit final offers for the select station group no later than” (p. 60)</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -1846,10 +1840,10 @@
       </c>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="3" t="n">
-        <v>44186</v>
+        <v>44208</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>44186</v>
+        <v>44208</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>44208</v>
@@ -1861,18 +1855,18 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>after 12/21/2020 meeting</t>
+          <t>01/25/2021</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Meredith (to Gray, Party A, Party B)</t>
+          <t>Meredith</t>
         </is>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -1891,24 +1885,28 @@
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Information access: board directs that select, value-driving LMG information go to parties that expressed LMG interest (Gray, A, B), not to station-only bidders C and D by implication.</t>
+          <t>Due date for final station offers and LMG proposals. Bids arrived on 01/25 and 01/26/2021, so at least one came after the due date; the board considered all of them on 01/28/2021. Markups from Gray, A, C and D had arrived on 01/21/2021.</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>“provide select, value-driving information to parties who expressed interest in a LMG transaction while proceeding with the next phase of the select station process” (p. 60)</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="n"/>
+          <t>“On January 25 and 26, 2021, the Company received five (including one from Gray) final indications of interest for the select stations” (p. 61)</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="3" t="n">
-        <v>44186</v>
+        <v>44221</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>44186</v>
+        <v>44221</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>44208</v>
+        <v>44221</v>
       </c>
     </row>
     <row r="22">
@@ -1917,18 +1915,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/12/2021</t>
+          <t>01/25/2021 or 01/26/2021</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n"/>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1939,36 +1941,50 @@
       </c>
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Final station offers from Gray, A, B, C, D due 01/25/2021 with asset purchase agreement markups; Gray, A, B also invited to submit LMG proposals by same date. Markups from Gray, A, C, D arrived 01/21 (not B).</t>
+          <t>Light: subject only to certain due diligence items and contract terms. Offered $425 million cash for the select stations except Flint-Saginaw-Bay City, as a first step toward acquiring LMG. It answered the final solicitation and came with an asset purchase agreement markup.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>“invited Gray, Party A, Party B, Party C and Party D to submit final offers for the select station group no later than” (p. 60)</t>
+          <t>“Gray proposed to purchase the select station group (other than the Flint-Saginaw-Bay City station) for $425 million in cash” (p. 61)</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q3</t>
+          <t>Q3; Q5</t>
         </is>
       </c>
       <c r="S22" s="2" t="n"/>
       <c r="T22" s="3" t="n">
-        <v>44208</v>
+        <v>44221</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>44208</v>
+        <v>44221</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>44208</v>
+        <v>44222</v>
       </c>
     </row>
     <row r="23">
@@ -1977,18 +1993,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/25/2021</t>
+          <t>01/25/2021 or 01/26/2021</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n"/>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1999,25 +2019,39 @@
       </c>
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Seven submissions arrived 01/25–26: five final station offers and two revised LMG indications (Gray, B). At least one came 01/26, after the due date; bidder not identified; all considered 01/28. Party A gave no LMG indication.</t>
+          <t>Light: subject to certain diligence items and contract terms; no financing contingency in a final proposal. Bid for all LMG RemainCo stock in cash at an enterprise value of $2.6–2.7 billion (low end up from $2.5 billion), not per share. Called a revised preliminary indication; no markup.</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>“the Company received five (including one from Gray) final indications of interest for the select stations and two (including one from Gray) revised preliminary indications of interest for LMG” (p. 61)</t>
+          <t>“Gray proposed to purchase for cash all of the stock of LMG RemainCo based on an enterprise value of $2.6-$2.7 billion” (p. 61)</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q3; Q5</t>
         </is>
       </c>
       <c r="S23" s="2" t="n"/>
@@ -2028,7 +2062,7 @@
         <v>44221</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>44221</v>
+        <v>44222</v>
       </c>
     </row>
     <row r="24">
@@ -2037,12 +2071,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>01/25–26/2021</t>
+          <t>01/25/2021 or 01/26/2021</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc.</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2075,7 +2109,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
@@ -2085,17 +2119,17 @@
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Subject to certain diligence items and contract terms. Three stations (excl. Flint-Saginaw-Bay City) $425m cash as first step to LMG. Final-offer response; APA markup 01/21.</t>
+          <t>Heavy: debt commitment letters were only promised 'shortly thereafter'. Offered $560 million cash for all four stations; a final offer with a markup filed 01/21/2021. Party A made no LMG proposal, although invited to.</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>“Gray proposed to purchase the select station group (other than the Flint-Saginaw-Bay City station) for $425 million in cash” (p. 61)</t>
+          <t>“Party A proposed to purchase all four stations of the select station group for $560 million in cash” (p. 61)</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3; Q5</t>
         </is>
       </c>
       <c r="S24" s="2" t="n"/>
@@ -2115,22 +2149,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>01/25–26/2021</t>
+          <t>01/25/2021 or 01/26/2021</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc.</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -2163,17 +2197,17 @@
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Subject to diligence items and contract terms; substantive diligence still ahead (done by 04/14, #44); cash plus new debt, no commitment reported. LMG RemainCo all stock, EV $2.6–2.7bn cash; “revised preliminary” indication; public-company basis.</t>
+          <t>Heavy: subject to completion of due diligence, and funded partly by new equity and new debt. Offered $510 million cash for the station group. Informal: no asset purchase agreement markup was filed, so the bid was not on the requested basis.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>“Gray proposed to purchase for cash all of the stock of LMG RemainCo based on an enterprise value of $2.6-$2.7 billion” (p. 61)</t>
+          <t>“Party B proposed to purchase the select station group for $510 million in cash.” (p. 61)</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>Q4; Q5</t>
+          <t>Q3; Q5</t>
         </is>
       </c>
       <c r="S25" s="2" t="n"/>
@@ -2193,22 +2227,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>01/25–26/2021</t>
+          <t>01/25/2021 or 01/26/2021</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -2221,12 +2255,12 @@
       <c r="I26" s="2" t="n"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Formal</t>
+          <t>Informal</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2241,17 +2275,17 @@
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Financing not yet committed: debt commitment letters promised later. All four stations $560m cash. Final-offer response with APA markup (01/21).</t>
+          <t>Heavy: subject to due diligence and contract terms, and financed by cash, new equity and new debt. Reconfirmed LMG RemainCo interest in cash and stock at an enterprise value of $2.5–2.7 billion (high end down from $2.75 billion). Wanted Meredith shareholders to keep a stake.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed to purchase all four stations of the select station group for $560 million in cash and pledged to provide executed debt financing commitment letters” (p. 61)</t>
+          <t>“Party B reconfirmed its interest in acquiring LMG RemainCo in a cash/stock transaction based on an enterprise value of $2.5-$2.7 billion” (p. 61)</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3; Q5</t>
         </is>
       </c>
       <c r="S26" s="2" t="n"/>
@@ -2271,17 +2305,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>01/25–26/2021</t>
+          <t>01/25/2021 or 01/26/2021</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2304,12 +2338,12 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Informal</t>
+          <t>Formal</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
@@ -2319,17 +2353,17 @@
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Subject to completion of due diligence and contract terms. Four stations $510m cash. No APA markup, so not on the basis the final solicitation requested.</t>
+          <t>Light: subject to final confirmatory due diligence. Offered $63 million cash for the Flint-Saginaw-Bay City station; a final offer with a markup filed 01/21/2021.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>“Party B proposed to purchase the select station group for $510 million in cash.” (p. 61)</t>
+          <t>“Party C proposed to acquire the Flint-Saginaw-Bay City station for $63 million in cash, subject to completion of final confirmatory due diligence.” (p. 61)</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3; Q5</t>
         </is>
       </c>
       <c r="S27" s="2" t="n"/>
@@ -2349,12 +2383,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/25–26/2021</t>
+          <t>01/25/2021 or 01/26/2021</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2364,7 +2398,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -2377,17 +2411,17 @@
       <c r="I28" s="2" t="n"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Informal</t>
+          <t>Formal</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
@@ -2397,17 +2431,17 @@
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Subject to completion of due diligence and contract terms; financing from cash, new equity, new debt. LMG RemainCo EV $2.5–2.7bn cash/stock (top cut from $2.75bn); wants holders to keep a stake.</t>
+          <t>Light: subject to confirmatory diligence and contract terms; expected no financing contingency. Offered $61 million cash for the Mobile-Pensacola station; a final offer with a markup filed 01/21/2021.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>“Party B reconfirmed its interest in acquiring LMG RemainCo in a cash/stock transaction based on an enterprise value of $2.5-$2.7 billion” (p. 61)</t>
+          <t>“Party D proposed to acquire the Mobile-Pensacola station for $61 million in cash” (p. 61)</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>Q4; Q5</t>
+          <t>Q3; Q5</t>
         </is>
       </c>
       <c r="S28" s="2" t="n"/>
@@ -2427,17 +2461,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/25–26/2021</t>
+          <t>01/25/2021 or 01/26/2021</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2475,17 +2509,17 @@
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Subject to final confirmatory diligence. Flint-Saginaw-Bay City station $63m cash. Final-offer response with APA markup (01/21).</t>
+          <t>Light: same conditions as the alternative in the previous row. Alternative offer of $146 million cash for both the Mobile-Pensacola and Flint-Saginaw-Bay City stations.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>“Party C proposed to acquire the Flint-Saginaw-Bay City station for $63 million in cash, subject to completion of final confirmatory due diligence.” (p. 61)</t>
+          <t>“or both the Mobile-Pensacola and Flint-Saginaw-Bay City stations for $146 million in cash” (p. 61)</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3; Q5</t>
         </is>
       </c>
       <c r="S29" s="2" t="n"/>
@@ -2505,22 +2539,18 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>01/25–26/2021</t>
+          <t>01/28/2021</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -2531,50 +2561,36 @@
       </c>
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Confirmatory diligence and contract terms; expects funds so no financing contingency. Mobile-Pensacola station $61m cash. Final-offer response with APA markup (01/21).</t>
+          <t>Citing values indicated by potential acquirers (best station combination $583 million), the board paused the select station sale and turned to a sale of LMG with a simultaneous NMG spin-off. The station sale never resumed.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>“Party D proposed to acquire the Mobile-Pensacola station for $61 million in cash” (p. 61)</t>
+          <t>“our Board decided to pause the select station sale process at that time and instructed our senior management and advisors to focus their efforts on advancing preparations” (p. 62)</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S30" s="2" t="n"/>
       <c r="T30" s="3" t="n">
-        <v>44221</v>
+        <v>44224</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>44221</v>
+        <v>44224</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>44222</v>
+        <v>44224</v>
       </c>
     </row>
     <row r="31">
@@ -2583,22 +2599,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>01/25–26/2021</t>
+          <t>by 01/28/2021</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2609,50 +2625,46 @@
       </c>
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="n"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Alternative to #29, same conditions: Mobile-Pensacola and Flint-Saginaw-Bay City stations $146m cash.</t>
+          <t>Inferred: the station sale in which it bid was paused on 01/28/2021. Afterwards only Gray and Party B were reported in LMG diligence and invited to bid (02/12, 03/17/2021). Party A made no LMG proposal in round 2 although invited to.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>“both the Mobile-Pensacola and Flint-Saginaw-Bay City stations for $146 million in cash” (p. 61)</t>
+          <t>“Moelis provided an update on the sale process and diligence activity by Gray and Party B and their advisors and potential lenders.” (p. 63)</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S31" s="2" t="n"/>
       <c r="T31" s="3" t="n">
-        <v>44221</v>
+        <v>44224</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>44221</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>44222</v>
+        <v>44224</v>
       </c>
     </row>
     <row r="32">
@@ -2661,18 +2673,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>01/28/2021</t>
+          <t>by 01/28/2021</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -2686,22 +2702,32 @@
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
+      <c r="M32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Board pauses the select station sale on the values indicated (best station combination $583m) and redirects to an LMG sale with NMG spin-off; Gray and B (the two LMG indications) continue.</t>
+          <t>Inferred: the station sale in which it bid was paused on 01/28/2021. Afterwards only Gray and Party B were reported in LMG diligence and invited to bid (02/12, 03/17/2021). Party C only ever bid for one station.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>“our Board decided to pause the select station sale process at that time and instructed our senior management and advisors to focus their efforts on advancing preparations” (p. 62)</t>
+          <t>“Moelis provided an update on the sale process and diligence activity by Gray and Party B and their advisors and potential lenders.” (p. 63)</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S32" s="2" t="n"/>
@@ -2709,7 +2735,7 @@
         <v>44224</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>44224</v>
+        <v>44221</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>44224</v>
@@ -2726,12 +2752,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2755,7 +2781,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Other stated reason</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -2765,12 +2791,12 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Station stage paused (#31); A had no LMG indication in round 2 and is not in the LMG stage (process letters 03/17 to Gray, B only). Target’s reason: values indicated.</t>
+          <t>Inferred: the station sale in which it bid was paused on 01/28/2021. Afterwards only Gray and Party B were reported in LMG diligence and invited to bid (02/12, 03/17/2021). Party D bid only for stations in round 2. It returned on its own with an LMG proposal on 03/11/2021.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>“After full discussion and based on current values being indicated by potential acquirors, our Board decided to pause the select station sale process at that time” (p. 62)</t>
+          <t>“Moelis provided an update on the sale process and diligence activity by Gray and Party B and their advisors and potential lenders.” (p. 63)</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
@@ -2795,29 +2821,29 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>by 01/28/2021</t>
+          <t>03/11/2021</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
@@ -2827,24 +2853,16 @@
       <c r="M34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>Other stated reason</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Station-only bidder; station stage paused (#31) and C never reappears. Target’s reason: values indicated.</t>
+          <t>Party D came back unsolicited with a written LMG proposal (next row). It was the first LMG interest Party D had shown; its earlier bids were for stations only.</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>“After full discussion and based on current values being indicated by potential acquirors, our Board decided to pause the select station sale process at that time” (p. 62)</t>
+          <t>“the Company received a written non-binding letter of interest from Party D to acquire LMG in a Reverse Morris Trust transaction” (p. 63)</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -2854,13 +2872,13 @@
       </c>
       <c r="S34" s="2" t="n"/>
       <c r="T34" s="3" t="n">
-        <v>44224</v>
+        <v>44266</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>44221</v>
+        <v>44266</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>44224</v>
+        <v>44266</v>
       </c>
     </row>
     <row r="35">
@@ -2869,7 +2887,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>by 01/28/2021</t>
+          <t>03/11/2021</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2884,57 +2902,61 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>Other stated reason</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Station-only bidder; station stage paused (#31); returns 03/11 with an LMG proposal (#37). Target’s reason: values indicated.</t>
+          <t>Heavy: subject to diligence and to reverse diligence confirming synergies, and conditional on a separate deal with Party E. Reverse Morris Trust (spin-off of LMG, not NMG): $2.5 billion cash plus 50.7% of the combined company, whose net leverage would be 6.75x. Not per share.</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>“After full discussion and based on current values being indicated by potential acquirors, our Board decided to pause the select station sale process at that time” (p. 62)</t>
+          <t>“Party D’s proposal included $2.5 billion of cash consideration (to refinance the Company’s debt and make a cash dividend to the Company’s shareholders) and a 50.7% ownership interest” (p. 63)</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q3; Q6</t>
         </is>
       </c>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="3" t="n">
-        <v>44224</v>
+        <v>44266</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>44221</v>
+        <v>44266</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>44224</v>
+        <v>44266</v>
       </c>
     </row>
     <row r="36">
@@ -2943,25 +2965,25 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2021</t>
+          <t>03/16/2021</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Deloitte Tax LLP</t>
+          <t>Meredith</t>
         </is>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
@@ -2973,24 +2995,24 @@
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Target tax adviser; first seen acting 03/05/2021 on a call with Party B and its accountants on NMG-LMG separation steps.</t>
+          <t>Information access differs: Moelis gave Party D access to a limited data room so it could finalize its indication. Gray and Party B had had the full LMG diligence process since February 2021.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>“Deloitte Tax LLP (“Deloitte”), tax advisors to the Company, spoke with representatives of Party B and its accountants” (p. 63)</t>
+          <t>“Moelis granted Party D access to a limited data room to finalize its indication of interest.” (p. 63)</t>
         </is>
       </c>
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="3" t="n">
-        <v>44260</v>
+        <v>44271</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>44260</v>
+        <v>44271</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>44260</v>
+        <v>44271</v>
       </c>
     </row>
     <row r="37">
@@ -2999,64 +3021,58 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/11/2021</t>
+          <t>03/17/2021</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M37" s="2" t="n"/>
       <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Returned after exit #34 with an unsolicited LMG proposal (#37).</t>
+          <t>Moelis sent Gray and Party B process letters and draft merger and separation agreements (3% break fee; $125 million reverse fee; committed financing at signing). Markups were due 04/01/2021; final LMG offers were due 04/14/2021.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>“the Company received a written non-binding letter of interest from Party D to acquire LMG in a Reverse Morris Trust transaction” (p. 63)</t>
+          <t>“representatives of Moelis provided process letters to Gray and Party B and invited them to submit final offers for LMG no later than April 14, 2021.” (p. 63)</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q6</t>
+          <t>Q1; Q7</t>
         </is>
       </c>
       <c r="S37" s="2" t="n"/>
       <c r="T37" s="3" t="n">
-        <v>44266</v>
+        <v>44272</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>44266</v>
+        <v>44272</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>44266</v>
+        <v>44272</v>
       </c>
     </row>
     <row r="38">
@@ -3065,12 +3081,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>03/11/2021</t>
+          <t>03/23/2021</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3080,32 +3096,20 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n">
         <v>1</v>
       </c>
@@ -3113,28 +3117,24 @@
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Subject to diligence and reverse diligence to confirm synergies. RMT: LMG spun and combined with D’s and Party E’s stations; $2.5bn cash (debt refinancing, dividend) plus 50.7% of combined company; 6.75x leverage; not per share.</t>
+          <t>Party B said it intended to bid all cash rather than in cash and stock; no price was given.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>“Party D’s proposal included $2.5 billion of cash consideration (to refinance the Company’s debt and make a cash dividend to the Company’s shareholders) and a 50.7% ownership interest” (p. 63)</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>Q1; Q4; Q5; Q7</t>
-        </is>
-      </c>
+          <t>“Party B communicated that it intended to submit an all-cash bid after completing its analysis of structure and other elements of the transaction.” (p. 64)</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="n"/>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="3" t="n">
-        <v>44266</v>
+        <v>44278</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>44266</v>
+        <v>44278</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>44266</v>
+        <v>44278</v>
       </c>
     </row>
     <row r="39">
@@ -3143,15 +3143,19 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>03/16/2021</t>
+          <t>03/30/2021</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Meredith (to Party D)</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n"/>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -3161,36 +3165,42 @@
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
+      <c r="M39" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Information access: Moelis, at the Company’s direction, gives Party D a limited data room so it can finalize its indication.</t>
+          <t>Target let Party D into the definitive-document stage: all transaction agreement drafts, with markups due 04/08/2021. That was 13 days after Gray and Party B got their drafts. On 03/31/2021 it also sent a structure preferring an NMG spin-off and reverse-diligence requests. Party D was given no final-bid date.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>“Moelis granted Party D access to a limited data room to finalize its indication of interest” (p. 63)</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="n"/>
+          <t>“representatives of Moelis provided drafts of all of the transaction agreements to Party D.” (p. 64)</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
       <c r="S39" s="2" t="n"/>
       <c r="T39" s="3" t="n">
-        <v>44271</v>
+        <v>44285</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>44271</v>
+        <v>44285</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>44271</v>
+        <v>44285</v>
       </c>
     </row>
     <row r="40">
@@ -3199,18 +3209,18 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>03/17/2021</t>
+          <t>04/02/2021</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
+          <t>Eversheds Sutherland (US) LLP (Eversheds)</t>
         </is>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -3229,28 +3239,24 @@
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Process letters to Gray and B: final LMG offers due 04/14/2021; draft Merger and Separation agreements (3% break fee, $125m reverse fee, committed financing at signing); markups due 04/01. Other drafts 03/20, 03/25.</t>
+          <t>Gray's legal adviser; filed Gray's markups of all the transaction agreements on 04/02/2021.</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>“provided process letters to Gray and Party B and invited them to submit final offers for LMG no later than April 14, 2021” (p. 63)</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>Q1; Q3</t>
-        </is>
-      </c>
+          <t>“Gray’s legal advisors, Eversheds Sutherland (US) LLP” (p. 65)</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="n"/>
       <c r="S40" s="2" t="n"/>
       <c r="T40" s="3" t="n">
-        <v>44272</v>
+        <v>44288</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>44272</v>
+        <v>44288</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>44272</v>
+        <v>44288</v>
       </c>
     </row>
     <row r="41">
@@ -3259,15 +3265,19 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>03/30/2021</t>
+          <t>04/08/2021</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Meredith (to Party D)</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n"/>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -3284,33 +3294,31 @@
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="n"/>
+      <c r="M41" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Admission: Party D gets drafts of all transaction agreements (NMG spin-off, all-cash merger) and is asked for markups by 04/08; 03/31 gets the Company’s preferred structure and a reverse-diligence request list.</t>
+          <t>Party D submitted a markup of the Merger Agreement only. It was subject to completing diligence, transaction structure and Party D's financing, and would cut the $125 million reverse fee without a counter-figure. Party D also sent structure proposals on 04/02 and 04/13/2021.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>“representatives of Moelis provided drafts of all of the transaction agreements to Party D” (p. 64)</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“Party D’s legal advisors submitted a markup of the Merger Agreement on behalf of Party D, but did not provide markups of any of the other transaction agreements.” (p. 65)</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="3" t="n">
-        <v>44285</v>
+        <v>44294</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>44285</v>
+        <v>44294</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>44285</v>
+        <v>44294</v>
       </c>
     </row>
     <row r="42">
@@ -3319,12 +3327,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>04/02/2021</t>
+          <t>04/11/2021</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Eversheds Sutherland (US) LLP</t>
+          <t>Wells Fargo Securities LLC (Wells Fargo)</t>
         </is>
       </c>
       <c r="D42" s="2" t="n"/>
@@ -3349,24 +3357,24 @@
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Gray’s legal adviser; first seen acting 04/02/2021, submitting Gray’s markups of all transaction agreements (MNI excluded, 5% break fee, station option, shareholder voting agreement).</t>
+          <t>Gray's financial adviser; took part in the 04/11/2021 feedback call on Gray's markups before Gray's final bid.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>“Gray’s legal advisors, Eversheds Sutherland (US) LLP (“Eversheds”), submitted markups of each of the transaction agreements on behalf of Gray” (p. 65)</t>
+          <t>“financial advisors, Wells Fargo Securities LLC” (p. 65)</t>
         </is>
       </c>
       <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="3" t="n">
-        <v>44288</v>
+        <v>44297</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>44288</v>
+        <v>44297</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>44288</v>
+        <v>44297</v>
       </c>
     </row>
     <row r="43">
@@ -3375,18 +3383,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>04/11/2021</t>
+          <t>04/14/2021</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Wells Fargo Securities LLC</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n"/>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
@@ -3397,32 +3409,50 @@
       </c>
       <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="n"/>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="n"/>
-      <c r="L43" s="2" t="n"/>
-      <c r="M43" s="2" t="n"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Gray’s financial adviser; first seen acting 04/11/2021 on a call with Cooley and Moelis before Gray’s final bid. (Wells Fargo Bank separately a Gray lender.)</t>
+          <t>Light: debt commitment letters; substantive diligence completed. Final offer: all LMG RemainCo stock for cash at $2.45 billion enterprise value (down from $2.6–2.7 billion); MNI excluded. Its 04/02/2021 markups sought a 5% break fee and a station purchase option.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>“financial advisors, Wells Fargo Securities LLC (“Wells Fargo”)” (p. 65)</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="n"/>
+          <t>“Gray submitted a proposal to purchase all of the stock of LMG RemainCo for cash based on an enterprise value of $2.45 billion” (p. 66)</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>Q3; Q7</t>
+        </is>
+      </c>
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="3" t="n">
-        <v>44297</v>
+        <v>44300</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>44297</v>
+        <v>44300</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>44297</v>
+        <v>44300</v>
       </c>
     </row>
     <row r="44">
@@ -3436,13 +3466,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
@@ -3453,25 +3487,39 @@
       </c>
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Final LMG offers due. Gray and B bid 04/14 (#44, #45); D bid 04/15 (#46) — the filing does not say D was given this date. Extended 04/16 (#47).</t>
+          <t>Light: debt commitment letters; substantive diligence completed. Final offer: all LMG RemainCo stock for cash at $2.3 billion enterprise value (down from $2.5–2.7 billion), MNI included. Merger Agreement markup plus an issues list; would divest one overlap station.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>“invited them to submit final offers for LMG no later than April 14, 2021” (p. 63)</t>
+          <t>“Party B also submitted a proposal to purchase all of the stock of LMG RemainCo for cash based on an enterprise value of $2.3 billion” (p. 66)</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q3; Q7</t>
         </is>
       </c>
       <c r="S44" s="2" t="n"/>
@@ -3496,17 +3544,13 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc.</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Meredith</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
@@ -3517,39 +3561,25 @@
       </c>
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
       <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Debt commitment letters; substantive diligence done (full completion confirmed later, #56). LMG RemainCo EV $2.45bn cash, down from $2.6–2.7bn; MNI excluded; will divest Flint station; with 04/02 markups.</t>
+          <t>Due date for final LMG offers from Gray and Party B; both bid on the day. On 04/16/2021 the board judged none of the proposals adequate and gave Gray and Party B a new date (04/20/2021).</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>“Gray submitted a proposal to purchase all of the stock of LMG RemainCo for cash based on an enterprise value of $2.45 billion” (p. 66)</t>
+          <t>“invited them to submit final offers for LMG no later than April 14, 2021.” (p. 63)</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="S45" s="2" t="n"/>
@@ -3569,12 +3599,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>04/14/2021</t>
+          <t>04/15/2021</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3597,7 +3627,7 @@
       <c r="I46" s="2" t="n"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3607,7 +3637,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
@@ -3617,28 +3647,28 @@
       <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Debt commitment letters; substantive diligence done. LMG RemainCo EV $2.3bn all cash (flagged 03/23), incl. MNI; Merger Agreement markup and issues list; will divest one overlap station.</t>
+          <t>Heavy: 'highly confident' letters only, up to three weeks needed for committed debt, no equity commitment, still negotiating with Party E. Morris Trust (NMG spin-off): $2.5 billion cash plus 50.8% of the combined company, MNI included; 7.0x leverage. Formal on its 04/08/2021 markup.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>“Party B also submitted a proposal to purchase all of the stock of LMG RemainCo for cash based on an enterprise value of $2.3 billion” (p. 66)</t>
+          <t>“Party D submitted a proposal for a Morris Trust transaction reflecting $2.5 billion in cash consideration” (p. 66)</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q3; Q7</t>
         </is>
       </c>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="3" t="n">
-        <v>44300</v>
+        <v>44301</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>44300</v>
+        <v>44301</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>44300</v>
+        <v>44301</v>
       </c>
     </row>
     <row r="47">
@@ -3647,22 +3677,18 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>04/15/2021</t>
+          <t>04/16/2021</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline revised</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
@@ -3673,50 +3699,36 @@
       </c>
       <c r="H47" s="2" t="n"/>
       <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n"/>
       <c r="N47" s="2" t="n"/>
       <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Financing not committed (“highly confident” debt letters, needs up to three weeks; no equity commitments); still negotiating with Party E. Morris Trust (NMG spin-off): $2.5bn cash plus 50.8%; MNI included. Formal via 04/08 Merger Agreement markup.</t>
+          <t>Board found none of the proposals adequate. Gray and Party B were told to raise value significantly, address contract terms and resubmit by 04/20/2021; Moelis passed this on the same day.</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>“Party D submitted a proposal for a Morris Trust transaction reflecting $2.5 billion in cash consideration” (p. 66)</t>
+          <t>“increase their value proposals significantly and address other contract terms if they desired to be successful in potentially acquiring LMG and ask them to resubmit proposals by April 20, 2021.” (p. 66)</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>Q5; Q7; Q8</t>
+          <t>Q7; Q1</t>
         </is>
       </c>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="3" t="n">
-        <v>44301</v>
+        <v>44302</v>
       </c>
       <c r="U47" s="3" t="n">
-        <v>44301</v>
+        <v>44302</v>
       </c>
       <c r="V47" s="3" t="n">
-        <v>44301</v>
+        <v>44302</v>
       </c>
     </row>
     <row r="48">
@@ -3736,7 +3748,7 @@
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Deadline revised</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
@@ -3755,17 +3767,17 @@
       <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Board finds no proposal adequate; Gray and B told that same day to raise value significantly, fix contract terms and resubmit by 04/20/2021.</t>
+          <t>Target set requirements for Party D: catch up with the other bidders, deliver firm financing commitments, raise the cash component, clarify value and sources and uses, and answer regulatory concerns. No due date was given.</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>“communicate to Gray and Party B that they would need to increase their value proposals significantly and address other contract terms” (p. 66)</t>
+          <t>“communicate to Party D that it would need to advance its proposal to catch up with the other parties, deliver firm financing commitments, increase the cash component” (p. 67)</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1; Q7</t>
         </is>
       </c>
       <c r="S48" s="2" t="n"/>
@@ -3785,12 +3797,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>04/16/2021</t>
+          <t>04/18/2021</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Meredith (to Party D)</t>
+          <t>Meredith</t>
         </is>
       </c>
       <c r="D49" s="2" t="n"/>
@@ -3815,24 +3827,28 @@
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Requirement to Party D, told that day: catch up with the others, deliver firm financing commitments, raise the cash component, clarify value and sources and uses, answer regulatory concerns. No due date stated.</t>
+          <t>Information access differs: Moelis sent Gray and Party B, but not Party D, a quarterly LMG update and a list of items a revised bid had to address (liabilities, closing certainty, break and reverse fees).</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>“communicate to Party D that it would need to advance its proposal to catch up with the other parties, deliver firm financing commitments, increase the cash component” (p. 67)</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="n"/>
+          <t>“representatives of Moelis provided to Gray and Party B a quarterly update on the LMG business” (p. 67)</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>Q1; Q7</t>
+        </is>
+      </c>
       <c r="S49" s="2" t="n"/>
       <c r="T49" s="3" t="n">
-        <v>44302</v>
+        <v>44304</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>44302</v>
+        <v>44304</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>44302</v>
+        <v>44304</v>
       </c>
     </row>
     <row r="50">
@@ -3841,18 +3857,22 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>04/18/2021</t>
+          <t>04/19/2021</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Meredith (to Gray, Party B)</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="n"/>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
@@ -3863,32 +3883,50 @@
       </c>
       <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="n"/>
-      <c r="J50" s="2" t="n"/>
-      <c r="K50" s="2" t="n"/>
-      <c r="L50" s="2" t="n"/>
-      <c r="M50" s="2" t="n"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N50" s="2" t="n"/>
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Information access: Gray and B receive a quarterly LMG business update and a list of items to address in revised bids (liabilities, closing certainty, break and reverse fees).</t>
+          <t>Light: revised financing commitments for the full price. Raised its bid to $2.65 billion cash (enterprise basis, MNI still excluded), cut the break fee to $36 million, accepted the $125 million reverse termination fee, and expected to close in 2021.</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>“representatives of Moelis provided to Gray and Party B a quarterly update on the LMG business and a list of certain items” (p. 67)</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="n"/>
+          <t>“Gray submitted a revised proposal for $2.65 billion in cash (up from $2.45 billion and still based on NMG SpinCo retaining the MNI business).” (p. 67)</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>Q3; Q7; Q1</t>
+        </is>
+      </c>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="3" t="n">
-        <v>44304</v>
+        <v>44305</v>
       </c>
       <c r="U50" s="3" t="n">
-        <v>44304</v>
+        <v>44305</v>
       </c>
       <c r="V50" s="3" t="n">
-        <v>44304</v>
+        <v>44305</v>
       </c>
     </row>
     <row r="51">
@@ -3897,17 +3935,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>04/19/2021</t>
+          <t>04/20/2021</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc.</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3945,28 +3983,28 @@
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Revised financing commitments for full price; expects 2021 closing. EV $2.65bn cash (up from $2.45bn), MNI still excluded; break fee cut to $36m; accepts $125m reverse fee.</t>
+          <t>Light: otherwise unchanged from 04/14/2021 (committed debt, diligence done). Raised its bid to $2.33 billion cash from $2.3 billion, MNI included.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>“Gray submitted a revised proposal for $2.65 billion in cash (up from $2.45 billion and still based on NMG SpinCo retaining the MNI business)” (p. 67)</t>
+          <t>“Party B submitted a revised proposal for $2.33 billion in cash (up from $2.3 billion).” (p. 67)</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q3; Q7; Q1</t>
         </is>
       </c>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="3" t="n">
-        <v>44305</v>
+        <v>44306</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>44305</v>
+        <v>44306</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>44305</v>
+        <v>44306</v>
       </c>
     </row>
     <row r="52">
@@ -3980,17 +4018,13 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
@@ -4001,39 +4035,25 @@
       </c>
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="n"/>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="n"/>
       <c r="N52" s="2" t="n"/>
       <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Otherwise unchanged from #45 (commitment letters, diligence done). EV $2.33bn cash (up from $2.3bn), MNI included.</t>
+          <t>Revised due date for Gray and Party B; both had bid. The board acted on the bids in hand on 04/23/2021.</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>“Party B submitted a revised proposal for $2.33 billion in cash (up from $2.3 billion).” (p. 67)</t>
+          <t>“ask them to resubmit proposals by April 20, 2021.” (p. 66)</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q7; Q1</t>
         </is>
       </c>
       <c r="S52" s="2" t="n"/>
@@ -4053,18 +4073,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>04/20/2021</t>
+          <t>04/23/2021</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="n"/>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
@@ -4075,36 +4099,50 @@
       </c>
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="2" t="n"/>
-      <c r="L53" s="2" t="n"/>
-      <c r="M53" s="2" t="n"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N53" s="2" t="n"/>
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Revised offers due: Gray 04/19 (#50), B 04/20 (#51). Party D, not shown to have this date, bid 04/23 (#53). Target selected Gray on 04/23 (#54).</t>
+          <t>Heavy: otherwise unchanged from 04/15/2021, so financing still not committed. Raised cash to $2.56 billion from $2.50 billion, plus 50.8% of the combined company. On 04/22/2021 Moelis had told Party D to put its best offer forward.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>“ask them to resubmit proposals by April 20, 2021” (p. 66)</t>
+          <t>“Party D submitted a revised Morris Trust proposal providing for $2.56 billion cash consideration” (p. 67)</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q3; Q7; Q1</t>
         </is>
       </c>
       <c r="S53" s="2" t="n"/>
       <c r="T53" s="3" t="n">
-        <v>44306</v>
+        <v>44309</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>44306</v>
+        <v>44309</v>
       </c>
       <c r="V53" s="3" t="n">
-        <v>44306</v>
+        <v>44309</v>
       </c>
     </row>
     <row r="54">
@@ -4118,17 +4156,13 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
@@ -4139,39 +4173,25 @@
       </c>
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n"/>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="n"/>
       <c r="N54" s="2" t="n"/>
       <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Conditions of #46 continue (“otherwise materially unchanged”). $2.56bn cash (up from $2.50bn) plus 50.8%; MNI included. Followed Moelis’s 04/22 request to put its best offer forward.</t>
+          <t>Board chose Gray as preferred bidder and required, before full negotiation: $50 million more cash, confirmation that diligence was done, ability to sign within a week, and no delay from approvals or financing. It told Party B it was not competitive and kept developing Party D.</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>“Party D submitted a revised Morris Trust proposal providing for $2.56 billion cash consideration” (p. 67)</t>
+          <t>“our Board determined that Gray’s proposal was stronger than the other proposals in terms of value and other key elements.” (p. 68)</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>Q5; Q8</t>
+          <t>Q7; Q1</t>
         </is>
       </c>
       <c r="S54" s="2" t="n"/>
@@ -4191,18 +4211,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>04/23/2021</t>
+          <t>by 04/23/2021</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
@@ -4216,22 +4240,32 @@
       <c r="J55" s="2" t="n"/>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
-      <c r="M55" s="2" t="n"/>
-      <c r="N55" s="2" t="n"/>
-      <c r="O55" s="2" t="n"/>
+      <c r="M55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>Preferred bidder: board rates Gray strongest; sets critical deal points for Gray (+$50m cash, diligence complete, sign within a week, no approval/financing delay); B told not competitive; D’s proposal kept under development.</t>
+          <t>Inferred: the board had Party B told its proposal was not competitive, and Party B never bid again. An affiliate later offered Party D preferred financing (04/29/2021), and Party B offered stations to Party D's 05/26/2021 bid.</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>“Our Board authorized senior management and our advisors to go back to Gray with a short list of critical deal points” (p. 68)</t>
+          <t>“Our Board authorized representatives of Moelis to communicate to Party B that its current proposal was not competitive.” (p. 68)</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q8; Q1; Q7</t>
         </is>
       </c>
       <c r="S55" s="2" t="n"/>
@@ -4239,7 +4273,7 @@
         <v>44309</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>44309</v>
+        <v>44306</v>
       </c>
       <c r="V55" s="3" t="n">
         <v>44309</v>
@@ -4251,22 +4285,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>by 04/23/2021</t>
+          <t>after the 04/23/2021 board meeting; by 04/25/2021</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Gray</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -4277,35 +4311,39 @@
       </c>
       <c r="H56" s="2" t="n"/>
       <c r="I56" s="2" t="n"/>
-      <c r="J56" s="2" t="n"/>
-      <c r="K56" s="2" t="n"/>
-      <c r="L56" s="2" t="n"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="M56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>Lower offer than rivals</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Board authorized telling B its $2.33bn (#51) was not competitive (Gray $2.65bn, #50); delivery not reported. B never bid again; later only an affiliate’s financing and station support for Party D (#58, #68).</t>
+          <t>None: diligence confirmed complete, financing committed, and ready to sign within a week. Accepted the $50 million increase (LMG enterprise value $2.7 billion; per-share figure not yet set). Definitive agreements were exchanged from 04/25/2021.</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>“Our Board authorized representatives of Moelis to communicate to Party B that its current proposal was not competitive.” (p. 68)</t>
+          <t>“Gray agreed to the $50 million consideration increase (for a total enterprise valuation of LMG of $2.7 billion) and accepted the other critical deal points” (p. 68)</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q3; Q1; Q7</t>
         </is>
       </c>
       <c r="S56" s="2" t="n"/>
@@ -4313,10 +4351,10 @@
         <v>44309</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>44306</v>
+        <v>44309</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>44309</v>
+        <v>44311</v>
       </c>
     </row>
     <row r="57">
@@ -4325,17 +4363,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>after 04/23/2021 meeting</t>
+          <t>04/26/2021</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc.</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -4353,7 +4391,7 @@
       <c r="I57" s="2" t="n"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4363,7 +4401,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
@@ -4373,28 +4411,28 @@
       <c r="O57" s="2" t="n"/>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>Accepts critical points (#54): diligence complete, can sign within a week, approvals and financing won’t delay closing. EV $2.7bn (+$50m). Per share $14.51 set 05/01–02 by $1.975bn net-debt allocation.</t>
+          <t>Heavy: no firm financing commitments; its 04/27/2021 markup stayed subject to diligence, structure and financing and added tax-opinion and Party E closing conditions. Offered $2.66 billion cash plus 50.2% of the combined company, MNI included, and a $100 million regulatory break fee.</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>“Gray agreed to the $50 million consideration increase (for a total enterprise valuation of LMG of $2.7 billion) and accepted the other critical deal points” (p. 68)</t>
+          <t>“provided for $2.66 billion cash consideration (increased from $2.56 billion, to refinance the Company’s debt and make a cash dividend to the Company’s shareholders)” (p. 69)</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q3; Q1; Q7</t>
         </is>
       </c>
       <c r="S57" s="2" t="n"/>
       <c r="T57" s="3" t="n">
-        <v>44309</v>
+        <v>44312</v>
       </c>
       <c r="U57" s="3" t="n">
-        <v>44309</v>
+        <v>44312</v>
       </c>
       <c r="V57" s="3" t="n">
-        <v>44311</v>
+        <v>44312</v>
       </c>
     </row>
     <row r="58">
@@ -4403,7 +4441,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/26/2021</t>
+          <t>04/27/2021</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4418,7 +4456,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
@@ -4429,21 +4467,9 @@
       </c>
       <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="n"/>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
       <c r="M58" s="2" t="n">
         <v>1</v>
       </c>
@@ -4451,28 +4477,28 @@
       <c r="O58" s="2" t="n"/>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>No firm financing; 04/27 revised markup still subject to diligence, structure and final financing commitments. $2.66bn cash plus 50.2%; MNI included; first $100m regulatory break fee.</t>
+          <t>Target let Party D approach an equity financing source affiliated with the exited Party B, which is a financing-support relationship. This does not form a group (E4).</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>“provided for $2.66 billion cash consideration (increased from $2.56 billion” (p. 69)</t>
+          <t>“The Company gave permission for Party D to speak to an equity financing source affiliated with Party B.” (p. 69)</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>Q5; Q8</t>
+          <t>Q8; Q1; Q7</t>
         </is>
       </c>
       <c r="S58" s="2" t="n"/>
       <c r="T58" s="3" t="n">
-        <v>44312</v>
+        <v>44313</v>
       </c>
       <c r="U58" s="3" t="n">
-        <v>44312</v>
+        <v>44313</v>
       </c>
       <c r="V58" s="3" t="n">
-        <v>44312</v>
+        <v>44313</v>
       </c>
     </row>
     <row r="59">
@@ -4481,18 +4507,22 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/27/2021</t>
+          <t>04/29/2021</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Meredith (to Party D)</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n"/>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
@@ -4503,36 +4533,50 @@
       </c>
       <c r="H59" s="2" t="n"/>
       <c r="I59" s="2" t="n"/>
-      <c r="J59" s="2" t="n"/>
-      <c r="K59" s="2" t="n"/>
-      <c r="L59" s="2" t="n"/>
-      <c r="M59" s="2" t="n"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N59" s="2" t="n"/>
       <c r="O59" s="2" t="n"/>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>Financing support permitted: Company lets Party D approach an equity financing source affiliated with Party B (B already out, #55). B affiliate’s preferred term sheet came 04/29 (#59); replaced by D’s own preferred 05/26 (#68).</t>
+          <t>Heavy: debt papers only 'near final', and a non-binding preferred term sheet from a Party B affiliate. Revised proposal keeping $2.66 billion cash plus 50.2% of the combined company, now with $2.58 billion debt and $275 million preferred (7.27x). MNI included.</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>“The Company gave permission for Party D to speak to an equity financing source affiliated with Party B.” (p. 69)</t>
+          <t>“The revised proposal continued to contemplate a spin-off of the NMG business and included an alternative” (p. 69)</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q3; Q1; Q7</t>
         </is>
       </c>
       <c r="S59" s="2" t="n"/>
       <c r="T59" s="3" t="n">
-        <v>44313</v>
+        <v>44315</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>44313</v>
+        <v>44315</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>44313</v>
+        <v>44315</v>
       </c>
     </row>
     <row r="60">
@@ -4589,17 +4633,17 @@
       <c r="O60" s="2" t="n"/>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>Debt papers “near final”, unsigned; B-affiliate preferred term sheet non-binding. Base case restated: $2.66bn cash plus 50.2%; financing now $2.58bn debt and $275m preferred.</t>
+          <t>Heavy: same financing as the previous row. Alternative to that row: $2.76 billion cash with Meredith shareholders' stake cut from 50.2% to 34%. A later letter put the implied cash dividend at $15.71 per share (p. 71), cash component only.</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>“The proposal included draft debt commitment papers that were characterized as “near final”” (p. 69)</t>
+          <t>“included an alternative to increase the cash consideration from $2.66 billion to $2.76 billion with a reduction of the ownership interest in the new combined company” (p. 69)</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>Q5; Q8</t>
+          <t>Q3; Q1; Q7</t>
         </is>
       </c>
       <c r="S60" s="2" t="n"/>
@@ -4619,22 +4663,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>04/29/2021</t>
+          <t>05/03/2021</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Gray</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Merger agreement signed</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
@@ -4645,21 +4689,9 @@
       </c>
       <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="n"/>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="J61" s="2" t="n"/>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="2" t="n"/>
       <c r="M61" s="2" t="n">
         <v>1</v>
       </c>
@@ -4667,28 +4699,28 @@
       <c r="O61" s="2" t="n"/>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Alternative to #59, same financing. $2.76bn cash plus 34%; later stated as $15.71/share cash dividend (p. 71) plus stock; no total per-share value given. Board weighed it before signing (p. 53).</t>
+          <t>Signed at $14.51 cash per share (LMG RemainCo net debt $1.975 billion; $725 million aggregate), plus NMG SpinCo shares in the spin-off. Break fee $36 million; reverse fee $125 million; Class B voting agreement. Moelis gave a fairness opinion.</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>“included an alternative to increase the cash consideration from $2.66 billion to $2.76 billion with a reduction of the ownership interest” (p. 69)</t>
+          <t>“the definitive Merger Agreement was executed by authorized officers of the Company, Gray and Merger Sub.” (p. 71)</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>Q5; Q8</t>
+          <t>Q1; Q7</t>
         </is>
       </c>
       <c r="S61" s="2" t="n"/>
       <c r="T61" s="3" t="n">
-        <v>44315</v>
+        <v>44319</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>44315</v>
+        <v>44319</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>44315</v>
+        <v>44319</v>
       </c>
     </row>
     <row r="62">
@@ -4702,13 +4734,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Meredith; Gray Television, Inc.</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="n"/>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Not selected at signing</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
@@ -4722,20 +4758,30 @@
       <c r="J62" s="2" t="n"/>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="n"/>
-      <c r="M62" s="2" t="n"/>
-      <c r="N62" s="2" t="n"/>
+      <c r="M62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Terms or process</t>
+        </is>
+      </c>
       <c r="O62" s="2" t="n"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>$14.51/share cash (EV $2.7bn; LMG RemainCo keeps $1.975bn net debt; $725m to holders) after NMG spin-off; $36m break fee, $125m reverse fee; class B voting agreement; Moelis fairness opinion. Separation agreements also signed.</t>
+          <t>Still live when Meredith signed with Gray. Board cited certainty of value, regulatory risk, the path to closing and timing; Party D's deal could not be done on Gray's timeline. Party D was told shortly before the announcement.</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>“the definitive Merger Agreement was executed by authorized officers of the Company, Gray and Merger Sub” (p. 71)</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="n"/>
+          <t>“a Moelis representative spoke with a principal of Party D to communicate that the Company would be announcing a transaction with another party” (p. 71)</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>Q1; Q7</t>
+        </is>
+      </c>
       <c r="S62" s="2" t="n"/>
       <c r="T62" s="3" t="n">
         <v>44319</v>
@@ -4758,54 +4804,42 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing</t>
+          <t>Merger announced</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="2" t="n">
-        <v>3</v>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
       </c>
       <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="n"/>
       <c r="J63" s="2" t="n"/>
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
-      <c r="M63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>Terms or process</t>
-        </is>
-      </c>
+      <c r="M63" s="2" t="n"/>
+      <c r="N63" s="2" t="n"/>
       <c r="O63" s="2" t="n"/>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Still bidding (#59, #60) when Meredith signed with Gray; board cited certainty of value, D/E regulatory risk and timing, unfirm financing and unfinished agreements. Moelis told D before the announcement.</t>
+          <t>Signing announced before market open. The filing mentions media reports about the process, but gives no date for them.</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>“a Moelis representative spoke with a principal of Party D to communicate that the Company would be announcing a transaction with another party” (p. 71)</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>“Execution of the Merger Agreement and other transaction agreements was publicly announced on the morning of May 3, 2021 before market open.” (p. 71)</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="n"/>
       <c r="S63" s="2" t="n"/>
       <c r="T63" s="3" t="n">
         <v>44319</v>
@@ -4823,18 +4857,22 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>05/03/2021</t>
+          <t>05/13/2021</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Meredith; Gray Television, Inc.</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="n"/>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Merger announced</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
@@ -4850,29 +4888,35 @@
       <c r="J64" s="2" t="n"/>
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="n"/>
-      <c r="M64" s="2" t="n"/>
+      <c r="M64" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N64" s="2" t="n"/>
       <c r="O64" s="2" t="n"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>Announced before market open.</t>
+          <t>Party D came back after signing with an unsolicited proposal (next row). There was no go-shop; the Merger Agreement's no-shop allowed the board to consider it.</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>“Execution of the Merger Agreement and other transaction agreements was publicly announced on the morning of May 3, 2021 before market open.” (p. 71)</t>
-        </is>
-      </c>
-      <c r="R64" s="2" t="n"/>
+          <t>“Party D sent a letter addressed to our senior management and our Board making an unsolicited, non-binding proposal to acquire LMG RemainCo.” (p. 71)</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
       <c r="S64" s="2" t="n"/>
       <c r="T64" s="3" t="n">
-        <v>44319</v>
+        <v>44329</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>44319</v>
+        <v>44329</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>44319</v>
+        <v>44329</v>
       </c>
     </row>
     <row r="65">
@@ -4896,7 +4940,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
@@ -4909,9 +4953,21 @@
       </c>
       <c r="H65" s="2" t="n"/>
       <c r="I65" s="2" t="n"/>
-      <c r="J65" s="2" t="n"/>
-      <c r="K65" s="2" t="n"/>
-      <c r="L65" s="2" t="n"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M65" s="2" t="n">
         <v>1</v>
       </c>
@@ -4919,17 +4975,17 @@
       <c r="O65" s="2" t="n"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>Returned after exit #62 with unsolicited post-signing proposal (#65).</t>
+          <t>Heavy: preferred commitment unsigned and subject to diligence; equity commitment unsigned. Offered $2.76 billion cash plus 19% of the combined company, MNI now excluded. Implied cash dividend $14.99 per share (cash component only). Came with markups of the signed Gray agreements.</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>“Party D sent a letter addressed to our senior management and our Board making an unsolicited, non-binding proposal to acquire LMG RemainCo” (p. 71)</t>
+          <t>“The proposal implied a $750 million cash dividend to the Company’s shareholders (based on the $1.975 billion closing net debt target agreed to with Gray), or $14.99 per share” (p. 71)</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q3; Q9</t>
         </is>
       </c>
       <c r="S65" s="2" t="n"/>
@@ -4949,22 +5005,22 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/13/2021</t>
+          <t>05/17/2021</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Gray</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
@@ -4977,21 +5033,9 @@
       </c>
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="n"/>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="J66" s="2" t="n"/>
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" s="2" t="n"/>
       <c r="M66" s="2" t="n">
         <v>1</v>
       </c>
@@ -4999,28 +5043,24 @@
       <c r="O66" s="2" t="n"/>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>Preferred (B affiliate) and equity commitments unsigned drafts, preferred subject to diligence; signed debt letter expires in 9 months. $2.76bn cash plus 19%; implied $14.99/share cash dividend plus stock; markups of Gray agreements.</t>
+          <t>Information to the rival: under the Merger Agreement, Moelis told Gray's CEO about Party D's proposal and sent a written summary of its material terms. Gray's counsel sent follow-up questions on 05/19/2021, answered 05/22/2021.</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>“The proposal implied a $750 million cash dividend to the Company’s shareholders (based on the $1.975 billion closing net debt target agreed to with Gray), or $14.99 per share” (p. 71)</t>
-        </is>
-      </c>
-      <c r="R66" s="2" t="inlineStr">
-        <is>
-          <t>Q5; Q8</t>
-        </is>
-      </c>
+          <t>“representatives of Moelis provided a written summary of the material terms of the proposal to Mr. Howell in accordance with the Merger Agreement.” (p. 73)</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="n"/>
       <c r="S66" s="2" t="n"/>
       <c r="T66" s="3" t="n">
-        <v>44329</v>
+        <v>44333</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>44329</v>
+        <v>44333</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>44329</v>
+        <v>44333</v>
       </c>
     </row>
     <row r="67">
@@ -5034,13 +5074,13 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Meredith (to Gray)</t>
+          <t>Jones Day</t>
         </is>
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
@@ -5061,12 +5101,12 @@
       <c r="O67" s="2" t="n"/>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Notice under Merger Agreement: Gray told of Party D’s proposal and given a written summary of its material terms. Jones Day (Gray legal adviser, alongside Eversheds) first seen this day.</t>
+          <t>Gray's legal adviser, alongside Eversheds; first shown acting on the 05/17/2021 call with Cooley about Party D's proposal.</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>“representatives of Moelis provided a written summary of the material terms of the proposal to Mr. Howell in accordance with the Merger Agreement” (p. 73)</t>
+          <t>“representatives of Eversheds and Jones Day, legal advisors to Gray” (p. 73)</t>
         </is>
       </c>
       <c r="R67" s="2" t="n"/>
@@ -5092,7 +5132,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc.</t>
+          <t>Gray</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -5113,10 +5153,10 @@
           <t>post</t>
         </is>
       </c>
-      <c r="H68" s="4" t="n">
+      <c r="H68" s="2" t="n">
         <v>15.25</v>
       </c>
-      <c r="I68" s="4" t="n">
+      <c r="I68" s="2" t="n">
         <v>15.25</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -5141,15 +5181,19 @@
       <c r="O68" s="2" t="n"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>Signed buyer with committed financing; no diligence condition. $15.25/share (EV $2.737bn) for break fee $36m→$73m and “force the vote”; expires 06/01. Ref: $14.51 signed price.</t>
+          <t>Light: an amendment to the signed agreement, requiring only documentation; the offer expired 06/01/2021. Offered $15.25 cash per share (from $14.51; enterprise value $2.737 billion) in return for raising the break fee to $73 million and adding a force-the-vote provision.</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>“proposing to increase the cash merger payment to the Company’s shareholders to $15.25 per share (an increase from $14.51 per share” (p. 74)</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="n"/>
+          <t>“Gray sent a letter addressed to our Board proposing to increase the cash merger payment to the Company’s shareholders to $15.25 per share” (p. 74)</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
       <c r="S68" s="2" t="n"/>
       <c r="T68" s="3" t="n">
         <v>44341</v>
@@ -5167,7 +5211,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>evening 05/26/2021</t>
+          <t>05/26/2021</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5217,17 +5261,17 @@
       <c r="O69" s="2" t="n"/>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>No updated preferred commitment; signed debt letter (delivered 05/27) expires in 9 months. $16.51/share cash dividend plus 10%; Party B to contribute four stations for warrants; D, not B affiliate, provides preferred.</t>
+          <t>Heavy: no updated commitment for the preferred financing (the debt commitment was signed and delivered 05/27/2021). Implied cash dividend $16.51 per share, cash component only, plus 10% of the combined company. Party B would contribute four stations for warrants.</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>“implied an $825 million aggregate cash dividend to the Company’s shareholders (based on the $1.975 billion closing net debt target agreed to with Gray), or $16.51 per share” (p. 74)</t>
+          <t>“implied an $825 million aggregate cash dividend to the Company’s shareholders (based on the $1.975 billion closing net debt target agreed to with Gray), or $16.51 per share.” (p. 74)</t>
         </is>
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>Q5; Q8; Q9</t>
+          <t>Q3; Q9; Q8</t>
         </is>
       </c>
       <c r="S69" s="2" t="n"/>
@@ -5252,10 +5296,14 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Meredith (to Gray)</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="n"/>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -5274,17 +5322,19 @@
       <c r="J70" s="2" t="n"/>
       <c r="K70" s="2" t="n"/>
       <c r="L70" s="2" t="n"/>
-      <c r="M70" s="2" t="n"/>
+      <c r="M70" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N70" s="2" t="n"/>
       <c r="O70" s="2" t="n"/>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>Standing-offer status: Moelis tells Gray the board is inclined to view D’s revised proposal (#68) as one that could lead to a Superior Company Proposal and shares its terms; Gray says it can improve.</t>
+          <t>Information to the rival: Moelis told Gray about Party D's revised proposal, sent a written summary, and said the board was inclined to find it could lead to a Superior Company Proposal. Gray's CEO said Gray could improve.</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>“our Board was inclined to view Party D’s revised proposal as one that “could reasonably be expected to lead to a Superior Company Proposal”” (p. 74)</t>
+          <t>“Later that day, a Moelis representative spoke with Mr. Howell to inform him of Party D’s revised proposal” (p. 74)</t>
         </is>
       </c>
       <c r="R70" s="2" t="n"/>
@@ -5310,7 +5360,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Meredith (to Gray)</t>
+          <t>Meredith</t>
         </is>
       </c>
       <c r="D71" s="2" t="n"/>
@@ -5337,7 +5387,7 @@
       <c r="O71" s="2" t="n"/>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>Price requirement: board seeks an amendment priced above D, no “force the vote”; Moelis offers to accept $73m break fee and 5-day match for EV $2.825bn ($16.99/share).</t>
+          <t>Target set a price requirement: after its board authorized talks for a cash price above Party D's, Meredith told Gray it would accept the $73 million break fee and a 5-business-day match right at $16.99 per share ($2.825 billion), without force-the-vote.</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -5345,7 +5395,11 @@
           <t>“the Company would accept the $73 million break fee if Gray increased enterprise value to $2.825 billion (or $16.99 per share)” (p. 75)</t>
         </is>
       </c>
-      <c r="R71" s="2" t="n"/>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
       <c r="S71" s="2" t="n"/>
       <c r="T71" s="3" t="n">
         <v>44344</v>
@@ -5368,7 +5422,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc.</t>
+          <t>Gray</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -5389,10 +5443,10 @@
           <t>post</t>
         </is>
       </c>
-      <c r="H72" s="4" t="n">
+      <c r="H72" s="2" t="n">
         <v>16.99</v>
       </c>
-      <c r="I72" s="4" t="n">
+      <c r="I72" s="2" t="n">
         <v>16.99</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -5417,7 +5471,7 @@
       <c r="O72" s="2" t="n"/>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>As #67 on financing and diligence. $16.99/share (EV $2.825bn) but keeps “force the vote”, adds option to buy three stations at a discount on a superior-proposal switch, and $73m fee if NMG SpinCo financing fails.</t>
+          <t>Light: an amendment needing only documentation, but the price was tied to deal-protection terms. Offered $16.99 per share ($2.825 billion) with force-the-vote, an option to buy three stations at a discount, and a $73 million fee if NMG SpinCo financing failed.</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -5425,7 +5479,11 @@
           <t>“Gray offered to increase the enterprise value to $2.825 billion ($16.99 per share) but continued to insist on the “force the vote” provision” (p. 75)</t>
         </is>
       </c>
-      <c r="R72" s="2" t="n"/>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
       <c r="S72" s="2" t="n"/>
       <c r="T72" s="3" t="n">
         <v>44344</v>
@@ -5448,7 +5506,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Meredith (to Gray)</t>
+          <t>Meredith</t>
         </is>
       </c>
       <c r="D73" s="2" t="n"/>
@@ -5475,7 +5533,7 @@
       <c r="O73" s="2" t="n"/>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>Counter-proposal via Cooley to Gray’s counsel: accept $73m financing-failure fee and raise break fee to $85m for EV $2.825bn without “force the vote” or station option.</t>
+          <t>Target made a counter-proposal through Cooley: it would accept the $73 million termination fee and raise the break fee to $85 million if Gray agreed to $2.825 billion without force-the-vote or the station option.</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -5483,7 +5541,11 @@
           <t>“offer to increase the break fee to $85 million if Gray would agree to $2.825 billion enterprise value without the “force the vote” provision and without the station purchase option” (p. 75)</t>
         </is>
       </c>
-      <c r="R73" s="2" t="n"/>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
       <c r="S73" s="2" t="n"/>
       <c r="T73" s="3" t="n">
         <v>44345</v>
@@ -5506,7 +5568,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc.</t>
+          <t>Gray</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -5527,10 +5589,10 @@
           <t>post</t>
         </is>
       </c>
-      <c r="H74" s="4" t="n">
+      <c r="H74" s="2" t="n">
         <v>16.55</v>
       </c>
-      <c r="I74" s="4" t="n">
+      <c r="I74" s="2" t="n">
         <v>16.55</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -5555,15 +5617,19 @@
       <c r="O74" s="2" t="n"/>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>Written: accepts $85m break fee and $73m financing-failure fee, drops “force the vote”, keeps station option; price cut to $16.55/share (EV $2.803bn).</t>
+          <t>Light: an amendment needing only documentation. Written response: accepted the $85 million break fee and $73 million termination fee and dropped force-the-vote, but kept the station option and cut the price to $16.55 per share ($2.803 billion).</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>“Gray retained the station purchase option and reduced its offer to $2.803 enterprise value ($16.55 per share in cash)” (p. 76)</t>
-        </is>
-      </c>
-      <c r="R74" s="2" t="n"/>
+          <t>“Gray retained the station purchase option and reduced its offer to $2.803 enterprise value ($16.55 per share in cash).” (p. 76)</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
       <c r="S74" s="2" t="n"/>
       <c r="T74" s="3" t="n">
         <v>44347</v>
@@ -5586,7 +5652,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc.</t>
+          <t>Gray</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -5607,10 +5673,10 @@
           <t>post</t>
         </is>
       </c>
-      <c r="H75" s="4" t="n">
+      <c r="H75" s="2" t="n">
         <v>16.99</v>
       </c>
-      <c r="I75" s="4" t="n">
+      <c r="I75" s="2" t="n">
         <v>16.99</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -5635,15 +5701,19 @@
       <c r="O75" s="2" t="n"/>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>Via Wells Fargo: $16.99/share (EV $2.825bn) only with either “force the vote” or the station purchase option.</t>
+          <t>Light: an amendment needing only documentation. Through Wells Fargo, Gray said it would go to $16.99 per share ($2.825 billion) only if Meredith accepted either force-the-vote or the station purchase option.</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>“Gray would only move forward at a $2.825 billion enterprise value ($16.99 per share in cash) if the Company agreed to either the “force the vote” provision” (p. 76)</t>
-        </is>
-      </c>
-      <c r="R75" s="2" t="n"/>
+          <t>“would only move forward at a $2.825 billion enterprise value ($16.99 per share in cash) if the Company agreed to either the “force the vote” provision” (p. 76)</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
       <c r="S75" s="2" t="n"/>
       <c r="T75" s="3" t="n">
         <v>44347</v>
@@ -5666,7 +5736,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc.</t>
+          <t>Gray</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -5687,10 +5757,10 @@
           <t>post</t>
         </is>
       </c>
-      <c r="H76" s="4" t="n">
+      <c r="H76" s="2" t="n">
         <v>16.99</v>
       </c>
-      <c r="I76" s="4" t="n">
+      <c r="I76" s="2" t="n">
         <v>16.99</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5715,15 +5785,19 @@
       <c r="O76" s="2" t="n"/>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>Howell to Moelis: $16.99/share without “force the vote” or station option if the break fee rises to $125m.</t>
+          <t>Light: an amendment needing only documentation. Gray's CEO proposed $16.99 per share ($2.825 billion) without force-the-vote or the station option if the break fee rose to $125 million.</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>“Mr. Howell asked if the Company would have flexibility to consider increasing the break fee to $125 million” (p. 76)</t>
-        </is>
-      </c>
-      <c r="R76" s="2" t="n"/>
+          <t>“Mr. Howell asked if the Company would have flexibility to consider increasing the break fee to $125 million if Gray agreed to a $2.825 billion enterprise value” (p. 76)</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
       <c r="S76" s="2" t="n"/>
       <c r="T76" s="3" t="n">
         <v>44347</v>
@@ -5741,12 +5815,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>evening 05/31/2021</t>
+          <t>05/31/2021 (evening)</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc.</t>
+          <t>Gray</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -5756,7 +5830,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
@@ -5767,27 +5841,11 @@
           <t>post</t>
         </is>
       </c>
-      <c r="H77" s="4" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="I77" s="4" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+      <c r="H77" s="2" t="n"/>
+      <c r="I77" s="2" t="n"/>
+      <c r="J77" s="2" t="n"/>
+      <c r="K77" s="2" t="n"/>
+      <c r="L77" s="2" t="n"/>
       <c r="M77" s="2" t="n">
         <v>1</v>
       </c>
@@ -5795,15 +5853,19 @@
       <c r="O77" s="2" t="n"/>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>Harty and Howell agree to recommend: $16.99/share (EV $2.825bn), $113m break fee (4%), $73m fee if NMG SpinCo financing fails; no “force the vote” or station option.</t>
+          <t>Agreement in principle: after Meredith countered at a $113 million (4%) break fee, both CEOs agreed to recommend an amendment at $16.99 per share with a $113 million break fee and a $73 million fee if NMG SpinCo financing failed.</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>“an amendment that provided for a $2.825 billion enterprise value ($16.99 per share) in exchange for a $113 million break fee payable by the Company” (p. 76)</t>
-        </is>
-      </c>
-      <c r="R77" s="2" t="n"/>
+          <t>“Messrs. Harty and Howell agreed that they were both prepared to recommend to their respective Boards an amendment that provided for a $2.825 billion enterprise value ($16.99 per share)” (p. 76)</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
       <c r="S77" s="2" t="n"/>
       <c r="T77" s="3" t="n">
         <v>44347</v>
@@ -5826,13 +5888,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Meredith; Gray Television, Inc.</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="n"/>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Merger agreement signed</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
@@ -5848,20 +5914,26 @@
       <c r="J78" s="2" t="n"/>
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="n"/>
-      <c r="M78" s="2" t="n"/>
+      <c r="M78" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N78" s="2" t="n"/>
       <c r="O78" s="2" t="n"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>Amendment executed after market close: price raised to $16.99/share cash on terms of #76. Meredith board approved 06/01, Gray board 06/02; Gray delivered updated executed financing commitments.</t>
+          <t>Amendment to the Merger Agreement executed at $16.99 cash per share (from $14.51), with a $113 million break fee, a $73 million financing-failure fee, and no force-the-vote or station option. Meredith's board approved it 06/01/2021; Gray delivered updated financing commitments.</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>“after market close, the parties executed the amendment to the Merger Agreement and the amendment to the Separation and Distribution Agreement” (p. 77)</t>
-        </is>
-      </c>
-      <c r="R78" s="2" t="n"/>
+          <t>“the parties executed the amendment to the Merger Agreement and the amendment to the Separation and Distribution Agreement, and Gray delivered updated executed financing commitments.” (p. 77)</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
       <c r="S78" s="2" t="n"/>
       <c r="T78" s="3" t="n">
         <v>44349</v>
@@ -5921,17 +5993,17 @@
       <c r="O79" s="2" t="n"/>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>Still bidding (#68) when the amendment with Gray was executed; board preferred Gray on certainty of value, regulatory path and timing (06/01 meeting). Moelis then told D.</t>
+          <t>Still live with its 05/26/2021 proposal when the Gray amendment was signed. Board cited certainty of value, regulatory risk, the path to closing and timing. Party D was told of the coming announcement.</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>“a Moelis representative spoke with a principal of Party D to communicate that the Company would be announcing the execution of the amendment with Gray” (p. 77)</t>
+          <t>“a Moelis representative spoke with a principal of Party D to communicate that the Company would be announcing the execution of the amendment with Gray.” (p. 77)</t>
         </is>
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="S79" s="2" t="n"/>
@@ -5956,13 +6028,13 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Meredith; Gray Television, Inc.</t>
+          <t>Meredith</t>
         </is>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Merger announced</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
@@ -5983,7 +6055,7 @@
       <c r="O80" s="2" t="n"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>Amendment publicly announced before market open.</t>
+          <t>Merger Agreement amendment ($16.99 per share) announced before market open. The 10/06/2021 Consent Agreement tied to the Dotdash sale of NMG SpinCo left the $16.99 unchanged.</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -6022,12 +6094,12 @@
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6094,12 +6166,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Moelis outreach to 20 parties for four select stations; 17 NDAs; preliminary IOIs requested</t>
+          <t>Moelis outreach to 20 parties to sell four select stations; NDA signers invited to submit preliminary indications (#5).</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>17 NDA signers: Gray (Strategic) plus 16 others, types unsplit, incl. Party A (Strategic), Party B (Financial), Party C (Strategic), Party D (Financial)</t>
+          <t>17 NDA signers (types not split; Unknown), incl. Gray (Strategic) and, apparently, Party A (Strategic), Party B (Financial), Party C (Strategic) and Party D (Financial).</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -6119,12 +6191,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>5: Party A, Party B (four stations and LMG), Party C (one station), Party D (two stations), Gray (LMG only); A also gave an LMG range</t>
+          <t>5 bidders: station bids from Parties A, B, C, D (Other-scope); LMG indications from Gray, Party A and Party B.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>five advanced (four station bidders to second round; Gray on LMG), twelve out (no submission)</t>
+          <t>Five advanced (Parties A–D to round 2 on 12/21/2020; Gray invited 01/12/2021); 12–16 NDA signers out without bidding.</t>
         </is>
       </c>
     </row>
@@ -6140,12 +6212,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Board advanced all first-round bidders; full data room; LMG information to Gray, A, B; 01/12 request for final station offers and LMG proposals</t>
+          <t>Board admitted first-round station bidders to a second round with full data room (#17); final station offers and LMG proposals requested 01/12/2021.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>5: Gray, Party A, Party C (Strategic); Party B, Party D (Financial). Party D’s 03/11 unsolicited LMG proposal (after its exit and re-entry) is also recorded here</t>
+          <t>5: Gray (Strategic, invited 01/12/2021), Party A (Strategic), Party B (Financial), Party C (Strategic), Party D (Financial).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -6160,17 +6232,17 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Announced as final</t>
+          <t>Not final</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>5 bidders: Gray (three stations; LMG), Party A (four stations), Party B (four stations; LMG), Party C (one station), Party D (one or two stations); later Party D (LMG, 03/11)</t>
+          <t>5 bidders: final station offers from Gray, Parties A, B, C, D; revised LMG proposals from Gray and Party B.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>station sale paused 01/28; A, C, D out; Gray and B continued on LMG; D re-entered 03/11</t>
+          <t>Station sale paused 01/28/2021; Gray and Party B carried forward for LMG; Parties A, C, D out (inferred).</t>
         </is>
       </c>
     </row>
@@ -6186,17 +6258,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Process letters to Gray and Party B for final LMG offers with draft agreements; Party D admitted 03/30 with drafts</t>
+          <t>Process letters to Gray and Party B inviting final LMG offers, with draft Merger and Separation agreements (#36).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3: Gray (Strategic), Party B (Financial), Party D (Financial; admitted 03/30)</t>
+          <t>2 admitted: Gray (Strategic), Party B (Financial); then Party D (Financial), re-entered unsolicited 03/11/2021, given a limited data room 03/16 and draft agreements 03/30/2021, but no bid due date.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>04/14/2021 → 04/20/2021</t>
+          <t>04/14/2021 → 04/20/2021 (Gray and Party B only)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6211,12 +6283,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3: Gray (04/14, 04/19, after 04/23), Party B (04/14, 04/20), Party D (04/15, 04/23, 04/26, 04/29 two alternatives)</t>
+          <t>3 bidders: Gray (04/14, 04/19, 04/23), Party B (04/14, 04/20), Party D (04/15, 04/23, 04/26, 04/29 with alternative).</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Gray selected 04/23 and signed 05/03; B out 04/23; D not selected at signing</t>
+          <t>Gray selected 04/23/2021 and signed 05/03/2021; Party B dropped 04/23; Party D not selected at signing. Post-signing, Party D re-entered and lost again at the 06/02/2021 amendment; no participant open at the filing cutoff.</t>
         </is>
       </c>
     </row>
@@ -6235,12 +6307,12 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -6289,27 +6361,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Process and round map: one process, three rounds plus post-signing. Correct?</t>
+          <t>Process and round map: one process with rounds 1 (11/16/2020 station outreach), 2 (12/21/2020 second round; final request 01/12/2021) and 3 (03/17/2021 final LMG letters), Party D's 03/11/2021 proposal in round 0, and the May–June 2021 contest post-signing. Is this right, and is round 2 Not final?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yes. R1 #6 station IOIs; R2 #19 station finals and LMG indications; R3 #39 final LMG offers; post-signing unsolicited D bids and Gray amendment. D’s 03/11 bid stays in R2. No late-reconfirmation sequence arises.</t>
+          <t>Keep this map. Alternatives: round 2 opens at the 01/12/2021 final request (#17–#18 move to round 1); 04/16/2021 opens round 4 (#46–#61 move; see Q7). Round 2 finality: keep Not final (Announced as final holds only for station offers).</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>No-contact gaps: Fall 2019 (uncertain) → 11/16/2020; within process, May 2020 (day uncertain) → 11/16/2020; post-signing 06/02/2021 → 10/06/2021 (Gray consent, p. 77) and → 11/08/2021 filing. C7 at 01/28 pause: (a) fails (Gray, B carried forward), (b) fails (contacts 02/12, 02/26, 03/05, p. 63), (c) fresh LMG focus. Fall 2019 talks have no month: background.</t>
+          <t>Station offers were requested as final (p. 60–61), but LMG proposals came back as 'revised preliminary indications' (p. 61). Gaps of about two months or more with no acquirer contact: May 2020 to 11/16/2020, before any contact (pp. 58–60); 06/03/2021 to 11/08/2021 filing (p. 77). E5: (a) fails, since Gray and Party B were carried from the 01/28/2021 pause (p. 62–63); (b) fails, with no gap of three months or more after 11/16/2020; (c) the 01/28/2021 LMG decision is a fresh start, but (a) and (b) fail. Result: one process. Fall 2019 talks (p. 58) are too vague for rows.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#6, #19, #21, #31, #36, #37, #39, #40, #54</t>
+          <t>#4, #5, #17, #18, #19, #29, #36, #46, #47, #48, #49, #50, #51, #52, #53, #54, #55, #56, #57, #58, #59, #60, #61</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Alternatives: 01/12 final request opens its own round (#21–#30 move; later rounds renumber); D’s 03/11 bid in R3 (#36–#38); or R3 opening at the 01/28 decision.</t>
+          <t>Round membership of bids and exits; the Rounds sheet; round 2's finality for the formality of later reinterpretations.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -6322,27 +6394,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Are Parties A–D among the 17 confidentiality-agreement signers, and can the 17 be split strategic/financial?</t>
+          <t>Are Parties A–D among the 17 NDA signers, which would make the residual non-submitter count exactly 12?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Yes for A–D; keep Gray (#8) plus a residual of 16 (Type Unknown) and 12 non-submitters. No split is available. Screen: Met, 17 parties.</t>
+          <t>Yes in substance, but keep Count blank ('12–16') unless the reviewer accepts the inference; then set #16 Count = 12.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>P. 60: NDA counterparties were invited to review information and bid; “of the 20 parties contacted, four submitted”. Total counts parties. Party E, a publicly-traded broadcaster, is within the 20 contacted; whether it signed is not reported.</t>
+          <t>Only NDA counterparties were invited to review information and submit indications by 12/17/2020 (p. 60), and the four bidders came from the 20 parties contacted. The filing names only Gray as a signer (p. 60).</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#7, #8, #9, #18</t>
+          <t>#7, #16</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>If any of A–D lacked an NDA, the residual (16) and non-submitter count (12) shift; screen stays Met.</t>
+          <t>Count on #16 (12 vs blank); the number of live units at the round 2 opening (5 either way).</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -6355,27 +6427,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Deadline outcomes: round 1 (12/17/2020), round 2 (01/25/2021), round 3 (04/14/2021 → 04/20/2021).</t>
+          <t>Should the LMG RemainCo proposals count as whole-company Bids, and how should prices stated as enterprise value or cash plus stock be handled?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>R1 Enforced; R2 Late bids accepted; R3 Extended; Enforced.</t>
+          <t>Treat LMG RemainCo proposals as Bids and station proposals as Other-scope bids. Leave per-share cells blank unless a per-share total is stated.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>R1: arrivals undated; all five submitters advanced #19 (p. 60). R2: submissions came “January 25 and 26” though due “no later than January 25” (pp. 60–61); the late bidder is unnamed, and all were weighed 01/28. R3: 04/16 revision to 04/20 (p. 66); Gray chosen 04/23 on bids in hand; D was not shown to hold the 04/20 date, so its 04/23 bid is not late. Markup dates (04/01, 04/08) are not bid due dates.</t>
+          <t>Gray buys all the stock of Meredith after it distributes NMG SpinCo to its own shareholders, who get $16.99 per share in cash plus the SpinCo shares (pp. 71, 77). This is analogous to a rollover. LMG bids were quoted as enterprise values until May 2021 (pp. 60–69). Party D's bids mix cash with stock of a new combined company; per-share figures cover only its cash dividend (pp. 71, 74).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#10, #21, #22, #39, #43, #47, #52</t>
+          <t>#8, #9, #10, #11, #12, #13, #14, #21, #22, #23, #24, #25, #26, #27, #28, #34, #42, #43, #45, #49, #50, #52, #55, #56, #58, #59, #64, #68</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>R2 could be Enforced or Unclear if 01/26 arrivals are not treated as late; R1 could be Unclear.</t>
+          <t>If LMG proposals were Other-scope, the ledger would have no whole-company bids before 05/25/2021 and the Deal facts screen would read 'No'; prices would be unaffected.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -6388,27 +6460,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Are proposals for LMG RemainCo (Meredith after spinning off NMG SpinCo) whole-company Bids, and station proposals Other-scope?</t>
+          <t>Outcome of the round 1 due date (12/17/2020).</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Yes. The merger target is the Meredith entity; LMG proposals buy all its stock post-spin, as the signed deal does. Four-station proposals are Other-scope. Party D’s 03/11 LMG-spin RMT is also scored a Bid.</t>
+          <t>Enforced.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Gray and B proposed to buy “all of the stock of LMG RemainCo” (pp. 61, 66); holders keep NMG SpinCo shares (p. 3). Station bids covered one to four of 17 stations (pp. 43, 58, 60).</t>
+          <t>On 12/21/2020 the board reviewed the four station bids and three LMG indications and invited only the submitters to round 2 (p. 60). No extension or late bid is reported. Arrival days are not given.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#11, #12, #13, #14, #15, #16, #17, #23, #24, #25, #26, #27, #28, #29, #30, #37</t>
+          <t>#15, #16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>If LMG counts as a segment, every LMG Bid becomes Other-scope and Deal facts would say no whole-company bids.</t>
+          <t>Deadline outcome in Rounds (Enforced vs Unclear); the inferred Did not submit exit on #16.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -6421,27 +6493,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Pre-signing LMG bids are enterprise values, and Party D’s bids are cash plus equity. Leave price cells blank?</t>
+          <t>Outcome of the round 2 due date (01/25/2021), when bids arrived on 01/25 and 01/26/2021.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Yes. No per-share conversion; EV and cash/equity terms stay in Notes. Per-share cells are filled only for Gray’s post-signing bids. The $14.51 signing price appears only in the signing row.</t>
+          <t>Late bids accepted.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Per-share figures arise only from the $1.975bn net-debt allocation (p. 70). D’s $14.99, $15.71 and $16.51 figures are the cash dividend only, beside 19%/34%/10% stakes (pp. 71, 74). C15 bars converting.</t>
+          <t>'On January 25 and 26, 2021, the Company received five ... final indications' against a 'no later than January 25, 2021' deadline (pp. 60–61). The board considered all of them on 01/28/2021 (p. 62). Which bid arrived on the 26th is not stated.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#15, #16, #17, #24, #27, #37, #44, #45, #46, #50, #51, #53, #56, #57, #59, #60, #65, #68</t>
+          <t>#20, #21, #22, #23, #24, #25, #26, #27, #28</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Filling cash-only per-share values for D would understate its offers; converting Gray’s EVs would import a net-debt assumption.</t>
+          <t>Rounds outcome would be Enforced if the 01/26 receipts are treated as on time; it does not affect exits.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -6454,27 +6526,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Were A, C and D out when the station sale was paused on 01/28/2021, and how should D’s later returns and exits be labelled?</t>
+          <t>Exits of Parties A, C and D at the 01/28/2021 station-process pause, and Party D's return on 03/11/2021 as a round 0 re-entry.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target by 01/28 (inferred), with D re-entering 03/11 and 05/13, and Not selected at signing on 05/03 and at the 06/02 amendment.</t>
+          <t>Keep the inferred Dropped by target exits by 01/28/2021 and Party D's Re-entered row plus round 0 bid on 03/11/2021.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Pause and LMG focus (p. 62); process letters went only to Gray and B (p. 63). D returned unsolicited (p. 63). D told at signing and at the amendment (pp. 71, 77).</t>
+          <t>The station sale was paused and never resumed (p. 62). Only Gray and Party B were later in LMG diligence and invited on 03/17/2021 (pp. 63). Party D's 03/11/2021 letter was unsolicited (p. 63), and it was brought into the document stage on 03/30/2021 (p. 64).</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#32, #33, #34, #36, #62, #64, #78</t>
+          <t>#30, #31, #32, #33, #34, #38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Without the 01/28 exits, A and C would stay live to signing (live count R3: 5 instead of 3) and D would have no exit/re-entry pair.</t>
+          <t>Alternative: A and C become Not selected at signing by 05/03/2021, and D stays live with no exit or re-entry and its 03/11 bid in round 3. That changes live counts between 01/28 and 03/17/2021.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -6487,27 +6559,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Party D’s type: Financial, or Mixed given Party E’s (a public broadcaster) equity role?</t>
+          <t>Outcomes of round 3's due dates (04/14/2021 and 04/20/2021).</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Financial. D is an investment firm bidding through its portfolio company; E contributes stations for equity to D’s combined company, a support role, not a separate bid. E never bid alone.</t>
+          <t>Extended; Enforced.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>D described as “an investment firm with a portfolio company” (p. 60); E contributes stations “in exchange for an ownership interest” (p. 66).</t>
+          <t>After judging the 04/14 bids inadequate, the board asked Gray and Party B to resubmit by 04/20/2021 (pp. 66–67), which counts as a later due date in the same round (E9). On 04/23/2021 it selected Gray on the bids in hand (p. 68). Party D was never given a bid date.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>#37, #46</t>
+          <t>#36, #42, #43, #44, #45, #46, #47, #48, #49, #50, #51, #52, #53, #54, #55, #56, #57, #58, #59, #60, #61</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Mixed would make D’s bids joint strategic-financial; E might then need a Bidding group changed row if it was a live NDA signer.</t>
+          <t>If 04/16 instead opens round 4, 04/14 becomes Enforced and round 4's 04/20 date Enforced; #46–#61 move to round 4, whose finality would be Inferred final.</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -6520,27 +6592,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Are Party D’s LMG bids from 04/15/2021 Formal?</t>
+          <t>How did Party B leave: Dropped by target on 04/23/2021, or Not selected at signing on 05/03/2021? And does its later support of Party D make a bidding group?</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Yes, Formal with Heavy conditions. The 04/15 bid rests on D’s 04/08 Merger Agreement markup, requested by the target for D’s final proposal. Later bids continue it; 05/13 came with markups of the executed agreements.</t>
+          <t>Dropped by target (inferred) by 04/23/2021, with no Bidding group changed row.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>P. 65: markup submitted 04/08; p. 66: the 04/15 bid relied on it. But the markup was “subject to completion of diligence and transaction structure” and financing (p. 65).</t>
+          <t>The board had Party B told its proposal 'was not competitive' (p. 68), and Party B never bid again. Its affiliate's preferred term sheet (p. 69) and its station contribution for warrants (p. 74) are financing and asset support for Party D after B's exit (E4).</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>#46, #53, #57, #59, #60, #65, #68</t>
+          <t>#54, #57, #68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Informal would leave D with no formal bid before signing, weakening the competitive reading of R3.</t>
+          <t>Exit label and date for Party B; if support is read as joining Party D's unit, a group-change row would follow on 05/26/2021.</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -6553,27 +6625,27 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>How did Party B leave, and do its later roles in Party D’s bid make it a group member?</t>
+          <t>Post-signing coding: Gray's amendment offers as Formal/Light, the 06/02/2021 amendment as Merger agreement signed, and Party D Not selected at signing.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target by 04/23 (inferred), Lower offer than rivals. The later affiliate financing and station contribution to D are support, not a bidding group, so B gets no further rows.</t>
+          <t>Keep this coding: Gray's offers amend a signed definitive agreement with specific contract terms.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Board authorized telling B “its current proposal was not competitive” (p. 68); B never bid again. Its affiliate’s preferred term sheet was offered 04/29 (p. 69); B’s stations were to be exchanged for warrants 05/26 (p. 74).</t>
+          <t>Gray's offers of 05/25–05/31/2021 set price and contract terms against the executed agreement (pp. 74–76). No markups are reported, so E11 criterion 1 is not literally met. Party D's post-signing proposals came with markups of the signed Gray agreements (p. 71).</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>#55, #58, #68</t>
+          <t>#63, #64, #67, #68, #70, #71, #72, #73, #74, #75, #76, #77, #78</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Alternative: Not selected at signing on 05/03, which keeps B live in R3 until signing (two live rivals to Gray, not one).</t>
+          <t>If Gray's post offers are Informal, #67, #71 and #73–#75 change Formality. If the amendment is only an Other material event, #77–#78 change and Party D stays open at the filing cutoff.</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -6594,7 +6666,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6617,7 +6689,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Meredith Corporation (Iowa); acquired as “LMG RemainCo” — Meredith holding only its local media group (17 TV stations) after spin-off of NMG SpinCo (Meredith Holdings Corporation) to its shareholders</t>
+          <t>Meredith Corporation (Iowa). The sale covers its local media group (LMG) business, by merger of Meredith after the spin-off of its national media group (NMG) and corporate operations into NMG SpinCo (Meredith Holdings Corporation).</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6701,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc., through Gray Hawkeye Stations, Inc. (merger sub)</t>
+          <t>Gray Television, Inc., through Gray Hawkeye Stations, Inc. (Merger Sub).</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6713,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategic (television broadcast company)</t>
+          <t>Strategic (television broadcast company).</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6725,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$16.99 per share in cash (amendment 06/02/2021; EV $2.825bn), up from $14.51 per share in cash at signing (EV $2.7bn). Shareholders also keep NMG SpinCo shares from the spin-off (NMG SpinCo later agreed to merge with Dotdash/IAC for $42.18 per share, 10/06/2021)</t>
+          <t>$16.99 per share in cash (amendment of 06/02/2021; $14.51 per share in cash at signing on 05/03/2021). Enterprise value $2.825 billion. Shareholders also receive NMG SpinCo shares in the spin-off, which Gray does not pay for.</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6737,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/03/2021 (amended 06/02/2021 for price; amended 10/06/2021 by consent agreement for Dotdash merger)</t>
+          <t>05/03/2021 (amended 06/02/2021; further amended by the Consent Agreement of 10/06/2021).</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6749,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/03/2021 (amendment announced 06/03/2021)</t>
+          <t>05/03/2021 (amendment announced 06/03/2021).</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6785,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Target-led</t>
+          <t>target-led</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6809,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Fall 2019: preliminary discussions with a few private equity firms (one later identified as Party B) about possible strategic transactions; no agreement reported; did not advance, no transaction (p. 58).</t>
+          <t>Fall 2019: preliminary talks with a few private equity firms (including Party B) about possible strategic transactions; none went beyond preliminary talks (p. 58). No month is given, so there are no rows.</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6821,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Met (process 1): 17 parties — confidentiality agreements with 17 parties incl. Gray; total counts parties. Pre-signing subtotal 17; no post-signing additions reported.</t>
+          <t>Met (process 1): 17 parties</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6833,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Yes — for LMG RemainCo (all stock of Meredith after the NMG spin-off), the merger target; station-group bids recorded as Other-scope (see Question on scope)</t>
+          <t>Yes: LMG RemainCo proposals (the whole of Meredith after the NMG spin-off to its shareholders) are recorded as Bids (Q3). The select-station proposals of 12/2020–01/2021 are Other-scope.</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6845,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>US dollars. Pre-signing LMG bids are enterprise values (billions) and station bids aggregate dollar amounts, neither per share. Per-share prices exist only at signing and post-signing. Party D offered cash plus equity (% of combined company)</t>
+          <t>US dollars. LMG bids were stated as enterprise values in billions until May 2021, and station bids as total dollars; per-share prices appear only in Gray's post-signing offers. Party D offered cash plus stock of a new combined company, with per-share figures for its cash dividend only (Q3).</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6857,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Moelis &amp; Company LLC (sole financial adviser; fairness opinion)</t>
+          <t>Moelis &amp; Company LLC</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6869,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Cooley LLP (primary outside legal counsel); tax adviser Deloitte Tax LLP; unnamed regulatory advisors</t>
+          <t>Cooley LLP (Deloitte Tax LLP was the tax adviser)</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6881,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Meredith, after deciding in 2020 to sell four TV stations and keep an option to sell its whole local media group, had Moelis contact 20 parties in November 2020; 17 signed confidentiality agreements. Four bid for stations, and Gray, Party A and Party B also floated prices for all of LMG after a spin-off of the national media business. After final station bids in January 2021 the board paused the station sale and ran a final LMG round with Gray and Party B; Party D joined with a cash-plus-stock Morris Trust proposal. Gray raised its bid to $2.7bn EV and signed on 05/03/2021 at $14.51 per share in cash, ahead of higher-headline but less certain proposals from Party D. After signing, Party D’s unsolicited proposals prompted Gray to raise its price, and after back-and-forth over deal protections the parties amended the agreement on 06/02/2021 to $16.99 per share. The proxy says the process drew media reports without producing a more certain offer (p. 53).</t>
+          <t>Meredith hired Moelis in 2020 to sell four select TV stations. The November 2020 outreach to 20 parties (17 NDAs) also drew LMG indications from Gray, Party A and Party B. After final station bids in January 2021, the board paused the station sale and ran a final LMG round with Gray and Party B. Party D joined unsolicited with a Morris Trust proposal. Gray was preferred on value and certainty and signed at $14.51 per share on 05/03/2021. Party D's post-signing proposals pushed Gray to an amendment at $16.99 per share on 06/02/2021; the filing also says media reports about the process drew no superior proposal (p. 53).</t>
         </is>
       </c>
     </row>

--- a/extraction/meredith.xlsx
+++ b/extraction/meredith.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="MM/DD/YYYY"/>
   </numFmts>
   <fonts count="2">
@@ -60,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -69,6 +69,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -436,12 +439,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V80"/>
+  <dimension ref="A1:V86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -452,12 +455,12 @@
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
@@ -586,7 +589,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Moelis &amp; Company LLC (Moelis)</t>
+          <t>Moelis &amp; Company LLC</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -611,12 +614,12 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Target's financial adviser. Moelis attended the May 2020 board meeting on selling select stations or all of LMG, was formally engaged afterwards, and in February 2021 amended its engagement letter to add an LMG sale fee.</t>
+          <t>Target's financial adviser. Moelis joined the May 2020 board meeting on LMG options and was later formally engaged for the select-station sale. Its engagement letter was amended in February 2021 to set a fee for an LMG sale (p.62).</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>“Members of our senior management and representatives of Moelis also participated in the meeting. The select station group” (p. 58)</t>
+          <t>Members of our senior management and representatives of Moelis also participated in the meeting. (p. 58)</t>
         </is>
       </c>
       <c r="R2" s="2" t="n"/>
@@ -642,7 +645,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
+          <t>Meredith (target)</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
@@ -667,12 +670,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Qualified decision: engaged Moelis to prepare to market four select stations after Labor Day 2020, while preparing an LMG sale and NMG spin-off as an option. On 08/24/2020 the board postponed marketing until after the November 2020 shareholder meeting.</t>
+          <t>Board engages Moelis to prepare to market four select stations (St. Louis, Mobile-Pensacola, Flint-Saginaw-Bay City, Springfield-Holyoke) after Labor Day 2020. It keeps open an option to sell all of LMG with a spin-off of NMG. The July 2020 meeting bounds the timing.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>“Subsequent to the May 2020 Board meeting, the Company formally engaged Moelis to begin preparations for marketing the select station group after Labor Day 2020 depending on market conditions.” (p. 59)</t>
+          <t>Subsequent to the May 2020 Board meeting, the Company formally engaged Moelis to begin preparations for marketing the select station group after Labor Day 2020 depending on market conditions. (p. 59)</t>
         </is>
       </c>
       <c r="R3" s="2" t="n"/>
@@ -698,7 +701,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Cooley LLP (Cooley)</t>
+          <t>Cooley LLP</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
@@ -723,12 +726,12 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Target's primary outside legal counsel. Cooley was first shown acting after the May 2020 meeting, preparing the LMG divestiture and NMG spin-off, and attended the July 2020 board meeting. Deloitte Tax LLP later acted as the target's tax adviser.</t>
+          <t>Target's primary outside legal counsel. Preparing a possible LMG divestiture and NMG spin-off, and had advised the Company on prior deals. Cooley attended the July 2020 board meeting.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>“the Company’s primary outside legal counsel Cooley LLP” (p. 59)</t>
+          <t>Moelis and the Company’s primary outside legal counsel Cooley LLP (“Cooley”) also continued analysis and preparations for a potential divestiture of LMG and a spin-off of NMG. (p. 59)</t>
         </is>
       </c>
       <c r="R4" s="2" t="n"/>
@@ -749,18 +752,18 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>after the 11/10/2020 board meeting</t>
+          <t>08/24/2020</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
+          <t>Meredith (target)</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -779,28 +782,24 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Board authorized management and advisers to market the select station sales (St. Louis, Mobile-Pensacola, Flint-Saginaw-Bay City, Springfield-Holyoke), begin buyer outreach and solicit initial indications of interest. The scope was assets only; an LMG sale was not yet decided.</t>
+          <t>Target defers the start of marketing: the board decides to seek shareholder approval of a charter amendment, which enables a tax-efficient separation with dual-class voting, before any strategic transaction.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>“our Board authorized our senior management and advisors to move forward with the marketing of the select station sales, to commence buyer outreach and solicit initial indications of interest.” (p. 60)</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>determined to wait to commence marketing the select station sale until after the November annual shareholders meeting. (p. 59)</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
       <c r="T5" s="3" t="n">
-        <v>44148</v>
+        <v>44067</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>44145</v>
+        <v>44067</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>44151</v>
+        <v>44067</v>
       </c>
     </row>
     <row r="6">
@@ -809,25 +808,25 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>11/16/2020</t>
+          <t>after the 11/10/2020 board meeting</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
+          <t>Meredith (target)</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
@@ -839,25 +838,21 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Moelis outreach for the four select stations. NDA counterparties could review preliminary financial and diligence information, with preliminary indications of interest due 12/17/2020. Interest in all of LMG came up within this outreach.</t>
+          <t>Board authorizes marketing of the select-station sale, buyer outreach and a request for initial indications of interest. Shareholders approved the charter amendment on 11/11/2020. Outreach began on 11/16/2020.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>“Commencing November 16, 2020 and over the next several weeks, representatives of Moelis contacted 20 parties (including Gray)” (p. 60)</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>our Board authorized our senior management and advisors to move forward with the marketing of the select station sales, to commence buyer outreach and solicit initial indications of interest. (p. 60)</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="3" t="n">
-        <v>44151</v>
+        <v>44148</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>44151</v>
+        <v>44145</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>44151</v>
@@ -869,22 +864,18 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>commencing 11/16/2020 and over the next several weeks</t>
+          <t>commencing 11/16/2020</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20 parties contacted by Moelis (incl. Gray)</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -898,22 +889,24 @@
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated contacts: all publicly traded broadcasters (incl. Gray), plus other broadcasters and broadcast investors seen as most likely to be interested. Several showed interest in some or all four stations. Types are not split.</t>
+          <t>Moelis outreach wave for the four-station group. NDA signers could review preliminary financial and diligence information on the four stations. Preliminary IOIs due 12/17/2020 (date communicated with the invitation; day not stated).</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>“The contacted parties included all of the publicly-traded broadcasters (including Gray) as well as other broadcasters and broadcast investors considered most likely to have potential interest.” (p. 60)</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="n"/>
+          <t>Commencing November 16, 2020 and over the next several weeks, representatives of Moelis contacted 20 parties (including Gray) and several expressed interest in certain of the select stations (p. 60)</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S7" s="2" t="n"/>
       <c r="T7" s="3" t="n">
         <v>44151</v>
@@ -922,7 +915,7 @@
         <v>44151</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>44186</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="8">
@@ -931,12 +924,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>between 11/16/2020 and 12/21/2020</t>
+          <t>commencing 11/16/2020, over the next several weeks</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17 NDA signers (incl. Gray)</t>
+          <t>20 parties contacted by Moelis (including Gray)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -946,7 +939,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -961,25 +954,21 @@
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Confidentiality agreements with customary standstill and fall-away provisions. The filing names only Gray among the 17. Parties A–D are presumably members, since only counterparties were invited to bid, but this is not stated (Q). About 3 contacted parties did not sign.</t>
+          <t>Target-initiated. The group includes all publicly traded broadcasters plus other broadcasters and broadcast investors seen as most likely buyers. The type split is not given. Twenty were contacted and 17 signed NDAs, so 3 did not sign. The 12/21/2020 report bounds the contacts.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>“The Company entered into confidentiality agreements with 17 parties (including Gray) who had expressed interest in a transaction with the Company.” (p. 60)</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>The contacted parties included all of the publicly-traded broadcasters (including Gray) as well as other broadcasters and broadcast investors considered most likely to have potential interest. (p. 60)</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="3" t="n">
         <v>44168</v>
@@ -997,12 +986,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>by 12/21/2020 (due 12/17/2020)</t>
+          <t>between 11/16/2020 and 12/21/2020</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Gray Television, Inc.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1012,7 +1001,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -1023,21 +1012,9 @@
       </c>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n">
         <v>1</v>
       </c>
@@ -1045,22 +1022,18 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Conditions: the filing states none for the station bids. First-round bid for all four select stations; its own price is not disclosed. The four station bids together showed a group value of $511–631 million, not per share.</t>
+          <t>Gray is named among the 17 signers. NDAs included standstill and fall-away provisions. Signed during the outreach and before first-round responses (reported 12/21/2020).</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>“Two parties bid for all four stations: a strategic party referred to as Party A, and a private equity sponsor” (p. 60)</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>The Company entered into confidentiality agreements with 17 parties (including Gray) who had expressed interest in a transaction with the Company. (p. 60)</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="3" t="n">
-        <v>44182</v>
+        <v>44168</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>44151</v>
@@ -1075,22 +1048,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>by 12/21/2020 (due 12/17/2020)</t>
+          <t>between 11/16/2020 and 12/21/2020</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -1101,44 +1074,36 @@
       </c>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Conditions: the filing states none for the station bids. Private equity sponsor that owned a station group and had talked with Meredith in Fall 2019. First-round bid for all four stations; its price is not disclosed (group range $511–631 million).</t>
+          <t>Inferred: Party A (strategic party) submitted a first-round bid. Only NDA counterparties were invited to review information and bid, so it is taken to be one of the 17 signers. No individual date is given.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>“a private equity sponsor which had acquired a station group and spoken with the Company in Fall 2019, referred to as Party B” (p. 60)</t>
+          <t>The Company entered into confidentiality agreements with 17 parties (including Gray) who had expressed interest in a transaction with the Company. (p. 60)</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="3" t="n">
-        <v>44182</v>
+        <v>44168</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>44151</v>
@@ -1153,22 +1118,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>by 12/21/2020 (due 12/17/2020)</t>
+          <t>between 11/16/2020 and 12/21/2020</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -1179,44 +1144,36 @@
       </c>
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Conditions: the filing states none for the station bids. First-round bid for the Flint-Saginaw-Bay City station only; its price is not disclosed.</t>
+          <t>Inferred: Party B (PE sponsor owning a station group) submitted a first-round bid. Only NDA counterparties were invited to review information and bid, so it is taken to be one of the 17 signers. No individual date is given.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>“Another strategic party, referred to as Party C, bid on the Flint-Saginaw-Bay City station only.” (p. 60)</t>
+          <t>The Company entered into confidentiality agreements with 17 parties (including Gray) who had expressed interest in a transaction with the Company. (p. 60)</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="3" t="n">
-        <v>44182</v>
+        <v>44168</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>44151</v>
@@ -1231,22 +1188,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>by 12/21/2020 (due 12/17/2020)</t>
+          <t>between 11/16/2020 and 12/21/2020</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -1257,44 +1214,36 @@
       </c>
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Conditions: the filing states none for the station bids. Investment firm whose portfolio company owned a small station group. First-round bid for the Mobile-Pensacola and Flint-Saginaw-Bay City stations; its price is not disclosed.</t>
+          <t>Inferred: Party C (strategic party) submitted a first-round bid. Only NDA counterparties were invited to review information and bid, so it is taken to be one of the 17 signers. No individual date is given.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>“An investment firm with a portfolio company that currently owned a small station group, referred to as Party D, bid on the Mobile- Pensacola and Flint-Saginaw-Bay City stations.” (p. 60)</t>
+          <t>The Company entered into confidentiality agreements with 17 parties (including Gray) who had expressed interest in a transaction with the Company. (p. 60)</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S12" s="2" t="n"/>
       <c r="T12" s="3" t="n">
-        <v>44182</v>
+        <v>44168</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>44151</v>
@@ -1309,22 +1258,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>by 12/21/2020 (due 12/17/2020)</t>
+          <t>between 11/16/2020 and 12/21/2020</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc. (Gray)</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -1335,44 +1284,36 @@
       </c>
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Heavy: subject to third-party debt financing and customary diligence; non-binding. Indicated interest in LMG after a simultaneous NMG spin-off, at an enterprise value of $2.5–2.7 billion all cash (not per share). Gray made no bid for the station group alone.</t>
+          <t>Inferred: Party D (investment firm whose portfolio company owns a small station group) submitted a first-round bid. Only NDA counterparties were invited to review information and bid, so it is taken to be one of the 17 signers. No individual date is given.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>“Gray indicated a value range of $2.5-$2.7 billion in an all cash transaction.” (p. 60)</t>
+          <t>The Company entered into confidentiality agreements with 17 parties (including Gray) who had expressed interest in a transaction with the Company. (p. 60)</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="3" t="n">
-        <v>44182</v>
+        <v>44168</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>44151</v>
@@ -1387,22 +1328,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>by 12/21/2020 (due 12/17/2020)</t>
+          <t>between 11/16/2020 and 12/21/2020</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>12 other NDA signers (unnamed)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1413,44 +1354,36 @@
       </c>
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Heavy: subject to third-party debt financing and customary diligence; non-binding. Indicated interest in LMG after an NMG spin-off at an enterprise value of $2.6–2.8 billion (not per share); the form of consideration is not stated. Made alongside its station bid.</t>
+          <t>Inferred remainder: 17 signers − Gray − Parties A–D = 12. This holds only if A–D are among the 17 (see Q7). The group mixes broadcasters and broadcast investors, with no split given.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>“Party A indicated a value range of $2.6-$2.8 billion.” (p. 60)</t>
+          <t>The Company entered into confidentiality agreements with 17 parties (including Gray) who had expressed interest in a transaction with the Company. (p. 60)</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S14" s="2" t="n"/>
       <c r="T14" s="3" t="n">
-        <v>44182</v>
+        <v>44168</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>44151</v>
@@ -1465,22 +1398,18 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>by 12/21/2020 (due 12/17/2020)</t>
+          <t>12/17/2020</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -1491,34 +1420,20 @@
       </c>
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Heavy: subject to third-party debt financing and customary diligence; non-binding. Indicated interest in LMG after an NMG spin-off at an enterprise value of $2.5–2.75 billion (not per share), in cash and stock in proportions to be determined.</t>
+          <t>Due date for preliminary IOIs on the select-station group. Responses were reported to the board on 12/21/2020, which then advanced the station bidders.</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>“Party B indicated a value range of $2.5-$2.75 billion in a combination of cash and stock to be determined.” (p. 60)</t>
+          <t>The counterparties were invited to review preliminary financial and due diligence information regarding the four select stations and submit preliminary indications of interest by December 17, 2020. (p. 60)</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -1531,10 +1446,10 @@
         <v>44182</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>44151</v>
+        <v>44182</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>44186</v>
+        <v>44182</v>
       </c>
     </row>
     <row r="16">
@@ -1543,18 +1458,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>12/17/2020</t>
+          <t>by 12/21/2020</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n"/>
+          <t>Gray Television, Inc.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -1565,20 +1484,34 @@
       </c>
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Due date for preliminary indications of interest on the four select stations. The board reviewed the results on 12/21/2020: 4 of the 20 contacted parties had bid on stations, and Gray, Party A and Party B had indicated interest in LMG.</t>
+          <t>Heavy: all LMG proposals were subject to customary diligence and third-party debt financing. Non-binding offer to buy LMG after a spin-off of NMG at EV $2.5–2.7B. No per-share figure. Gray made no select-station bid.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>“submit preliminary indications of interest by December 17, 2020.” (p. 60)</t>
+          <t>Gray indicated a value range of $2.5-$2.7 billion in an all cash transaction. (p. 60)</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -1591,10 +1524,10 @@
         <v>44182</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>44182</v>
+        <v>44151</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>44182</v>
+        <v>44186</v>
       </c>
     </row>
     <row r="17">
@@ -1603,22 +1536,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>by 12/17/2020</t>
+          <t>by 12/21/2020</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>NDA signers that made no first-round proposal</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -1629,35 +1562,37 @@
       </c>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Count: 12–16. The count is 17 signers minus Gray minus those of Parties A–D who were signers: 12 if all four were (likely, since only counterparties were invited), up to 16 if none were. None was invited to round 2.</t>
+          <t>Unclear: the conditions sentence refers to the LMG proposals. First-round bid for all four select stations, price not disclosed individually. The four station bids together indicated $511–631M for the four-station group.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>“Representatives of Moelis reported to our Board that, of the 20 parties contacted, four submitted first round bids.” (p. 60)</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>Q2; Q4</t>
-        </is>
-      </c>
+          <t>Two parties bid for all four stations: a strategic party referred to as Party A, and a private equity sponsor which had acquired a station group (p. 60)</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
       <c r="T17" s="3" t="n">
         <v>44182</v>
@@ -1666,7 +1601,7 @@
         <v>44151</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>44182</v>
+        <v>44186</v>
       </c>
     </row>
     <row r="18">
@@ -1675,58 +1610,76 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>after the 12/21/2020 board meeting</t>
+          <t>by 12/21/2020</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n"/>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Board invited the four first-round station bidders (Parties A–D) to a second round with full data room access and LMG management diligence calls. Gray was added by the 01/12/2021 invitation. No due date was set until 01/12/2021.</t>
+          <t>Heavy: subject to customary diligence and third-party debt financing. Non-binding LMG indication (stock purchase after NMG spin-off) at EV $2.6–2.8B. No per-share figure and no consideration form stated.</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>“Each of the parties that submitted first round proposals for the select stations was invited to participate in the second round and granted full data room access.” (p. 60)</t>
+          <t>Party A indicated a value range of $2.6-$2.8 billion. (p. 60)</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="3" t="n">
+        <v>44182</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>44151</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>44186</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>44186</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>44208</v>
       </c>
     </row>
     <row r="19">
@@ -1735,58 +1688,72 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>after the 12/21/2020 board meeting</t>
+          <t>by 12/21/2020</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Information access differs: the board had select, value-driving LMG information given only to the parties interested in LMG (Gray, Party A, Party B). Parties C and D got station information only.</t>
+          <t>Unclear: the conditions sentence refers to the LMG proposals. First-round bid for all four select stations, price not disclosed individually; part of the $511–631M range for the four bids. Private equity sponsor.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>“our Board instructed our senior management and advisors to provide select, value-driving information to parties who expressed interest in a LMG transaction” (p. 60)</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>Two parties bid for all four stations: a strategic party referred to as Party A, and a private equity sponsor which had acquired a station group (p. 60)</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="n"/>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="3" t="n">
+        <v>44182</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>44151</v>
+      </c>
+      <c r="V19" s="3" t="n">
         <v>44186</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>44186</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>44208</v>
       </c>
     </row>
     <row r="20">
@@ -1795,58 +1762,76 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>01/12/2021</t>
+          <t>by 12/21/2020</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Moelis invited Gray and Parties A–D to submit final offers for the select station group by 01/25/2021, with markups of an asset purchase agreement. Gray, A and B were also invited to submit LMG proposals by that date; these were not called final.</t>
+          <t>Heavy: subject to customary diligence and third-party debt financing. Non-binding LMG indication at EV $2.5–2.75B in a cash and stock mix to be determined. No per-share figure.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>“representatives of Moelis invited Gray, Party A, Party B, Party C and Party D to submit final offers for the select station group no later than” (p. 60)</t>
+          <t>Party B indicated a value range of $2.5-$2.75 billion in a combination of cash and stock to be determined. (p. 60)</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="3" t="n">
-        <v>44208</v>
+        <v>44182</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>44208</v>
+        <v>44151</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>44208</v>
+        <v>44186</v>
       </c>
     </row>
     <row r="21">
@@ -1855,58 +1840,72 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>01/25/2021</t>
+          <t>by 12/21/2020</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Due date for final station offers and LMG proposals. Bids arrived on 01/25 and 01/26/2021, so at least one came after the due date; the board considered all of them on 01/28/2021. Markups from Gray, A, C and D had arrived on 01/21/2021.</t>
+          <t>Unclear: no condition reported for station bids. First-round bid for the Flint-Saginaw-Bay City station only, price not disclosed individually.</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>“On January 25 and 26, 2021, the Company received five (including one from Gray) final indications of interest for the select stations” (p. 61)</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
+          <t>Another strategic party, referred to as Party C, bid on the Flint-Saginaw-Bay City station only. (p. 60)</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="3" t="n">
-        <v>44221</v>
+        <v>44182</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>44221</v>
+        <v>44151</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>44221</v>
+        <v>44186</v>
       </c>
     </row>
     <row r="22">
@@ -1915,17 +1914,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/25/2021 or 01/26/2021</t>
+          <t>by 12/21/2020</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1937,23 +1936,23 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Formal</t>
+          <t>Informal</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
@@ -1963,28 +1962,24 @@
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Light: subject only to certain due diligence items and contract terms. Offered $425 million cash for the select stations except Flint-Saginaw-Bay City, as a first step toward acquiring LMG. It answered the final solicitation and came with an asset purchase agreement markup.</t>
+          <t>Unclear: no condition reported for station bids. First-round bid for the Mobile-Pensacola and Flint-Saginaw-Bay City stations, price not disclosed individually. Investment firm with a station-owning portfolio company.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>“Gray proposed to purchase the select station group (other than the Flint-Saginaw-Bay City station) for $425 million in cash” (p. 61)</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>Q3; Q5</t>
-        </is>
-      </c>
+          <t>Party D, bid on the Mobile- Pensacola and Flint-Saginaw-Bay City stations. (p. 60)</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="n"/>
       <c r="S22" s="2" t="n"/>
       <c r="T22" s="3" t="n">
-        <v>44221</v>
+        <v>44182</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>44221</v>
+        <v>44151</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>44222</v>
+        <v>44186</v>
       </c>
     </row>
     <row r="23">
@@ -1993,76 +1988,70 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/25/2021 or 01/26/2021</t>
+          <t>by 12/17/2020</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>12 other NDA signers (unnamed)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" s="2" t="n"/>
-      <c r="O23" s="2" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Light: subject to certain diligence items and contract terms; no financing contingency in a final proposal. Bid for all LMG RemainCo stock in cash at an enterprise value of $2.6–2.7 billion (low end up from $2.5 billion), not per share. Called a revised preliminary indication; no markup.</t>
+          <t>Inferred. 17 signers − Gray (LMG indication) − Parties A–D (four station bids) = 12 with no submission. Exact only if A–D are among the 17 (Q7). No reason given.</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>“Gray proposed to purchase for cash all of the stock of LMG RemainCo based on an enterprise value of $2.6-$2.7 billion” (p. 61)</t>
+          <t>Representatives of Moelis reported to our Board that, of the 20 parties contacted, four submitted first round bids. (p. 60)</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q5</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S23" s="2" t="n"/>
       <c r="T23" s="3" t="n">
-        <v>44221</v>
-      </c>
-      <c r="U23" s="3" t="n">
-        <v>44221</v>
-      </c>
+        <v>44182</v>
+      </c>
+      <c r="U23" s="3" t="n"/>
       <c r="V23" s="3" t="n">
-        <v>44222</v>
+        <v>44182</v>
       </c>
     </row>
     <row r="24">
@@ -2071,22 +2060,18 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>01/25/2021 or 01/26/2021</t>
+          <t>after the 12/21/2020 board meeting</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -2097,50 +2082,36 @@
       </c>
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Heavy: debt commitment letters were only promised 'shortly thereafter'. Offered $560 million cash for all four stations; a final offer with a markup filed 01/21/2021. Party A made no LMG proposal, although invited to.</t>
+          <t>Target admits the four first-round station bidders (A, B, C, D) to a second round with full data room access, plus diligence calls with LMG management. Gray was invited to bid on 01/12/2021. Final station offers due 01/25/2021.</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed to purchase all four stations of the select station group for $560 million in cash” (p. 61)</t>
+          <t>Each of the parties that submitted first round proposals for the select stations was invited to participate in the second round and granted full data room access. (p. 60)</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q5</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S24" s="2" t="n"/>
       <c r="T24" s="3" t="n">
-        <v>44221</v>
+        <v>44186</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>44221</v>
+        <v>44186</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>44222</v>
+        <v>44208</v>
       </c>
     </row>
     <row r="25">
@@ -2149,22 +2120,18 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>01/25/2021 or 01/26/2021</t>
+          <t>after the 12/21/2020 board meeting</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -2175,50 +2142,32 @@
       </c>
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
       <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Heavy: subject to completion of due diligence, and funded partly by new equity and new debt. Offered $510 million cash for the station group. Informal: no asset purchase agreement markup was filed, so the bid was not on the requested basis.</t>
+          <t>Information difference: selected value-driving LMG information goes only to the parties interested in LMG (Gray, Party A, Party B), not to C or D. The station process continues in parallel.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>“Party B proposed to purchase the select station group for $510 million in cash.” (p. 61)</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>Q3; Q5</t>
-        </is>
-      </c>
+          <t>our Board instructed our senior management and advisors to provide select, value-driving information to parties who expressed interest in a LMG transaction (p. 60)</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="n"/>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="3" t="n">
-        <v>44221</v>
+        <v>44186</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>44221</v>
+        <v>44186</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>44222</v>
+        <v>44208</v>
       </c>
     </row>
     <row r="26">
@@ -2227,22 +2176,18 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>01/25/2021 or 01/26/2021</t>
+          <t>01/12/2021</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -2253,50 +2198,32 @@
       </c>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Heavy: subject to due diligence and contract terms, and financed by cash, new equity and new debt. Reconfirmed LMG RemainCo interest in cash and stock at an enterprise value of $2.5–2.7 billion (high end down from $2.75 billion). Wanted Meredith shareholders to keep a stake.</t>
+          <t>Moelis asks Gray and Parties A–D for final offers on the select-station group by 01/25/2021, with markups of the asset purchase agreement. It asks Gray, A and B for LMG proposals by the same date.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>“Party B reconfirmed its interest in acquiring LMG RemainCo in a cash/stock transaction based on an enterprise value of $2.5-$2.7 billion” (p. 61)</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>Q3; Q5</t>
-        </is>
-      </c>
+          <t>representatives of Moelis invited Gray, Party A, Party B, Party C and Party D to submit final offers for the select station group no later than (p. 60)</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="3" t="n">
-        <v>44221</v>
+        <v>44208</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>44221</v>
+        <v>44208</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>44222</v>
+        <v>44208</v>
       </c>
     </row>
     <row r="27">
@@ -2305,22 +2232,18 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>01/25/2021 or 01/26/2021</t>
+          <t>01/23/2021</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -2331,50 +2254,32 @@
       </c>
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Light: subject to final confirmatory due diligence. Offered $63 million cash for the Flint-Saginaw-Bay City station; a final offer with a markup filed 01/21/2021.</t>
+          <t>Target gives feedback on the preliminary APA markups received 01/21/2021 from Gray, A, C and D (B sent none). It signals that closing conditions and indemnities would hurt their bids against rival markups.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>“Party C proposed to acquire the Flint-Saginaw-Bay City station for $63 million in cash, subject to completion of final confirmatory due diligence.” (p. 61)</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>Q3; Q5</t>
-        </is>
-      </c>
+          <t>Moelis communicated that adding closing conditionality and post-closing indemnification obligations would be negatively viewed and put bids at a competitive disadvantage. (p. 61)</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="n"/>
       <c r="S27" s="2" t="n"/>
       <c r="T27" s="3" t="n">
-        <v>44221</v>
+        <v>44219</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>44221</v>
+        <v>44219</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>44222</v>
+        <v>44219</v>
       </c>
     </row>
     <row r="28">
@@ -2383,22 +2288,18 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/25/2021 or 01/26/2021</t>
+          <t>01/25/2021</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -2409,39 +2310,25 @@
       </c>
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Light: subject to confirmatory diligence and contract terms; expected no financing contingency. Offered $61 million cash for the Mobile-Pensacola station; a final offer with a markup filed 01/21/2021.</t>
+          <t>Due date for final select-station offers and revised LMG proposals. Responses arrived on 01/25 and 01/26/2021 and were reviewed by the board on 01/28/2021.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>“Party D proposed to acquire the Mobile-Pensacola station for $61 million in cash” (p. 61)</t>
+          <t>On January 25 and 26, 2021, the Company received five (including one from Gray) final indications of interest for the select stations (p. 61)</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q5</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S28" s="2" t="n"/>
@@ -2452,7 +2339,7 @@
         <v>44221</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>44222</v>
+        <v>44221</v>
       </c>
     </row>
     <row r="29">
@@ -2466,12 +2353,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Gray Television, Inc.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2509,19 +2396,15 @@
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Light: same conditions as the alternative in the previous row. Alternative offer of $146 million cash for both the Mobile-Pensacola and Flint-Saginaw-Bay City stations.</t>
+          <t>Light: subject to certain due diligence items and contract terms. $425M cash for the select stations other than Flint-Saginaw-Bay City, as a first step to acquiring LMG. Formal: APA markup filed 01/21/2021 in reply to the final-offer request.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>“or both the Mobile-Pensacola and Flint-Saginaw-Bay City stations for $146 million in cash” (p. 61)</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>Q3; Q5</t>
-        </is>
-      </c>
+          <t>Gray proposed to purchase the select station group (other than the Flint-Saginaw-Bay City station) for $425 million in cash as a first step in acquiring LMG (p. 61)</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="n"/>
       <c r="S29" s="2" t="n"/>
       <c r="T29" s="3" t="n">
         <v>44221</v>
@@ -2539,18 +2422,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>01/28/2021</t>
+          <t>01/25/2021 or 01/26/2021</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n"/>
+          <t>Gray Television, Inc.</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -2561,36 +2448,50 @@
       </c>
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Citing values indicated by potential acquirers (best station combination $583 million), the board paused the select station sale and turned to a sale of LMG with a simultaneous NMG spin-off. The station sale never resumed.</t>
+          <t>Heavy: subject to diligence items, and substantive LMG diligence continued to April. Revised preliminary proposal for LMG RemainCo stock at EV $2.6–2.7B cash, up from $2.5B at the low end. Public-company deal terms; debt-financed; final bid to have no financing contingency.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>“our Board decided to pause the select station sale process at that time and instructed our senior management and advisors to focus their efforts on advancing preparations” (p. 62)</t>
+          <t>Gray proposed to purchase for cash all of the stock of LMG RemainCo based on an enterprise value of $2.6-$2.7 billion and certain other assumptions (p. 61)</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S30" s="2" t="n"/>
       <c r="T30" s="3" t="n">
-        <v>44224</v>
+        <v>44221</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>44224</v>
+        <v>44221</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>44224</v>
+        <v>44222</v>
       </c>
     </row>
     <row r="31">
@@ -2599,7 +2500,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>by 01/28/2021</t>
+          <t>01/25/2021 or 01/26/2021</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2614,7 +2515,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2625,46 +2526,46 @@
       </c>
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Inferred: the station sale in which it bid was paused on 01/28/2021. Afterwards only Gray and Party B were reported in LMG diligence and invited to bid (02/12, 03/17/2021). Party A made no LMG proposal in round 2 although invited to.</t>
+          <t>Heavy: financing not yet committed; A pledged debt commitment letters 'shortly thereafter'. $560M cash for all four select stations. Formal: APA markup filed 01/21/2021 in reply to the final-offer request.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>“Moelis provided an update on the sale process and diligence activity by Gray and Party B and their advisors and potential lenders.” (p. 63)</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>Party A proposed to purchase all four stations of the select station group for $560 million in cash and pledged to provide executed debt financing commitment letters (p. 61)</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="n"/>
       <c r="S31" s="2" t="n"/>
       <c r="T31" s="3" t="n">
-        <v>44224</v>
+        <v>44221</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>44221</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>44224</v>
+        <v>44222</v>
       </c>
     </row>
     <row r="32">
@@ -2673,22 +2574,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>by 01/28/2021</t>
+          <t>01/25/2021 or 01/26/2021</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -2699,46 +2600,46 @@
       </c>
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Inferred: the station sale in which it bid was paused on 01/28/2021. Afterwards only Gray and Party B were reported in LMG diligence and invited to bid (02/12, 03/17/2021). Party C only ever bid for one station.</t>
+          <t>Heavy: subject to due diligence and contract terms; financing from cash, new equity and new debt. $510M cash for the select-station group. Informal: no APA markup, so not on the requested basis.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>“Moelis provided an update on the sale process and diligence activity by Gray and Party B and their advisors and potential lenders.” (p. 63)</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>Party B proposed to purchase the select station group for $510 million in cash. (p. 61)</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
       <c r="T32" s="3" t="n">
-        <v>44224</v>
+        <v>44221</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>44221</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>44224</v>
+        <v>44222</v>
       </c>
     </row>
     <row r="33">
@@ -2747,12 +2648,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>by 01/28/2021</t>
+          <t>01/25/2021 or 01/26/2021</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2762,7 +2663,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -2773,46 +2674,50 @@
       </c>
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Inferred: the station sale in which it bid was paused on 01/28/2021. Afterwards only Gray and Party B were reported in LMG diligence and invited to bid (02/12, 03/17/2021). Party D bid only for stations in round 2. It returned on its own with an LMG proposal on 03/11/2021.</t>
+          <t>Heavy: subject to due diligence and contract terms; new equity and debt financing. Restates interest in LMG RemainCo at EV $2.5–2.7B in cash and stock, cut from a $2.75B high end. Wants shareholders to keep a stake so LMG RemainCo stays public.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>“Moelis provided an update on the sale process and diligence activity by Gray and Party B and their advisors and potential lenders.” (p. 63)</t>
+          <t>Party B reconfirmed its interest in acquiring LMG RemainCo in a cash/stock transaction based on an enterprise value of $2.5-$2.7 billion (p. 61)</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S33" s="2" t="n"/>
       <c r="T33" s="3" t="n">
-        <v>44224</v>
+        <v>44221</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>44221</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>44224</v>
+        <v>44222</v>
       </c>
     </row>
     <row r="34">
@@ -2821,35 +2726,47 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>03/11/2021</t>
+          <t>01/25/2021 or 01/26/2021</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="n">
         <v>1</v>
       </c>
@@ -2857,28 +2774,24 @@
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Party D came back unsolicited with a written LMG proposal (next row). It was the first LMG interest Party D had shown; its earlier bids were for stations only.</t>
+          <t>Light: subject only to final confirmatory diligence. $63M cash for the Flint-Saginaw-Bay City station. Formal: APA markup filed 01/21/2021 in reply to the final-offer request.</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>“the Company received a written non-binding letter of interest from Party D to acquire LMG in a Reverse Morris Trust transaction” (p. 63)</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>Party C proposed to acquire the Flint-Saginaw-Bay City station for $63 million in cash, subject to completion of final confirmatory due diligence. (p. 61)</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n"/>
       <c r="T34" s="3" t="n">
-        <v>44266</v>
+        <v>44221</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>44266</v>
+        <v>44221</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>44266</v>
+        <v>44222</v>
       </c>
     </row>
     <row r="35">
@@ -2887,7 +2800,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>03/11/2021</t>
+          <t>01/25/2021 or 01/26/2021</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2902,30 +2815,30 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Informal</t>
+          <t>Formal</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
@@ -2935,28 +2848,24 @@
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Heavy: subject to diligence and to reverse diligence confirming synergies, and conditional on a separate deal with Party E. Reverse Morris Trust (spin-off of LMG, not NMG): $2.5 billion cash plus 50.7% of the combined company, whose net leverage would be 6.75x. Not per share.</t>
+          <t>Light: confirmatory diligence and contract terms; D expects no financing contingency. $61M cash for the Mobile-Pensacola station. Formal: APA markup filed 01/21/2021.</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>“Party D’s proposal included $2.5 billion of cash consideration (to refinance the Company’s debt and make a cash dividend to the Company’s shareholders) and a 50.7% ownership interest” (p. 63)</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>Q3; Q6</t>
-        </is>
-      </c>
+          <t>Party D proposed to acquire the Mobile-Pensacola station for $61 million in cash (p. 61)</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="n"/>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="3" t="n">
-        <v>44266</v>
+        <v>44221</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>44266</v>
+        <v>44221</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>44266</v>
+        <v>44222</v>
       </c>
     </row>
     <row r="36">
@@ -2965,54 +2874,72 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/16/2021</t>
+          <t>01/25/2021 or 01/26/2021</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n"/>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Information access differs: Moelis gave Party D access to a limited data room so it could finalize its indication. Gray and Party B had had the full LMG diligence process since February 2021.</t>
+          <t>Light: same terms as the single-station bid. Alternative to the preceding row: $146M cash for both the Mobile-Pensacola and Flint-Saginaw-Bay City stations.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>“Moelis granted Party D access to a limited data room to finalize its indication of interest.” (p. 63)</t>
+          <t>or both the Mobile-Pensacola and Flint-Saginaw-Bay City stations for $146 million in cash. (p. 61)</t>
         </is>
       </c>
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="3" t="n">
-        <v>44271</v>
+        <v>44221</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>44271</v>
+        <v>44221</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>44271</v>
+        <v>44222</v>
       </c>
     </row>
     <row r="37">
@@ -3021,58 +2948,70 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/17/2021</t>
+          <t>by 01/26/2021</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n"/>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2" t="n"/>
-      <c r="O37" s="2" t="n"/>
+      <c r="M37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Moelis sent Gray and Party B process letters and draft merger and separation agreements (3% break fee; $125 million reverse fee; committed financing at signing). Markups were due 04/01/2021; final LMG offers were due 04/14/2021.</t>
+          <t>Inferred. A was invited on 01/12/2021 to submit an LMG proposal. Only two LMG proposals arrived, and the board was updated only on Gray's and B's. A sent only its station bid and is not mentioned again. No reason given.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>“representatives of Moelis provided process letters to Gray and Party B and invited them to submit final offers for LMG no later than April 14, 2021.” (p. 63)</t>
+          <t>two (including one from Gray) revised preliminary indications of interest for LMG. (p. 61)</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q7</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S37" s="2" t="n"/>
       <c r="T37" s="3" t="n">
-        <v>44272</v>
-      </c>
-      <c r="U37" s="3" t="n">
-        <v>44272</v>
-      </c>
+        <v>44222</v>
+      </c>
+      <c r="U37" s="3" t="n"/>
       <c r="V37" s="3" t="n">
-        <v>44272</v>
+        <v>44222</v>
       </c>
     </row>
     <row r="38">
@@ -3081,60 +3020,58 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>03/23/2021</t>
+          <t>01/28/2021</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M38" s="2" t="n"/>
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Party B said it intended to bid all cash rather than in cash and stock; no price was given.</t>
+          <t>Board pauses the select-station sale because of the values bid, and turns to a sale of LMG with a spin-off of NMG. The station-only bidders have no further role. Gray and Party B continue LMG diligence (02/12/2021).</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>“Party B communicated that it intended to submit an all-cash bid after completing its analysis of structure and other elements of the transaction.” (p. 64)</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="n"/>
+          <t>our Board decided to pause the select station sale process at that time (p. 62)</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="3" t="n">
-        <v>44278</v>
+        <v>44224</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>44278</v>
+        <v>44224</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>44278</v>
+        <v>44224</v>
       </c>
     </row>
     <row r="39">
@@ -3143,29 +3080,29 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>03/30/2021</t>
+          <t>by 01/28/2021</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
@@ -3175,16 +3112,24 @@
       <c r="M39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="n"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Target let Party D into the definitive-document stage: all transaction agreement drafts, with markups due 04/08/2021. That was 13 days after Gray and Party B got their drafts. On 03/31/2021 it also sent a structure preferring an NMG spin-off and reverse-diligence requests. Party D was given no final-bid date.</t>
+          <t>Inferred. Party C bid only for select stations. Pausing the station sale left it no stage in the LMG track. No reason given.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>“representatives of Moelis provided drafts of all of the transaction agreements to Party D.” (p. 64)</t>
+          <t>our Board decided to pause the select station sale process at that time (p. 62)</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -3194,13 +3139,11 @@
       </c>
       <c r="S39" s="2" t="n"/>
       <c r="T39" s="3" t="n">
-        <v>44285</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>44285</v>
-      </c>
+        <v>44224</v>
+      </c>
+      <c r="U39" s="3" t="n"/>
       <c r="V39" s="3" t="n">
-        <v>44285</v>
+        <v>44224</v>
       </c>
     </row>
     <row r="40">
@@ -3209,54 +3152,70 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>04/02/2021</t>
+          <t>by 01/28/2021</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Eversheds Sutherland (US) LLP (Eversheds)</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n"/>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2" t="n"/>
-      <c r="O40" s="2" t="n"/>
+      <c r="M40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Gray's legal adviser; filed Gray's markups of all the transaction agreements on 04/02/2021.</t>
+          <t>Inferred. Party D bid only for select stations. Pausing the station sale left it no stage in the LMG track. No reason given. D returned on 03/11/2021.</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>“Gray’s legal advisors, Eversheds Sutherland (US) LLP” (p. 65)</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="n"/>
+          <t>our Board decided to pause the select station sale process at that time (p. 62)</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
       <c r="S40" s="2" t="n"/>
       <c r="T40" s="3" t="n">
-        <v>44288</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>44288</v>
-      </c>
+        <v>44224</v>
+      </c>
+      <c r="U40" s="3" t="n"/>
       <c r="V40" s="3" t="n">
-        <v>44288</v>
+        <v>44224</v>
       </c>
     </row>
     <row r="41">
@@ -3265,60 +3224,54 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>04/08/2021</t>
+          <t>03/05/2021</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Deloitte Tax LLP</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M41" s="2" t="n"/>
       <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Party D submitted a markup of the Merger Agreement only. It was subject to completing diligence, transaction structure and Party D's financing, and would cut the $125 million reverse fee without a counter-figure. Party D also sent structure proposals on 04/02 and 04/13/2021.</t>
+          <t>Target's tax adviser. It first appears in talks with Party B's accountants on the NMG-LMG separation steps; it later worked on Party D's structure.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>“Party D’s legal advisors submitted a markup of the Merger Agreement on behalf of Party D, but did not provide markups of any of the other transaction agreements.” (p. 65)</t>
+          <t>Deloitte Tax LLP (“Deloitte”), tax advisors to the Company, spoke with representatives of Party B and its accountants (p. 63)</t>
         </is>
       </c>
       <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="3" t="n">
-        <v>44294</v>
+        <v>44260</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>44294</v>
+        <v>44260</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>44294</v>
+        <v>44260</v>
       </c>
     </row>
     <row r="42">
@@ -3327,54 +3280,64 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>04/11/2021</t>
+          <t>03/11/2021</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Wells Fargo Securities LLC (Wells Fargo)</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n"/>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="n"/>
+      <c r="M42" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N42" s="2" t="n"/>
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Gray's financial adviser; took part in the 04/11/2021 feedback call on Gray's markups before Gray's final bid.</t>
+          <t>D returns uninvited with a written LMG proposal after its station bid was paused on 01/28/2021 (bidder-initiated). No NDA is mentioned; its earlier agreement is presumed to cover it.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>“financial advisors, Wells Fargo Securities LLC” (p. 65)</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="n"/>
+          <t>the Company received a written non-binding letter of interest from Party D to acquire LMG in a Reverse Morris Trust transaction (p. 63)</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="3" t="n">
-        <v>44297</v>
+        <v>44266</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>44297</v>
+        <v>44266</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>44297</v>
+        <v>44266</v>
       </c>
     </row>
     <row r="43">
@@ -3383,17 +3346,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>04/14/2021</t>
+          <t>03/11/2021</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3405,23 +3368,23 @@
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Formal</t>
+          <t>Informal</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
@@ -3431,28 +3394,28 @@
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Light: debt commitment letters; substantive diligence completed. Final offer: all LMG RemainCo stock for cash at $2.45 billion enterprise value (down from $2.6–2.7 billion); MNI excluded. Its 04/02/2021 markups sought a 5% break fee and a station purchase option.</t>
+          <t>Heavy: subject to diligence and reverse diligence. Non-binding RMT: LMG spun off and combined with D's portfolio stations and Party E's stations. $2.5B cash (debt refinancing and dividend) plus 50.7% of the combined company; 6.75x leverage. No per-share figure.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>“Gray submitted a proposal to purchase all of the stock of LMG RemainCo for cash based on an enterprise value of $2.45 billion” (p. 66)</t>
+          <t>Party D’s proposal included $2.5 billion of cash consideration (to refinance the Company’s debt and make a cash dividend to the Company’s shareholders) and a 50.7% ownership interest (p. 63)</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q7</t>
+          <t>Q7; Q4; Q8</t>
         </is>
       </c>
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="3" t="n">
-        <v>44300</v>
+        <v>44266</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>44300</v>
+        <v>44266</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>44300</v>
+        <v>44266</v>
       </c>
     </row>
     <row r="44">
@@ -3461,12 +3424,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/14/2021</t>
+          <t>03/16/2021</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3476,32 +3439,20 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
       <c r="M44" s="2" t="n">
         <v>1</v>
       </c>
@@ -3509,28 +3460,24 @@
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Light: debt commitment letters; substantive diligence completed. Final offer: all LMG RemainCo stock for cash at $2.3 billion enterprise value (down from $2.5–2.7 billion), MNI included. Merger Agreement markup plus an issues list; would divest one overlap station.</t>
+          <t>Information difference: at the Company's direction D receives only a limited data room so it can finalize its indication, while Gray and Party B were in the full LMG diligence process.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>“Party B also submitted a proposal to purchase all of the stock of LMG RemainCo for cash based on an enterprise value of $2.3 billion” (p. 66)</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>Q3; Q7</t>
-        </is>
-      </c>
+          <t>Moelis granted Party D access to a limited data room to finalize its indication of interest. (p. 63)</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="3" t="n">
-        <v>44300</v>
+        <v>44271</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>44300</v>
+        <v>44271</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>44300</v>
+        <v>44271</v>
       </c>
     </row>
     <row r="45">
@@ -3539,18 +3486,18 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/14/2021</t>
+          <t>03/17/2021</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
+          <t>Meredith (target)</t>
         </is>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
@@ -3569,28 +3516,28 @@
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Due date for final LMG offers from Gray and Party B; both bid on the day. On 04/16/2021 the board judged none of the proposals adequate and gave Gray and Party B a new date (04/20/2021).</t>
+          <t>Process letters invite Gray and Party B to make final LMG offers by 04/14/2021. Draft Merger Agreement and Separation and Distribution Agreement sent, markups due 04/01/2021. Other drafts sent to both on 03/20 and 03/25/2021.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>“invited them to submit final offers for LMG no later than April 14, 2021.” (p. 63)</t>
+          <t>representatives of Moelis provided process letters to Gray and Party B and invited them to submit final offers for LMG no later than April 14, 2021. (p. 63)</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="3" t="n">
-        <v>44300</v>
+        <v>44272</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>44300</v>
+        <v>44272</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>44300</v>
+        <v>44272</v>
       </c>
     </row>
     <row r="46">
@@ -3599,7 +3546,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>04/15/2021</t>
+          <t>03/30/2021</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3614,7 +3561,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -3625,21 +3572,9 @@
       </c>
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
       <c r="M46" s="2" t="n">
         <v>1</v>
       </c>
@@ -3647,28 +3582,28 @@
       <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Heavy: 'highly confident' letters only, up to three weeks needed for committed debt, no equity commitment, still negotiating with Party E. Morris Trust (NMG spin-off): $2.5 billion cash plus 50.8% of the combined company, MNI included; 7.0x leverage. Formal on its 04/08/2021 markup.</t>
+          <t>Target admits D to the documentation stage: drafts of all agreements (NMG spin-off, all-cash merger), markups due 04/08/2021. On 03/31 it states a preference for spinning off NMG and requests reverse-diligence items. D had no 04/14 bid date.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>“Party D submitted a proposal for a Morris Trust transaction reflecting $2.5 billion in cash consideration” (p. 66)</t>
+          <t>representatives of Moelis provided drafts of all of the transaction agreements to Party D. (p. 64)</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q7</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="3" t="n">
-        <v>44301</v>
+        <v>44285</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>44301</v>
+        <v>44285</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>44301</v>
+        <v>44285</v>
       </c>
     </row>
     <row r="47">
@@ -3677,18 +3612,18 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>04/16/2021</t>
+          <t>04/02/2021</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
+          <t>Eversheds Sutherland (US) LLP</t>
         </is>
       </c>
       <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Deadline revised</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
@@ -3707,28 +3642,24 @@
       <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Board found none of the proposals adequate. Gray and Party B were told to raise value significantly, address contract terms and resubmit by 04/20/2021; Moelis passed this on the same day.</t>
+          <t>Gray's legal adviser. Filed Gray's markups of all transaction agreements on 04/02/2021.</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>“increase their value proposals significantly and address other contract terms if they desired to be successful in potentially acquiring LMG and ask them to resubmit proposals by April 20, 2021.” (p. 66)</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>Q7; Q1</t>
-        </is>
-      </c>
+          <t>Gray’s legal advisors, Eversheds Sutherland (US) LLP (“Eversheds”), submitted markups of each of the transaction agreements on behalf of Gray. (p. 65)</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="3" t="n">
-        <v>44302</v>
+        <v>44288</v>
       </c>
       <c r="U47" s="3" t="n">
-        <v>44302</v>
+        <v>44288</v>
       </c>
       <c r="V47" s="3" t="n">
-        <v>44302</v>
+        <v>44288</v>
       </c>
     </row>
     <row r="48">
@@ -3737,18 +3668,18 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>04/16/2021</t>
+          <t>04/11/2021</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
+          <t>Wells Fargo Securities LLC</t>
         </is>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
@@ -3767,28 +3698,24 @@
       <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Target set requirements for Party D: catch up with the other bidders, deliver firm financing commitments, raise the cash component, clarify value and sources and uses, and answer regulatory concerns. No due date was given.</t>
+          <t>Gray's financial adviser. First shown taking part in the target's feedback call on 04/11/2021, before Gray's final bid. Gray's committed financing later came from Wells Fargo Bank and other lenders (p.101).</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>“communicate to Party D that it would need to advance its proposal to catch up with the other parties, deliver firm financing commitments, increase the cash component” (p. 67)</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>Q1; Q7</t>
-        </is>
-      </c>
+          <t>financial advisors, Wells Fargo Securities LLC (“Wells Fargo”), to provide feedback on behalf of the Company in advance of Gray’s final bid (p. 65)</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="n"/>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="3" t="n">
-        <v>44302</v>
+        <v>44297</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>44302</v>
+        <v>44297</v>
       </c>
       <c r="V48" s="3" t="n">
-        <v>44302</v>
+        <v>44297</v>
       </c>
     </row>
     <row r="49">
@@ -3797,18 +3724,18 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>04/18/2021</t>
+          <t>04/14/2021</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
+          <t>Meredith (target)</t>
         </is>
       </c>
       <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
@@ -3827,28 +3754,28 @@
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Information access differs: Moelis sent Gray and Party B, but not Party D, a quarterly LMG update and a list of items a revised bid had to address (liabilities, closing certainty, break and reverse fees).</t>
+          <t>Due date for final LMG offers from Gray and Party B. Both bid that day. D's proposal came 04/15/2021 (D had no 04/14 date). The board found all bids inadequate on 04/16/2021 and set 04/20/2021.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>“representatives of Moelis provided to Gray and Party B a quarterly update on the LMG business” (p. 67)</t>
+          <t>On April 14, 2021, Gray submitted a proposal to purchase all of the stock of LMG RemainCo (p. 66)</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q7</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="S49" s="2" t="n"/>
       <c r="T49" s="3" t="n">
-        <v>44304</v>
+        <v>44300</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>44304</v>
+        <v>44300</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>44304</v>
+        <v>44300</v>
       </c>
     </row>
     <row r="50">
@@ -3857,12 +3784,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>04/19/2021</t>
+          <t>04/14/2021</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Gray Television, Inc.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3905,28 +3832,28 @@
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Light: revised financing commitments for the full price. Raised its bid to $2.65 billion cash (enterprise basis, MNI still excluded), cut the break fee to $36 million, accepted the $125 million reverse termination fee, and expected to close in 2021.</t>
+          <t>Light: debt commitment letters in hand and substantive diligence completed; full completion was later made a deal point. EV $2.45B cash, down from $2.6–2.7B, excluding MNI. Formal: agreement markups (04/02/2021) came with the bid. Will divest Flint station.</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>“Gray submitted a revised proposal for $2.65 billion in cash (up from $2.45 billion and still based on NMG SpinCo retaining the MNI business).” (p. 67)</t>
+          <t>Gray submitted a proposal to purchase all of the stock of LMG RemainCo for cash based on an enterprise value of $2.45 billion (p. 66)</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q7; Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="3" t="n">
-        <v>44305</v>
+        <v>44300</v>
       </c>
       <c r="U50" s="3" t="n">
-        <v>44305</v>
+        <v>44300</v>
       </c>
       <c r="V50" s="3" t="n">
-        <v>44305</v>
+        <v>44300</v>
       </c>
     </row>
     <row r="51">
@@ -3935,7 +3862,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>04/20/2021</t>
+          <t>04/14/2021</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3983,28 +3910,28 @@
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Light: otherwise unchanged from 04/14/2021 (committed debt, diligence done). Raised its bid to $2.33 billion cash from $2.3 billion, MNI included.</t>
+          <t>Light: debt commitment letters and substantive diligence completed. EV $2.3B cash including MNI, down from $2.5–2.7B; B said on 03/23/2021 it would bid all cash. Formal: Merger Agreement markup plus issues list. Will divest one overlap station.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>“Party B submitted a revised proposal for $2.33 billion in cash (up from $2.3 billion).” (p. 67)</t>
+          <t>Party B also submitted a proposal to purchase all of the stock of LMG RemainCo for cash based on an enterprise value of $2.3 billion (p. 66)</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q7; Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="3" t="n">
-        <v>44306</v>
+        <v>44300</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>44306</v>
+        <v>44300</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>44306</v>
+        <v>44300</v>
       </c>
     </row>
     <row r="52">
@@ -4013,18 +3940,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>04/20/2021</t>
+          <t>04/15/2021</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="n"/>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
@@ -4035,36 +3966,50 @@
       </c>
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="n"/>
-      <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="n"/>
-      <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="n"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N52" s="2" t="n"/>
       <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Revised due date for Gray and Party B; both had bid. The board acted on the bids in hand on 04/23/2021.</t>
+          <t>Heavy: 'highly confident' letters only; up to 3 weeks to commit debt; no equity commitments; still negotiating with Party E. Morris Trust spinning off NMG: $2.5B cash plus 50.8%, MNI included. Formal: 04/08 Merger Agreement markup, itself subject to diligence and financing.</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>“ask them to resubmit proposals by April 20, 2021.” (p. 66)</t>
+          <t>Party D submitted a proposal for a Morris Trust transaction reflecting $2.5 billion in cash consideration (p. 66)</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>Q7; Q1</t>
+          <t>Q7; Q4; Q8; Q10</t>
         </is>
       </c>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="3" t="n">
-        <v>44306</v>
+        <v>44301</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>44306</v>
+        <v>44301</v>
       </c>
       <c r="V52" s="3" t="n">
-        <v>44306</v>
+        <v>44301</v>
       </c>
     </row>
     <row r="53">
@@ -4073,22 +4018,18 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>04/23/2021</t>
+          <t>04/16/2021</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline revised</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
@@ -4099,50 +4040,36 @@
       </c>
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="n"/>
+      <c r="M53" s="2" t="n"/>
       <c r="N53" s="2" t="n"/>
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Heavy: otherwise unchanged from 04/15/2021, so financing still not committed. Raised cash to $2.56 billion from $2.50 billion, plus 50.8% of the combined company. On 04/22/2021 Moelis had told Party D to put its best offer forward.</t>
+          <t>The board finds none of the proposals adequate. Moelis tells Gray and Party B the same day to raise value significantly, fix contract terms and resubmit by 04/20/2021.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>“Party D submitted a revised Morris Trust proposal providing for $2.56 billion cash consideration” (p. 67)</t>
+          <t>communicate to Gray and Party B that they would need to increase their value proposals significantly and address other contract terms if they desired to be successful (p. 66)</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q7; Q1</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="S53" s="2" t="n"/>
       <c r="T53" s="3" t="n">
-        <v>44309</v>
+        <v>44302</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>44309</v>
+        <v>44302</v>
       </c>
       <c r="V53" s="3" t="n">
-        <v>44309</v>
+        <v>44302</v>
       </c>
     </row>
     <row r="54">
@@ -4151,15 +4078,19 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>04/23/2021</t>
+          <t>04/16/2021</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n"/>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -4176,33 +4107,31 @@
       <c r="J54" s="2" t="n"/>
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="n"/>
-      <c r="M54" s="2" t="n"/>
+      <c r="M54" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N54" s="2" t="n"/>
       <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Board chose Gray as preferred bidder and required, before full negotiation: $50 million more cash, confirmation that diligence was done, ability to sign within a week, and no delay from approvals or financing. It told Party B it was not competitive and kept developing Party D.</t>
+          <t>Target requirement: Moelis tells D the same day to catch up, deliver firm financing commitments, raise the cash component, clarify value and address regulatory concerns. No due date given.</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>“our Board determined that Gray’s proposal was stronger than the other proposals in terms of value and other key elements.” (p. 68)</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>Q7; Q1</t>
-        </is>
-      </c>
+          <t>communicate to Party D that it would need to advance its proposal to catch up with the other parties, deliver firm financing commitments, increase the cash component (p. 67)</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="n"/>
       <c r="S54" s="2" t="n"/>
       <c r="T54" s="3" t="n">
-        <v>44309</v>
+        <v>44302</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>44309</v>
+        <v>44302</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>44309</v>
+        <v>44302</v>
       </c>
     </row>
     <row r="55">
@@ -4211,22 +4140,18 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>by 04/23/2021</t>
+          <t>04/18/2021</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
@@ -4240,43 +4165,29 @@
       <c r="J55" s="2" t="n"/>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
-      <c r="M55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M55" s="2" t="n"/>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="n"/>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>Inferred: the board had Party B told its proposal was not competitive, and Party B never bid again. An affiliate later offered Party D preferred financing (04/29/2021), and Party B offered stations to Party D's 05/26/2021 bid.</t>
+          <t>Information difference: Gray and Party B receive a quarterly LMG business update and a list of items for their revised bids (liabilities, closing certainty, fees). No such delivery to Party D is reported.</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>“Our Board authorized representatives of Moelis to communicate to Party B that its current proposal was not competitive.” (p. 68)</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>Q8; Q1; Q7</t>
-        </is>
-      </c>
+          <t>representatives of Moelis provided to Gray and Party B a quarterly update on the LMG business and a list of certain items that would need to be addressed (p. 67)</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="n"/>
       <c r="S55" s="2" t="n"/>
       <c r="T55" s="3" t="n">
-        <v>44309</v>
+        <v>44304</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>44306</v>
+        <v>44304</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>44309</v>
+        <v>44304</v>
       </c>
     </row>
     <row r="56">
@@ -4285,12 +4196,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>after the 04/23/2021 board meeting; by 04/25/2021</t>
+          <t>04/19/2021</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Gray Television, Inc.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -4323,7 +4234,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
@@ -4333,28 +4244,28 @@
       <c r="O56" s="2" t="n"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>None: diligence confirmed complete, financing committed, and ready to sign within a week. Accepted the $50 million increase (LMG enterprise value $2.7 billion; per-share figure not yet set). Definitive agreements were exchanged from 04/25/2021.</t>
+          <t>Light: revised financing commitments cover the full price, but the board later required confirmation that all diligence was complete. $2.65B cash, up from $2.45B; MNI stays with SpinCo. Break fee cut to $36M; $125M reverse termination fee accepted.</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>“Gray agreed to the $50 million consideration increase (for a total enterprise valuation of LMG of $2.7 billion) and accepted the other critical deal points” (p. 68)</t>
+          <t>Gray submitted a revised proposal for $2.65 billion in cash (up from $2.45 billion and still based on NMG SpinCo retaining the MNI business). (p. 67)</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q1; Q7</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S56" s="2" t="n"/>
       <c r="T56" s="3" t="n">
-        <v>44309</v>
+        <v>44305</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>44309</v>
+        <v>44305</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>44311</v>
+        <v>44305</v>
       </c>
     </row>
     <row r="57">
@@ -4363,12 +4274,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>04/26/2021</t>
+          <t>04/20/2021</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -4391,7 +4302,7 @@
       <c r="I57" s="2" t="n"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4401,7 +4312,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
@@ -4411,28 +4322,28 @@
       <c r="O57" s="2" t="n"/>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>Heavy: no firm financing commitments; its 04/27/2021 markup stayed subject to diligence, structure and financing and added tax-opinion and Party E closing conditions. Offered $2.66 billion cash plus 50.2% of the combined company, MNI included, and a $100 million regulatory break fee.</t>
+          <t>Light: same terms as the 04/14/2021 bid. $2.33B cash, up from $2.3B, including the MNI business. Formal: the Merger Agreement markup still stands.</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>“provided for $2.66 billion cash consideration (increased from $2.56 billion, to refinance the Company’s debt and make a cash dividend to the Company’s shareholders)” (p. 69)</t>
+          <t>Party B submitted a revised proposal for $2.33 billion in cash (up from $2.3 billion). (p. 67)</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q1; Q7</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S57" s="2" t="n"/>
       <c r="T57" s="3" t="n">
-        <v>44312</v>
+        <v>44306</v>
       </c>
       <c r="U57" s="3" t="n">
-        <v>44312</v>
+        <v>44306</v>
       </c>
       <c r="V57" s="3" t="n">
-        <v>44312</v>
+        <v>44306</v>
       </c>
     </row>
     <row r="58">
@@ -4441,22 +4352,18 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/27/2021</t>
+          <t>04/20/2021</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
@@ -4470,35 +4377,33 @@
       <c r="J58" s="2" t="n"/>
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="n"/>
-      <c r="M58" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M58" s="2" t="n"/>
       <c r="N58" s="2" t="n"/>
       <c r="O58" s="2" t="n"/>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>Target let Party D approach an equity financing source affiliated with the exited Party B, which is a financing-support relationship. This does not form a group (E4).</t>
+          <t>Resubmission date for Gray and Party B; both bid (04/19 and 04/20). The board acted on the bids in hand on 04/23/2021.</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>“The Company gave permission for Party D to speak to an equity financing source affiliated with Party B.” (p. 69)</t>
+          <t>ask them to resubmit proposals by April 20, 2021. (p. 66)</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>Q8; Q1; Q7</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="S58" s="2" t="n"/>
       <c r="T58" s="3" t="n">
-        <v>44313</v>
+        <v>44306</v>
       </c>
       <c r="U58" s="3" t="n">
-        <v>44313</v>
+        <v>44306</v>
       </c>
       <c r="V58" s="3" t="n">
-        <v>44313</v>
+        <v>44306</v>
       </c>
     </row>
     <row r="59">
@@ -4507,7 +4412,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/29/2021</t>
+          <t>04/23/2021</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4555,28 +4460,28 @@
       <c r="O59" s="2" t="n"/>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>Heavy: debt papers only 'near final', and a non-binding preferred term sheet from a Party B affiliate. Revised proposal keeping $2.66 billion cash plus 50.2% of the combined company, now with $2.58 billion debt and $275 million preferred (7.27x). MNI included.</t>
+          <t>Heavy: financing and regulatory concerns unresolved; terms otherwise as on 04/15. $2.56B cash, up from $2.50B, plus 50.8% of the combined company. On 04/22 Moelis told D to put its best offer forward.</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>“The revised proposal continued to contemplate a spin-off of the NMG business and included an alternative” (p. 69)</t>
+          <t>Party D submitted a revised Morris Trust proposal providing for $2.56 billion cash consideration (up from $2.50 billion (p. 67)</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q1; Q7</t>
+          <t>Q7; Q4; Q10</t>
         </is>
       </c>
       <c r="S59" s="2" t="n"/>
       <c r="T59" s="3" t="n">
-        <v>44315</v>
+        <v>44309</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>44315</v>
+        <v>44309</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>44315</v>
+        <v>44309</v>
       </c>
     </row>
     <row r="60">
@@ -4585,22 +4490,18 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>04/29/2021</t>
+          <t>04/23/2021</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
@@ -4611,50 +4512,32 @@
       </c>
       <c r="H60" s="2" t="n"/>
       <c r="I60" s="2" t="n"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" s="2" t="n"/>
       <c r="N60" s="2" t="n"/>
       <c r="O60" s="2" t="n"/>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>Heavy: same financing as the previous row. Alternative to that row: $2.76 billion cash with Meredith shareholders' stake cut from 50.2% to 34%. A later letter put the implied cash dividend at $15.71 per share (p. 71), cash component only.</t>
+          <t>Preferred bidder: the board picks Gray and sets critical deal points: +$50M cash, all diligence complete, able to sign within a week, and no closing delay from approvals or financing. Work on Party D continues.</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>“included an alternative to increase the cash consideration from $2.66 billion to $2.76 billion with a reduction of the ownership interest in the new combined company” (p. 69)</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>Q3; Q1; Q7</t>
-        </is>
-      </c>
+          <t>After discussion, our Board determined that Gray’s proposal was stronger than the other proposals in terms of value and other key elements. (p. 68)</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="n"/>
       <c r="S60" s="2" t="n"/>
       <c r="T60" s="3" t="n">
-        <v>44315</v>
+        <v>44309</v>
       </c>
       <c r="U60" s="3" t="n">
-        <v>44315</v>
+        <v>44309</v>
       </c>
       <c r="V60" s="3" t="n">
-        <v>44315</v>
+        <v>44309</v>
       </c>
     </row>
     <row r="61">
@@ -4663,22 +4546,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>05/03/2021</t>
+          <t>04/23/2021</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
@@ -4695,32 +4578,32 @@
       <c r="M61" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N61" s="2" t="n"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Lower offer than rivals</t>
+        </is>
+      </c>
       <c r="O61" s="2" t="n"/>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Signed at $14.51 cash per share (LMG RemainCo net debt $1.975 billion; $725 million aggregate), plus NMG SpinCo shares in the spin-off. Break fee $36 million; reverse fee $125 million; Class B voting agreement. Moelis gave a fairness opinion.</t>
+          <t>The board authorized telling B that its $2.33B bid was not competitive; Gray's was $2.65B and judged stronger on value. The call itself is not reported. B later appears only as a supporter of D.</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>“the definitive Merger Agreement was executed by authorized officers of the Company, Gray and Merger Sub.” (p. 71)</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="inlineStr">
-        <is>
-          <t>Q1; Q7</t>
-        </is>
-      </c>
+          <t>Our Board authorized representatives of Moelis to communicate to Party B that its current proposal was not competitive. (p. 68)</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="n"/>
       <c r="S61" s="2" t="n"/>
       <c r="T61" s="3" t="n">
-        <v>44319</v>
+        <v>44309</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>44319</v>
+        <v>44309</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>44319</v>
+        <v>44309</v>
       </c>
     </row>
     <row r="62">
@@ -4729,22 +4612,22 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>05/03/2021</t>
+          <t>after the 04/23/2021 board meeting</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Gray Television, Inc.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
@@ -4755,42 +4638,50 @@
       </c>
       <c r="H62" s="2" t="n"/>
       <c r="I62" s="2" t="n"/>
-      <c r="J62" s="2" t="n"/>
-      <c r="K62" s="2" t="n"/>
-      <c r="L62" s="2" t="n"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="M62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>Terms or process</t>
-        </is>
-      </c>
+      <c r="N62" s="2" t="n"/>
       <c r="O62" s="2" t="n"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Still live when Meredith signed with Gray. Board cited certainty of value, regulatory risk, the path to closing and timing; Party D's deal could not be done on Gray's timeline. Party D was told shortly before the announcement.</t>
+          <t>None: Gray confirms all diligence is complete, it can sign within a week, and approvals and financing will not delay closing. It accepts the +$50M, taking EV to $2.7B cash. Drafts reflecting these terms went to Gray on 04/25/2021.</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>“a Moelis representative spoke with a principal of Party D to communicate that the Company would be announcing a transaction with another party” (p. 71)</t>
+          <t>Gray agreed to the $50 million consideration increase (for a total enterprise valuation of LMG of $2.7 billion) and accepted the other critical deal points (p. 68)</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q7</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S62" s="2" t="n"/>
       <c r="T62" s="3" t="n">
-        <v>44319</v>
+        <v>44310</v>
       </c>
       <c r="U62" s="3" t="n">
-        <v>44319</v>
+        <v>44309</v>
       </c>
       <c r="V62" s="3" t="n">
-        <v>44319</v>
+        <v>44311</v>
       </c>
     </row>
     <row r="63">
@@ -4799,56 +4690,76 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>05/03/2021</t>
+          <t>04/26/2021</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="n"/>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Merger announced</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
+      <c r="G63" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="n"/>
-      <c r="J63" s="2" t="n"/>
-      <c r="K63" s="2" t="n"/>
-      <c r="L63" s="2" t="n"/>
-      <c r="M63" s="2" t="n"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N63" s="2" t="n"/>
       <c r="O63" s="2" t="n"/>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Signing announced before market open. The filing mentions media reports about the process, but gives no date for them.</t>
+          <t>Heavy: no firm financing commitments; $2.58B debt plus $200M unspecified sources. $2.66B cash plus 50.2%, with MNI. Adds a $100M regulatory break fee, which the 04/27 markup routes through D's thinly capitalized portfolio company with a 9-month end date.</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>“Execution of the Merger Agreement and other transaction agreements was publicly announced on the morning of May 3, 2021 before market open.” (p. 71)</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="n"/>
+          <t>provided for $2.66 billion cash consideration (increased from $2.56 billion, to refinance the Company’s debt and make a cash dividend to the Company’s shareholders) and a 50.2% continuing ownership interest (p. 69)</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>Q7; Q4; Q10</t>
+        </is>
+      </c>
       <c r="S63" s="2" t="n"/>
       <c r="T63" s="3" t="n">
-        <v>44319</v>
+        <v>44312</v>
       </c>
       <c r="U63" s="3" t="n">
-        <v>44319</v>
+        <v>44312</v>
       </c>
       <c r="V63" s="3" t="n">
-        <v>44319</v>
+        <v>44312</v>
       </c>
     </row>
     <row r="64">
@@ -4857,7 +4768,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>05/13/2021</t>
+          <t>04/27/2021</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4872,16 +4783,14 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
+      <c r="G64" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="H64" s="2" t="n"/>
       <c r="I64" s="2" t="n"/>
@@ -4895,28 +4804,28 @@
       <c r="O64" s="2" t="n"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>Party D came back after signing with an unsolicited proposal (next row). There was no go-shop; the Merger Agreement's no-shop allowed the board to consider it.</t>
+          <t>Financing support: the target lets D talk to an equity financing source affiliated with Party B, which Party B had dropped on 04/23/2021. That affiliate later offered a preferred-stock term sheet (04/29/2021).</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>“Party D sent a letter addressed to our senior management and our Board making an unsolicited, non-binding proposal to acquire LMG RemainCo.” (p. 71)</t>
+          <t>The Company gave permission for Party D to speak to an equity financing source affiliated with Party B. (p. 69)</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="S64" s="2" t="n"/>
       <c r="T64" s="3" t="n">
-        <v>44329</v>
+        <v>44313</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>44329</v>
+        <v>44313</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>44329</v>
+        <v>44313</v>
       </c>
     </row>
     <row r="65">
@@ -4925,7 +4834,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>05/13/2021</t>
+          <t>04/29/2021</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4946,10 +4855,8 @@
       <c r="F65" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
+      <c r="G65" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="H65" s="2" t="n"/>
       <c r="I65" s="2" t="n"/>
@@ -4975,28 +4882,28 @@
       <c r="O65" s="2" t="n"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>Heavy: preferred commitment unsigned and subject to diligence; equity commitment unsigned. Offered $2.76 billion cash plus 19% of the combined company, MNI now excluded. Implied cash dividend $14.99 per share (cash component only). Came with markups of the signed Gray agreements.</t>
+          <t>Heavy: debt papers 'near final'; preferred term sheet from a Party B affiliate non-binding. Alternative to the 04/26 terms: $2.76B cash with shareholders' stake cut to 34%. Implied cash dividend $15.71/share (p.71). Further markups promised 05/01 but never delivered.</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>“The proposal implied a $750 million cash dividend to the Company’s shareholders (based on the $1.975 billion closing net debt target agreed to with Gray), or $14.99 per share” (p. 71)</t>
+          <t>included an alternative to increase the cash consideration from $2.66 billion to $2.76 billion with a reduction of the ownership interest in the new combined company (p. 69)</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q9</t>
+          <t>Q7; Q4; Q8; Q10</t>
         </is>
       </c>
       <c r="S65" s="2" t="n"/>
       <c r="T65" s="3" t="n">
-        <v>44329</v>
+        <v>44315</v>
       </c>
       <c r="U65" s="3" t="n">
-        <v>44329</v>
+        <v>44315</v>
       </c>
       <c r="V65" s="3" t="n">
-        <v>44329</v>
+        <v>44315</v>
       </c>
     </row>
     <row r="66">
@@ -5005,19 +4912,15 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/17/2021</t>
+          <t>undated; before 05/03/2021</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -5026,41 +4929,35 @@
       <c r="F66" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
+      <c r="G66" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="n"/>
       <c r="J66" s="2" t="n"/>
       <c r="K66" s="2" t="n"/>
       <c r="L66" s="2" t="n"/>
-      <c r="M66" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M66" s="2" t="n"/>
       <c r="N66" s="2" t="n"/>
       <c r="O66" s="2" t="n"/>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>Information to the rival: under the Merger Agreement, Moelis told Gray's CEO about Party D's proposal and sent a written summary of its material terms. Gray's counsel sent follow-up questions on 05/19/2021, answered 05/22/2021.</t>
+          <t>Media reports about the process are mentioned only in the board's reasons (p.53). They are undated and placed just before signing. The board says they produced no more certain proposal than Gray's.</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>“representatives of Moelis provided a written summary of the material terms of the proposal to Mr. Howell in accordance with the Merger Agreement.” (p. 73)</t>
+          <t>the fact that this process, even after media reports about it, did not result in any proposals to acquire the Company or the LMG business (p. 53)</t>
         </is>
       </c>
       <c r="R66" s="2" t="n"/>
       <c r="S66" s="2" t="n"/>
       <c r="T66" s="3" t="n">
-        <v>44333</v>
-      </c>
-      <c r="U66" s="3" t="n">
-        <v>44333</v>
-      </c>
+        <v>44319</v>
+      </c>
+      <c r="U66" s="3" t="n"/>
       <c r="V66" s="3" t="n">
-        <v>44333</v>
+        <v>44319</v>
       </c>
     </row>
     <row r="67">
@@ -5069,56 +4966,60 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/17/2021</t>
+          <t>05/03/2021</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Jones Day</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="n"/>
+          <t>Gray Television, Inc.</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Merger agreement signed</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
+      <c r="G67" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="H67" s="2" t="n"/>
       <c r="I67" s="2" t="n"/>
       <c r="J67" s="2" t="n"/>
       <c r="K67" s="2" t="n"/>
       <c r="L67" s="2" t="n"/>
-      <c r="M67" s="2" t="n"/>
+      <c r="M67" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N67" s="2" t="n"/>
       <c r="O67" s="2" t="n"/>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Gray's legal adviser, alongside Eversheds; first shown acting on the 05/17/2021 call with Cooley about Party D's proposal.</t>
+          <t>$14.51/share cash ($725M = $2.7B EV less $1.975B net debt left in LMG RemainCo), plus one NMG SpinCo share per Meredith share. Terms: $36M break fee and $125M reverse fee. Class B holders signed a Gray voting agreement.</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>“representatives of Eversheds and Jones Day, legal advisors to Gray” (p. 73)</t>
+          <t>the definitive Merger Agreement was executed by authorized officers of the Company, Gray and Merger Sub. (p. 71)</t>
         </is>
       </c>
       <c r="R67" s="2" t="n"/>
       <c r="S67" s="2" t="n"/>
       <c r="T67" s="3" t="n">
-        <v>44333</v>
+        <v>44319</v>
       </c>
       <c r="U67" s="3" t="n">
-        <v>44333</v>
+        <v>44319</v>
       </c>
       <c r="V67" s="3" t="n">
-        <v>44333</v>
+        <v>44319</v>
       </c>
     </row>
     <row r="68">
@@ -5127,82 +5028,64 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>05/25/2021</t>
+          <t>05/03/2021</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Not selected at signing</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+      <c r="G68" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="2" t="n"/>
+      <c r="J68" s="2" t="n"/>
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" s="2" t="n"/>
       <c r="M68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N68" s="2" t="n"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Terms or process</t>
+        </is>
+      </c>
       <c r="O68" s="2" t="n"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>Light: an amendment to the signed agreement, requiring only documentation; the offer expired 06/01/2021. Offered $15.25 cash per share (from $14.51; enterprise value $2.737 billion) in return for raising the break fee to $73 million and adding a force-the-vote provision.</t>
+          <t>Told just before the announcement that the Company would sign with another party and must end talks. The board cited certainty, regulatory risk, financing and timing; D's cash headline ($2.76B) exceeded Gray's.</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>“Gray sent a letter addressed to our Board proposing to increase the cash merger payment to the Company’s shareholders to $15.25 per share” (p. 74)</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
+          <t>a Moelis representative spoke with a principal of Party D to communicate that the Company would be announcing a transaction with another party (p. 71)</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="n"/>
       <c r="S68" s="2" t="n"/>
       <c r="T68" s="3" t="n">
-        <v>44341</v>
+        <v>44319</v>
       </c>
       <c r="U68" s="3" t="n">
-        <v>44341</v>
+        <v>44319</v>
       </c>
       <c r="V68" s="3" t="n">
-        <v>44341</v>
+        <v>44319</v>
       </c>
     </row>
     <row r="69">
@@ -5211,78 +5094,54 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>05/26/2021</t>
+          <t>05/03/2021</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Merger announced</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
+      <c r="G69" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="H69" s="2" t="n"/>
       <c r="I69" s="2" t="n"/>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J69" s="2" t="n"/>
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" s="2" t="n"/>
+      <c r="M69" s="2" t="n"/>
       <c r="N69" s="2" t="n"/>
       <c r="O69" s="2" t="n"/>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>Heavy: no updated commitment for the preferred financing (the debt commitment was signed and delivered 05/27/2021). Implied cash dividend $16.51 per share, cash component only, plus 10% of the combined company. Party B would contribute four stations for warrants.</t>
+          <t>Signing announced before the market opened on 05/03/2021.</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>“implied an $825 million aggregate cash dividend to the Company’s shareholders (based on the $1.975 billion closing net debt target agreed to with Gray), or $16.51 per share.” (p. 74)</t>
-        </is>
-      </c>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t>Q3; Q9; Q8</t>
-        </is>
-      </c>
+          <t>Execution of the Merger Agreement and other transaction agreements was publicly announced on the morning of May 3, 2021 before market open. (p. 71)</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="n"/>
       <c r="S69" s="2" t="n"/>
       <c r="T69" s="3" t="n">
-        <v>44342</v>
+        <v>44319</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>44342</v>
+        <v>44319</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>44342</v>
+        <v>44319</v>
       </c>
     </row>
     <row r="70">
@@ -5291,22 +5150,22 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>05/27/2021</t>
+          <t>05/13/2021</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
@@ -5329,24 +5188,28 @@
       <c r="O70" s="2" t="n"/>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>Information to the rival: Moelis told Gray about Party D's revised proposal, sent a written summary, and said the board was inclined to find it could lead to a Superior Company Proposal. Gray's CEO said Gray could improve.</t>
+          <t>D returns after signing with an unsolicited letter to management and the board. Its participation had ended at signing on 05/03/2021.</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>“Later that day, a Moelis representative spoke with Mr. Howell to inform him of Party D’s revised proposal” (p. 74)</t>
-        </is>
-      </c>
-      <c r="R70" s="2" t="n"/>
+          <t>Party D sent a letter addressed to our senior management and our Board making an unsolicited, non-binding proposal to acquire LMG RemainCo. (p. 71)</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
       <c r="S70" s="2" t="n"/>
       <c r="T70" s="3" t="n">
-        <v>44343</v>
+        <v>44329</v>
       </c>
       <c r="U70" s="3" t="n">
-        <v>44343</v>
+        <v>44329</v>
       </c>
       <c r="V70" s="3" t="n">
-        <v>44343</v>
+        <v>44329</v>
       </c>
     </row>
     <row r="71">
@@ -5355,18 +5218,22 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>05/28/2021</t>
+          <t>05/13/2021</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="n"/>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
@@ -5379,36 +5246,50 @@
       </c>
       <c r="H71" s="2" t="n"/>
       <c r="I71" s="2" t="n"/>
-      <c r="J71" s="2" t="n"/>
-      <c r="K71" s="2" t="n"/>
-      <c r="L71" s="2" t="n"/>
-      <c r="M71" s="2" t="n"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N71" s="2" t="n"/>
       <c r="O71" s="2" t="n"/>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>Target set a price requirement: after its board authorized talks for a cash price above Party D's, Meredith told Gray it would accept the $73 million break fee and a 5-business-day match right at $16.99 per share ($2.825 billion), without force-the-vote.</t>
+          <t>Heavy: preferred commitment (Party B affiliate) unsigned and subject to diligence; equity commitment unsigned. $2.76B cash plus 19%; implied dividend $14.99/share; MNI stays with SpinCo. Signed 9-month debt letter. Formal: markups of the signed Gray agreements.</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>“the Company would accept the $73 million break fee if Gray increased enterprise value to $2.825 billion (or $16.99 per share)” (p. 75)</t>
+          <t>The proposal implied a $750 million cash dividend to the Company’s shareholders (based on the $1.975 billion closing net debt target agreed to with Gray), or $14.99 per share (p. 71)</t>
         </is>
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q7; Q4; Q8; Q11; Q10</t>
         </is>
       </c>
       <c r="S71" s="2" t="n"/>
       <c r="T71" s="3" t="n">
-        <v>44344</v>
+        <v>44329</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>44344</v>
+        <v>44329</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>44344</v>
+        <v>44329</v>
       </c>
     </row>
     <row r="72">
@@ -5417,22 +5298,18 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>05/28/2021</t>
+          <t>05/17/2021</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Jones Day</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
@@ -5443,56 +5320,34 @@
           <t>post</t>
         </is>
       </c>
-      <c r="H72" s="2" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" s="2" t="n"/>
       <c r="N72" s="2" t="n"/>
       <c r="O72" s="2" t="n"/>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>Light: an amendment needing only documentation, but the price was tied to deal-protection terms. Offered $16.99 per share ($2.825 billion) with force-the-vote, an option to buy three stations at a discount, and a $73 million fee if NMG SpinCo financing failed.</t>
+          <t>Gray's legal adviser, working with Eversheds on reviewing Party D's proposal.</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>“Gray offered to increase the enterprise value to $2.825 billion ($16.99 per share) but continued to insist on the “force the vote” provision” (p. 75)</t>
-        </is>
-      </c>
-      <c r="R72" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
+          <t>representatives of Cooley spoke with representatives of Eversheds and Jones Day, legal advisors to Gray (“Jones Day”). (p. 73)</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="n"/>
       <c r="S72" s="2" t="n"/>
       <c r="T72" s="3" t="n">
-        <v>44344</v>
+        <v>44333</v>
       </c>
       <c r="U72" s="3" t="n">
-        <v>44344</v>
+        <v>44333</v>
       </c>
       <c r="V72" s="3" t="n">
-        <v>44344</v>
+        <v>44333</v>
       </c>
     </row>
     <row r="73">
@@ -5501,15 +5356,19 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>05/29/2021</t>
+          <t>05/17/2021</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="n"/>
+          <t>Gray Television, Inc.</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -5528,33 +5387,35 @@
       <c r="J73" s="2" t="n"/>
       <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="n"/>
-      <c r="M73" s="2" t="n"/>
+      <c r="M73" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N73" s="2" t="n"/>
       <c r="O73" s="2" t="n"/>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>Target made a counter-proposal through Cooley: it would accept the $73 million termination fee and raise the break fee to $85 million if Gray agreed to $2.825 billion without force-the-vote or the station option.</t>
+          <t>Information to the winner: under the Merger Agreement the target tells Gray about Party D's proposal and gives a written summary of its material terms. Gray's counsel then send follow-up questions (05/19/2021).</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>“offer to increase the break fee to $85 million if Gray would agree to $2.825 billion enterprise value without the “force the vote” provision and without the station purchase option” (p. 75)</t>
+          <t>representatives of Moelis provided a written summary of the material terms of the proposal to Mr. Howell in accordance with the Merger Agreement. (p. 73)</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="S73" s="2" t="n"/>
       <c r="T73" s="3" t="n">
-        <v>44345</v>
+        <v>44333</v>
       </c>
       <c r="U73" s="3" t="n">
-        <v>44345</v>
+        <v>44333</v>
       </c>
       <c r="V73" s="3" t="n">
-        <v>44345</v>
+        <v>44333</v>
       </c>
     </row>
     <row r="74">
@@ -5563,12 +5424,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/31/2021</t>
+          <t>05/25/2021</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Gray Television, Inc.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -5589,11 +5450,11 @@
           <t>post</t>
         </is>
       </c>
-      <c r="H74" s="2" t="n">
-        <v>16.55</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>16.55</v>
+      <c r="H74" s="4" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>15.25</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -5617,28 +5478,28 @@
       <c r="O74" s="2" t="n"/>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>Light: an amendment needing only documentation. Written response: accepted the $85 million break fee and $73 million termination fee and dropped force-the-vote, but kept the station option and cut the price to $16.55 per share ($2.803 billion).</t>
+          <t>Light: committed financing and diligence complete; subject to documenting the amendment. $15.25/share cash, up from $14.51 (EV $2.737B). Asks for a $73M break fee (from $36M) and a 'force the vote' clause. Offer expires 06/01/2021.</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>“Gray retained the station purchase option and reduced its offer to $2.803 enterprise value ($16.55 per share in cash).” (p. 76)</t>
+          <t>Gray sent a letter addressed to our Board proposing to increase the cash merger payment to the Company’s shareholders to $15.25 per share (p. 74)</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="S74" s="2" t="n"/>
       <c r="T74" s="3" t="n">
-        <v>44347</v>
+        <v>44341</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>44347</v>
+        <v>44341</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>44347</v>
+        <v>44341</v>
       </c>
     </row>
     <row r="75">
@@ -5647,17 +5508,17 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/31/2021</t>
+          <t>05/26/2021</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -5673,15 +5534,11 @@
           <t>post</t>
         </is>
       </c>
-      <c r="H75" s="2" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>16.99</v>
-      </c>
+      <c r="H75" s="2" t="n"/>
+      <c r="I75" s="2" t="n"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5691,7 +5548,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
@@ -5701,28 +5558,28 @@
       <c r="O75" s="2" t="n"/>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>Light: an amendment needing only documentation. Through Wells Fargo, Gray said it would go to $16.99 per share ($2.825 billion) only if Meredith accepted either force-the-vote or the station purchase option.</t>
+          <t>Heavy: no updated commitment for preferred financing (now from D). Cash dividend $825M, or $16.51/share, plus 10% of the combined company. Party B contributes four stations for warrants. $2.863B signed debt commitment (delivered 05/27; 9 months).</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>“would only move forward at a $2.825 billion enterprise value ($16.99 per share in cash) if the Company agreed to either the “force the vote” provision” (p. 76)</t>
+          <t>implied an $825 million aggregate cash dividend to the Company’s shareholders (based on the $1.975 billion closing net debt target agreed to with Gray), or $16.51 per share. (p. 74)</t>
         </is>
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q7; Q4; Q8; Q11; Q10</t>
         </is>
       </c>
       <c r="S75" s="2" t="n"/>
       <c r="T75" s="3" t="n">
-        <v>44347</v>
+        <v>44342</v>
       </c>
       <c r="U75" s="3" t="n">
-        <v>44347</v>
+        <v>44342</v>
       </c>
       <c r="V75" s="3" t="n">
-        <v>44347</v>
+        <v>44342</v>
       </c>
     </row>
     <row r="76">
@@ -5731,12 +5588,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>05/31/2021</t>
+          <t>05/27/2021</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Gray Television, Inc.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -5746,7 +5603,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
@@ -5757,27 +5614,11 @@
           <t>post</t>
         </is>
       </c>
-      <c r="H76" s="2" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+      <c r="H76" s="2" t="n"/>
+      <c r="I76" s="2" t="n"/>
+      <c r="J76" s="2" t="n"/>
+      <c r="K76" s="2" t="n"/>
+      <c r="L76" s="2" t="n"/>
       <c r="M76" s="2" t="n">
         <v>1</v>
       </c>
@@ -5785,28 +5626,28 @@
       <c r="O76" s="2" t="n"/>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>Light: an amendment needing only documentation. Gray's CEO proposed $16.99 per share ($2.825 billion) without force-the-vote or the station option if the break fee rose to $125 million.</t>
+          <t>Information to the winner: Gray is told the board leans toward treating D's revised proposal as possibly leading to a superior proposal, and receives a written summary. Gray replies that it can improve.</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>“Mr. Howell asked if the Company would have flexibility to consider increasing the break fee to $125 million if Gray agreed to a $2.825 billion enterprise value” (p. 76)</t>
+          <t>Mr. Howell indicated that Gray had flexibility to improve its proposal and was prepared to negotiate a potential amendment to the transaction agreements over the holiday weekend. (p. 74)</t>
         </is>
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="S76" s="2" t="n"/>
       <c r="T76" s="3" t="n">
-        <v>44347</v>
+        <v>44343</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>44347</v>
+        <v>44343</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>44347</v>
+        <v>44343</v>
       </c>
     </row>
     <row r="77">
@@ -5815,19 +5656,15 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>05/31/2021 (evening)</t>
+          <t>05/28/2021</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -5846,35 +5683,33 @@
       <c r="J77" s="2" t="n"/>
       <c r="K77" s="2" t="n"/>
       <c r="L77" s="2" t="n"/>
-      <c r="M77" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M77" s="2" t="n"/>
       <c r="N77" s="2" t="n"/>
       <c r="O77" s="2" t="n"/>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>Agreement in principle: after Meredith countered at a $113 million (4%) break fee, both CEOs agreed to recommend an amendment at $16.99 per share with a $113 million break fee and a $73 million fee if NMG SpinCo financing failed.</t>
+          <t>Target price requirement: the board wants cash above D's revised proposal. Moelis offers to accept a $73M break fee and a 5-business-day match right at EV $2.825B ($16.99/share), without 'force the vote'.</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>“Messrs. Harty and Howell agreed that they were both prepared to recommend to their respective Boards an amendment that provided for a $2.825 billion enterprise value ($16.99 per share)” (p. 76)</t>
+          <t>the Moelis representative communicated that the Company would accept the $73 million break fee if Gray increased enterprise value to $2.825 billion (or $16.99 per share) (p. 75)</t>
         </is>
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="S77" s="2" t="n"/>
       <c r="T77" s="3" t="n">
-        <v>44347</v>
+        <v>44344</v>
       </c>
       <c r="U77" s="3" t="n">
-        <v>44347</v>
+        <v>44344</v>
       </c>
       <c r="V77" s="3" t="n">
-        <v>44347</v>
+        <v>44344</v>
       </c>
     </row>
     <row r="78">
@@ -5883,12 +5718,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/02/2021</t>
+          <t>05/28/2021</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Gray Television, Inc.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -5898,7 +5733,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
@@ -5909,11 +5744,27 @@
           <t>post</t>
         </is>
       </c>
-      <c r="H78" s="2" t="n"/>
-      <c r="I78" s="2" t="n"/>
-      <c r="J78" s="2" t="n"/>
-      <c r="K78" s="2" t="n"/>
-      <c r="L78" s="2" t="n"/>
+      <c r="H78" s="4" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
       <c r="M78" s="2" t="n">
         <v>1</v>
       </c>
@@ -5921,28 +5772,28 @@
       <c r="O78" s="2" t="n"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>Amendment to the Merger Agreement executed at $16.99 cash per share (from $14.51), with a $113 million break fee, a $73 million financing-failure fee, and no force-the-vote or station option. Meredith's board approved it 06/01/2021; Gray delivered updated financing commitments.</t>
+          <t>Light: as on 05/25. $16.99/share cash (EV $2.825B), but insists on 'force the vote'. Adds an option to buy three stations at a discount if the board changes course, plus a $73M fee if SpinCo financing fails.</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>“the parties executed the amendment to the Merger Agreement and the amendment to the Separation and Distribution Agreement, and Gray delivered updated executed financing commitments.” (p. 77)</t>
+          <t>Gray offered to increase the enterprise value to $2.825 billion ($16.99 per share) but continued to insist on the “force the vote” provision (p. 75)</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="S78" s="2" t="n"/>
       <c r="T78" s="3" t="n">
-        <v>44349</v>
+        <v>44344</v>
       </c>
       <c r="U78" s="3" t="n">
-        <v>44349</v>
+        <v>44344</v>
       </c>
       <c r="V78" s="3" t="n">
-        <v>44349</v>
+        <v>44344</v>
       </c>
     </row>
     <row r="79">
@@ -5951,22 +5802,18 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/02/2021</t>
+          <t>05/29/2021</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
@@ -5982,39 +5829,33 @@
       <c r="J79" s="2" t="n"/>
       <c r="K79" s="2" t="n"/>
       <c r="L79" s="2" t="n"/>
-      <c r="M79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N79" s="2" t="inlineStr">
-        <is>
-          <t>Terms or process</t>
-        </is>
-      </c>
+      <c r="M79" s="2" t="n"/>
+      <c r="N79" s="2" t="n"/>
       <c r="O79" s="2" t="n"/>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>Still live with its 05/26/2021 proposal when the Gray amendment was signed. Board cited certainty of value, regulatory risk, the path to closing and timing. Party D was told of the coming announcement.</t>
+          <t>Target counter-proposal, relayed by Cooley that morning: accept the $73M termination fee and raise the break fee to $85M if Gray pays EV $2.825B with no 'force the vote' and no station option.</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>“a Moelis representative spoke with a principal of Party D to communicate that the Company would be announcing the execution of the amendment with Gray.” (p. 77)</t>
+          <t>offer to increase the break fee to $85 million if Gray would agree to $2.825 billion enterprise value without the “force the vote” provision and without the station purchase option (p. 75)</t>
         </is>
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="S79" s="2" t="n"/>
       <c r="T79" s="3" t="n">
-        <v>44349</v>
+        <v>44345</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>44349</v>
+        <v>44345</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>44349</v>
+        <v>44345</v>
       </c>
     </row>
     <row r="80">
@@ -6023,18 +5864,22 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>06/03/2021</t>
+          <t>05/31/2021</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="n"/>
+          <t>Gray Television, Inc.</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Merger announced</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
@@ -6045,38 +5890,514 @@
           <t>post</t>
         </is>
       </c>
-      <c r="H80" s="2" t="n"/>
-      <c r="I80" s="2" t="n"/>
-      <c r="J80" s="2" t="n"/>
-      <c r="K80" s="2" t="n"/>
-      <c r="L80" s="2" t="n"/>
-      <c r="M80" s="2" t="n"/>
+      <c r="H80" s="4" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N80" s="2" t="n"/>
       <c r="O80" s="2" t="n"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>Merger Agreement amendment ($16.99 per share) announced before market open. The 10/06/2021 Consent Agreement tied to the Dotdash sale of NMG SpinCo left the $16.99 unchanged.</t>
+          <t>Light: as before. Written reply accepts the $85M break fee and $73M termination fee and drops 'force the vote', but keeps the station option and cuts the price to $16.55/share (EV $2.803B).</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>“The Company and Gray publicly announced their agreement on the Merger Agreement amendment early in the morning of June 3, 2021” (p. 77)</t>
-        </is>
-      </c>
-      <c r="R80" s="2" t="n"/>
+          <t>Gray retained the station purchase option and reduced its offer to $2.803 enterprise value ($16.55 per share in cash). (p. 76)</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
       <c r="S80" s="2" t="n"/>
       <c r="T80" s="3" t="n">
+        <v>44347</v>
+      </c>
+      <c r="U80" s="3" t="n">
+        <v>44347</v>
+      </c>
+      <c r="V80" s="3" t="n">
+        <v>44347</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>05/31/2021</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Gray Television, Inc.</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N81" s="2" t="n"/>
+      <c r="O81" s="2" t="n"/>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>Light: as before. Via Wells Fargo, Gray returns to $16.99/share (EV $2.825B), but only with either 'force the vote' or the station purchase option.</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>Gray would only move forward at a $2.825 billion enterprise value ($16.99 per share in cash) if the Company agreed to either the “force the vote” provision (p. 76)</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="n"/>
+      <c r="T81" s="3" t="n">
+        <v>44347</v>
+      </c>
+      <c r="U81" s="3" t="n">
+        <v>44347</v>
+      </c>
+      <c r="V81" s="3" t="n">
+        <v>44347</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>05/31/2021</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Gray Television, Inc.</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" s="2" t="n"/>
+      <c r="O82" s="2" t="n"/>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>Light: as before. Howell floats $16.99/share with no 'force the vote' or station option, in exchange for a $125M break fee. The Company answered with $113M (4% of transaction value).</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>Mr. Howell asked if the Company would have flexibility to consider increasing the break fee to $125 million if Gray agreed to a $2.825 billion enterprise value (p. 76)</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="n"/>
+      <c r="T82" s="3" t="n">
+        <v>44347</v>
+      </c>
+      <c r="U82" s="3" t="n">
+        <v>44347</v>
+      </c>
+      <c r="V82" s="3" t="n">
+        <v>44347</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>evening of 05/31/2021</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Gray Television, Inc.</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" s="2" t="n"/>
+      <c r="O83" s="2" t="n"/>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>Light: pending board approval and documentation. Harty and Howell agree to recommend $16.99/share (EV $2.825B) with a $113M break fee and a $73M SpinCo-financing termination fee. The Meredith board backed it on 06/01/2021.</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>Messrs. Harty and Howell agreed that they were both prepared to recommend to their respective Boards an amendment that provided for a $2.825 billion enterprise value ($16.99 per share) (p. 76)</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="n"/>
+      <c r="T83" s="3" t="n">
+        <v>44347</v>
+      </c>
+      <c r="U83" s="3" t="n">
+        <v>44347</v>
+      </c>
+      <c r="V83" s="3" t="n">
+        <v>44347</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>06/02/2021</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Gray Television, Inc.</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Other material event</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n"/>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="2" t="n"/>
+      <c r="K84" s="2" t="n"/>
+      <c r="L84" s="2" t="n"/>
+      <c r="M84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" s="2" t="n"/>
+      <c r="O84" s="2" t="n"/>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>Amendment executed after market close: $16.99/share cash, $113M break fee, $73M financing-failure fee, no 'force the vote' or station option. Gray delivered updated financing commitments. Recorded as an amendment, not a new signing.</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>the parties executed the amendment to the Merger Agreement and the amendment to the Separation and Distribution Agreement, and Gray delivered updated executed financing commitments. (p. 77)</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="n"/>
+      <c r="T84" s="3" t="n">
+        <v>44349</v>
+      </c>
+      <c r="U84" s="3" t="n">
+        <v>44349</v>
+      </c>
+      <c r="V84" s="3" t="n">
+        <v>44349</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>06/02/2021</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Not selected at signing</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n"/>
+      <c r="I85" s="2" t="n"/>
+      <c r="J85" s="2" t="n"/>
+      <c r="K85" s="2" t="n"/>
+      <c r="L85" s="2" t="n"/>
+      <c r="M85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Terms or process</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="n"/>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>Told the amended Gray deal would be announced. The board judged Gray's amended offer better on certainty, regulation, path to closing and timing than D's 05/26 proposal. No further D activity is reported.</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>a Moelis representative spoke with a principal of Party D to communicate that the Company would be announcing the execution of the amendment with Gray. (p. 77)</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="S85" s="2" t="n"/>
+      <c r="T85" s="3" t="n">
+        <v>44349</v>
+      </c>
+      <c r="U85" s="3" t="n">
+        <v>44349</v>
+      </c>
+      <c r="V85" s="3" t="n">
+        <v>44349</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>06/03/2021</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Meredith (target)</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Other material event</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n"/>
+      <c r="I86" s="2" t="n"/>
+      <c r="J86" s="2" t="n"/>
+      <c r="K86" s="2" t="n"/>
+      <c r="L86" s="2" t="n"/>
+      <c r="M86" s="2" t="n"/>
+      <c r="N86" s="2" t="n"/>
+      <c r="O86" s="2" t="n"/>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>Public announcement of the amendment ($16.99/share) before market open. Later event, no row: on 10/06/2021 NMG SpinCo agreed to sell to Dotdash (IAC), with Gray's consent (Deal facts).</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>The Company and Gray publicly announced their agreement on the Merger Agreement amendment early in the morning of June 3, 2021 before market open. (p. 77)</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="n"/>
+      <c r="T86" s="3" t="n">
         <v>44350</v>
       </c>
-      <c r="U80" s="3" t="n">
+      <c r="U86" s="3" t="n">
         <v>44350</v>
       </c>
-      <c r="V80" s="3" t="n">
+      <c r="V86" s="3" t="n">
         <v>44350</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V80"/>
+  <autoFilter ref="A1:V86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6093,12 +6414,12 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
     <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -6166,12 +6487,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Moelis outreach to 20 parties to sell four select stations; NDA signers invited to submit preliminary indications (#5).</t>
+          <t>Moelis outreach to 20 parties for the four-station group (St. Louis, Mobile-Pensacola, Flint-Saginaw-Bay City, Springfield-Holyoke). Preliminary IOIs requested; NDA signers got preliminary financial and diligence information.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>17 NDA signers (types not split; Unknown), incl. Gray (Strategic) and, apparently, Party A (Strategic), Party B (Financial), Party C (Strategic) and Party D (Financial).</t>
+          <t>17 NDA signers. Strategic 3: Gray, Party A, Party C. Financial 2: Party B, Party D. Unknown 12: unnamed signers (A–D inferred to be among the 17; Q2).</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -6191,12 +6512,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>5 bidders: station bids from Parties A, B, C, D (Other-scope); LMG indications from Gray, Party A and Party B.</t>
+          <t>5 bidders: Party A, Party B (station bids plus LMG EV ranges), Party C, Party D (station bids), Gray (LMG EV range only).</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Five advanced (Parties A–D to round 2 on 12/21/2020; Gray invited 01/12/2021); 12–16 NDA signers out without bidding.</t>
+          <t>five advanced (A–D invited to round 2; Gray included in the 01/12/2021 invitation), twelve out (no submission)</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6533,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Board admitted first-round station bidders to a second round with full data room (#17); final station offers and LMG proposals requested 01/12/2021.</t>
+          <t>After the 12/21/2020 board meeting, first-round station bidders were invited to a second round with full data rooms, and LMG-interested parties got selected LMG information. On 01/12/2021 final station offers (with APA markups) and revised LMG proposals were requested. Only the station offers were called 'final'.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>5: Gray (Strategic, invited 01/12/2021), Party A (Strategic), Party B (Financial), Party C (Strategic), Party D (Financial).</t>
+          <t>5 admitted. Strategic 3: Gray, Party A, Party C. Financial 2: Party B, Party D. Party D after its 03/11/2021 re-entry (uninvited LMG proposal; limited data room 03/16): still being received, not admitted.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -6232,17 +6553,17 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Not final</t>
+          <t>Announced as final</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>5 bidders: final station offers from Gray, Parties A, B, C, D; revised LMG proposals from Gray and Party B.</t>
+          <t>5 bidders: Gray, Party A, Party B, Party C, Party D (select-station offers). Gray and Party B also sent revised LMG proposals. Party D sent an uninvited LMG proposal on 03/11/2021.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Station sale paused 01/28/2021; Gray and Party B carried forward for LMG; Parties A, C, D out (inferred).</t>
+          <t>Station sale paused 01/28/2021. Two advanced to the final LMG round (Gray, Party B). Party A made no LMG proposal; Parties C and D dropped. D re-entered 03/11/2021 and was admitted to round 3 on 03/30/2021.</t>
         </is>
       </c>
     </row>
@@ -6258,17 +6579,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Process letters to Gray and Party B inviting final LMG offers, with draft Merger and Separation agreements (#36).</t>
+          <t>Process letters invited final LMG offers, with draft Merger Agreement and separation agreements (markups due 04/01/2021).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2 admitted: Gray (Strategic), Party B (Financial); then Party D (Financial), re-entered unsolicited 03/11/2021, given a limited data room 03/16 and draft agreements 03/30/2021, but no bid due date.</t>
+          <t>3. Strategic 1: Gray. Financial 2: Party B (both invited 03/17/2021) and Party D (admitted 03/30/2021 through draft agreements and a markup request for 04/08/2021; no bid date).</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>04/14/2021 → 04/20/2021 (Gray and Party B only)</t>
+          <t>04/14/2021 → 04/20/2021 (Gray and Party B)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6283,12 +6604,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3 bidders: Gray (04/14, 04/19, 04/23), Party B (04/14, 04/20), Party D (04/15, 04/23, 04/26, 04/29 with alternative).</t>
+          <t>3 bidders: Gray (04/14, 04/19, 04/23), Party B (04/14, 04/20), Party D (04/15, 04/23, 04/26, 04/29).</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Gray selected 04/23/2021 and signed 05/03/2021; Party B dropped 04/23; Party D not selected at signing. Post-signing, Party D re-entered and lost again at the 06/02/2021 amendment; no participant open at the filing cutoff.</t>
+          <t>signing with Gray 05/03/2021 at $14.51 cash per share. Party B dropped 04/23/2021; Party D not selected at signing. After signing, D's unsolicited bids ended with the 06/02/2021 amendment to $16.99.</t>
         </is>
       </c>
     </row>
@@ -6304,16 +6625,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6361,27 +6682,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Process and round map: one process with rounds 1 (11/16/2020 station outreach), 2 (12/21/2020 second round; final request 01/12/2021) and 3 (03/17/2021 final LMG letters), Party D's 03/11/2021 proposal in round 0, and the May–June 2021 contest post-signing. Is this right, and is round 2 Not final?</t>
+          <t>Is the sale correctly mapped as one process with three rounds? R1 is the select-station IOI round from 11/16/2020, R2 the second round from 12/21/2020 (final station offers, revised LMG proposals) and R3 the final LMG round from 03/17/2021. Post-signing contests are post.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Keep this map. Alternatives: round 2 opens at the 01/12/2021 final request (#17–#18 move to round 1); 04/16/2021 opens round 4 (#46–#61 move; see Q7). Round 2 finality: keep Not final (Announced as final holds only for station offers).</t>
+          <t>Yes. Keep one process with three rounds. Keep R2 open through the 01/28/2021 pivot to LMG and D's uninvited 03/11/2021 proposal, and close it when the final-offer letters went out on 03/17/2021.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Station offers were requested as final (p. 60–61), but LMG proposals came back as 'revised preliminary indications' (p. 61). Gaps of about two months or more with no acquirer contact: May 2020 to 11/16/2020, before any contact (pp. 58–60); 06/03/2021 to 11/08/2021 filing (p. 77). E5: (a) fails, since Gray and Party B were carried from the 01/28/2021 pause (p. 62–63); (b) fails, with no gap of three months or more after 11/16/2020; (c) the 01/28/2021 LMG decision is a fresh start, but (a) and (b) fail. Result: one process. Fall 2019 talks (p. 58) are too vague for rows.</t>
+          <t>E5 tests: (a) no; Gray and B stayed in LMG diligence (p.63) and D returned 03/11/2021. (b) No break: no gap of about two months without acquirer contact between 11/16/2020 and 06/02/2021. (c) Not needed. Gaps of about two months or more: Fall 2019–11/16/2020 (before the process) and 06/02/2021–10/06/2021 (after signing; Gray's consent to Dotdash). Next-best alternative: open a round at the 01/28/2021 pivot, since Feb 2021 was an LMG diligence stage (pp.62–63). R2's Finality reflects the station offers called 'final'; the LMG proposals in R2 were preliminary.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#4, #5, #17, #18, #19, #29, #36, #46, #47, #48, #49, #50, #51, #52, #53, #54, #55, #56, #57, #58, #59, #60, #61</t>
+          <t>#6, #23, #37, #44, #45</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Round membership of bids and exits; the Rounds sheet; round 2's finality for the formality of later reinterpretations.</t>
+          <t>Split at 01/28/2021: rows #37–#43 would form a new round 3, and #44–#68 would become round 4. Dating R2 from 01/12/2021 would move #23 to 01/12/2021 and put #24 in round 1. Live-bidder counts at each opening would be unchanged.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -6394,27 +6715,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Are Parties A–D among the 17 NDA signers, which would make the residual non-submitter count exactly 12?</t>
+          <t>Are Parties A–D among the 17 NDA signers, so that exactly 12 unnamed signers made no round-1 submission?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Yes in substance, but keep Count blank ('12–16') unless the reviewer accepts the inference; then set #16 Count = 12.</t>
+          <t>Yes. Keep Count 12 on both cohort rows and the inferred NDA rows for A–D.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Only NDA counterparties were invited to review information and submit indications by 12/17/2020 (p. 60), and the four bidders came from the 20 parties contacted. The filing names only Gray as a signer (p. 60).</t>
+          <t>p.60: NDAs were signed with 17 interested parties, including Gray, and 'the counterparties' were invited to review information and bid by 12/17/2020. The four bidders answered that invitation (p.60). No party is described as bidding without an NDA.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#7, #16</t>
+          <t>#9, #10, #11, #12, #13, #22</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Count on #16 (12 vs blank); the number of live units at the round 2 opening (5 either way).</t>
+          <t>If a bidder bid without an NDA, the non-submitting remainder would be 12–16. Count would then be blank and R1's 'Who was in' qualified. The auction screen stays Met: Gray plus at least one other.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -6427,27 +6748,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Should the LMG RemainCo proposals count as whole-company Bids, and how should prices stated as enterprise value or cash plus stock be handled?</t>
+          <t>Round 1 due date 12/17/2020: is the outcome Enforced?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Treat LMG RemainCo proposals as Bids and station proposals as Other-scope bids. Leave per-share cells blank unless a per-share total is stated.</t>
+          <t>Enforced.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Gray buys all the stock of Meredith after it distributes NMG SpinCo to its own shareholders, who get $16.99 per share in cash plus the SpinCo shares (pp. 71, 77). This is analogous to a rollover. LMG bids were quoted as enterprise values until May 2021 (pp. 60–69). Party D's bids mix cash with stock of a new combined company; per-share figures cover only its cash dividend (pp. 71, 74).</t>
+          <t>p.60: IOIs were due by 12/17/2020. On 12/21/2020 the board reviewed the four station bids and the LMG indications in hand, then advanced the station bidders. No late or extended submission is reported.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#8, #9, #10, #11, #12, #13, #14, #21, #22, #23, #24, #25, #26, #27, #28, #34, #42, #43, #45, #49, #50, #52, #55, #56, #58, #59, #64, #68</t>
+          <t>#14</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>If LMG proposals were Other-scope, the ledger would have no whole-company bids before 05/25/2021 and the Deal facts screen would read 'No'; prices would be unaffected.</t>
+          <t>If arrival dates are treated as unknown, the outcome is Unclear. Participation counts are unchanged.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -6460,27 +6781,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Outcome of the round 1 due date (12/17/2020).</t>
+          <t>LMG bids are stated as enterprise values, EV ranges, or (for Party D) cash plus a stake in a new combined company. Per-share figures appear only from signing onward. Should price cells stay blank where no per-share total is given, including D's implied per-share cash dividends?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Enforced.</t>
+          <t>Yes. Keep EV and structure in the Notes. Fill price cells only for Gray's stated per-share offers ($15.25, $16.99, $16.55). Leave D's cash-only figures ($15.71, $14.99, $16.51) out of the price cells.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>On 12/21/2020 the board reviewed the four station bids and three LMG indications and invited only the submitters to round 2 (p. 60). No extension or late bid is reported. Arrival days are not given.</t>
+          <t>E13 fills per-share cells only with a per-share figure for the whole offer. D's figures are cash dividends and exclude its stake in the combined company (pp.71, 74). EVs could be turned into per-share values only through the $1.975B net-debt figure agreed on 05/02/2021 (p.70), which the filing does not apply to earlier bids.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#15, #16</t>
+          <t>#15, #17, #19, #29, #32, #42, #49, #50, #51, #55, #56, #58, #61, #62, #64, #70, #74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Deadline outcome in Rounds (Enforced vs Unclear); the inferred Did not submit exit on #16.</t>
+          <t>Converting EVs would add per-share prices to most pre-signing bids. Entering D's cash figures as prices would understate D's offers, which also included 10–50.8% of the combined company.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -6493,7 +6814,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Outcome of the round 2 due date (01/25/2021), when bids arrived on 01/25 and 01/26/2021.</t>
+          <t>Round 2 due date 01/25/2021: is the outcome Late bids accepted?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -6503,17 +6824,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>'On January 25 and 26, 2021, the Company received five ... final indications' against a 'no later than January 25, 2021' deadline (pp. 60–61). The board considered all of them on 01/28/2021 (p. 62). Which bid arrived on the 26th is not stated.</t>
+          <t>p.61: final offers were due 'no later than January 25, 2021'. The Company received them 'on January 25 and 26, 2021', and the board reviewed all of them on 01/28/2021 (p.62). So at least one arrived a day late and was considered. The filing does not say which.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#20, #21, #22, #23, #24, #25, #26, #27, #28</t>
+          <t>#27</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Rounds outcome would be Enforced if the 01/26 receipts are treated as on time; it does not affect exits.</t>
+          <t>If 25–26 January is read as an on-time receipt window, the outcome would be Enforced. Only the Rounds cell changes.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -6526,27 +6847,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Exits of Parties A, C and D at the 01/28/2021 station-process pause, and Party D's return on 03/11/2021 as a round 0 re-entry.</t>
+          <t>How should Parties A, C and D leave round 2, and is D's 03/11/2021 letter a re-entry?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Keep the inferred Dropped by target exits by 01/28/2021 and Party D's Re-entered row plus round 0 bid on 03/11/2021.</t>
+          <t>A: Did not submit its LMG proposal by 01/26/2021. C and D: Dropped by target by 01/28/2021 when the station sale was paused. D: Re-entered on 03/11/2021. All exits are inferred, with reason Not stated.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>The station sale was paused and never resumed (p. 62). Only Gray and Party B were later in LMG diligence and invited on 03/17/2021 (pp. 63). Party D's 03/11/2021 letter was unsolicited (p. 63), and it was brought into the document stage on 03/30/2021 (p. 64).</t>
+          <t>p.61: A was invited to bid for LMG, but only two LMG proposals came in, and the 01/28 update names only Gray's and B's (p.62). The pause left station-only bidders without a stage (p.62). D came back uninvited (p.63).</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#30, #31, #32, #33, #34, #38</t>
+          <t>#36, #38, #39, #41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Alternative: A and C become Not selected at signing by 05/03/2021, and D stays live with no exit or re-entry and its 03/11 bid in round 3. That changes live counts between 01/28 and 03/17/2021.</t>
+          <t>Alternatives: A as Dropped by target at the pause (its station bid was still outstanding), or D kept live throughout (no exit or re-entry). Either would change the live count between 01/28 and 03/11/2021 and whether A's exit signals its valuation.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -6559,27 +6880,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Outcomes of round 3's due dates (04/14/2021 and 04/20/2021).</t>
+          <t>Should Party D's Reverse Morris Trust / Morris Trust proposals (cash for debt refinancing and a dividend, plus 50.7%, later down to 10%, of a combined company) be whole-company Bids with All cash = No?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Extended; Enforced.</t>
+          <t>Yes. Each was a proposal 'to acquire LMG' or LMG RemainCo, the business Gray bought, and the board compared them directly with Gray's bids.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>After judging the 04/14 bids inadequate, the board asked Gray and Party B to resubmit by 04/20/2021 (pp. 66–67), which counts as a later due date in the same round (E9). On 04/23/2021 it selected Gray on the bids in hand (p. 68). Party D was never given a bid date.</t>
+          <t>pp.63–74: the filing calls them proposals to acquire LMG and LMG RemainCo. From 04/13/2021 they spun off NMG exactly as the Gray deal does. The 03/11 version spun off LMG instead, but the whole LMG business still passed to the combined company.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>#36, #42, #43, #44, #45, #46, #47, #48, #49, #50, #51, #52, #53, #54, #55, #56, #57, #58, #59, #60, #61</t>
+          <t>#42, #51, #58, #62, #64, #70, #74</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>If 04/16 instead opens round 4, 04/14 becomes Enforced and round 4's 04/20 date Enforced; #46–#61 move to round 4, whose finality would be Inferred final.</t>
+          <t>Treating D's proposals, or only the 03/11 RMT, as Other-scope bids would remove D's whole-company bids from rounds 2–3 and post. That would leave Gray almost unopposed in the final stage.</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -6592,27 +6913,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>How did Party B leave: Dropped by target on 04/23/2021, or Not selected at signing on 05/03/2021? And does its later support of Party D make a bidding group?</t>
+          <t>Do Party E (contributing stations) and Party B (its affiliate offered preferred equity from 04/27/2021; B contributed four stations for warrants on 05/26/2021) form a bidding group with Party D?</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target (inferred) by 04/23/2021, with no Bidding group changed row.</t>
+          <t>No. Keep D as a single Financial bidder and name its supporters in the Notes.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>The board had Party B told its proposal 'was not competitive' (p. 68), and Party B never bid again. Its affiliate's preferred term sheet (p. 69) and its station contribution for warrants (p. 74) are financing and asset support for Party D after B's exit (E4).</t>
+          <t>E never bid alone or entered the process (p.63, p.66). B's affiliate gave financing support that the target allowed (p.69). B's stations were contributed for warrants inside D's proposal (p.74), after B was dropped on 04/23/2021 (p.68). Under E4, financing support does not make a group.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>#54, #57, #68</t>
+          <t>#42, #51, #63, #64, #70, #74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Exit label and date for Party B; if support is read as joining Party D's unit, a group-change row would follow on 05/26/2021.</t>
+          <t>A Bidding group changed row on 04/27 or 05/26/2021 would merge B into D's unit after B's exit. D's type might then be reread as Mixed.</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -6625,33 +6946,99 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Post-signing coding: Gray's amendment offers as Formal/Light, the 06/02/2021 amendment as Merger agreement signed, and Party D Not selected at signing.</t>
+          <t>Round 3 due dates 04/14/2021 → 04/20/2021: are the outcomes Extended, then Enforced?</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Keep this coding: Gray's offers amend a signed definitive agreement with specific contract terms.</t>
+          <t>Extended; Enforced.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Gray's offers of 05/25–05/31/2021 set price and contract terms against the executed agreement (pp. 74–76). No markups are reported, so E11 criterion 1 is not literally met. Party D's post-signing proposals came with markups of the signed Gray agreements (p. 71).</t>
+          <t>p.66: after reviewing the 04/14 bids, on 04/16 the board gave Gray and Party B until 04/20/2021 to improve. Both bid (pp.66–67), and on 04/23 the board acted on the bids in hand, choosing Gray and dropping B (p.68). D's 04/15 bid is not late, because D was never given 04/14.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>#63, #64, #67, #68, #70, #71, #72, #73, #74, #75, #76, #77, #78</t>
+          <t>#48, #52, #57</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>If Gray's post offers are Informal, #67, #71 and #73–#75 change Formality. If the amendment is only an Other material event, #77–#78 change and Party D stays open at the filing cutoff.</t>
+          <t>If 04/16 is read as a new request to improve with its own Deadline set, the Deadline revised label changes. The outcomes stay the same.</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Are Party D's priced proposals from 04/15/2021 Formal (with Heavy conditions)? The support is D's Merger Agreement markup of 04/08, revised 04/27, and its 05/13 markups of the signed Gray agreements.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Formal, Heavy.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>E11(1): markups of the acquisition agreement supported the priced proposals (pp.65, 69, 72). They were subject to diligence, structure and financing, and firm financing was missing, hence Heavy. The 05/13 and 05/26 letters call themselves 'non-binding', which does not decide formality.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>#51, #58, #62, #64, #70, #74</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Informal would show D as a weaker, conditional rival to Gray in round 3 and after signing. It affects whether the final stage had more than one formal bidder.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Post-signing: should the Gray–Party D contest (05/13–06/02/2021) be post rows, with the 06/02 amendment and its 06/03 announcement as Other material events rather than a second signing or announcement?</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Yes. The no-shop stayed in force and there was no go-shop or organized solicitation. Record Gray's post-signing offers as Formal Bids (Light), and D's re-entry and its second Not selected at signing on 06/02/2021.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>pp.71–77: D's proposals were unsolicited. Gray used its match rights, and the Company negotiated only with Gray. The amendment raised the price to $16.99 (p.77). The later Dotdash sale of NMG SpinCo (10/06/2021) is neither a competing proposal nor a termination, so it gets no row (E2).</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>#69, #70, #72, #73, #74, #75, #76, #77, #78, #79, #80, #81, #82, #83, #84, #85</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Labelling the amendment Merger agreement signed / Merger announced would add a second signing. Treating the contest as a new round would add a Rounds line with no due date.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6689,7 +7076,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Meredith Corporation (Iowa). The sale covers its local media group (LMG) business, by merger of Meredith after the spin-off of its national media group (NMG) and corporate operations into NMG SpinCo (Meredith Holdings Corporation).</t>
+          <t>Meredith Corporation (NYSE: MDP). What is sold is Meredith holding only its local media group (LMG, 17 TV stations), after spinning off its national media group (NMG) as NMG SpinCo.</t>
         </is>
       </c>
     </row>
@@ -6701,7 +7088,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Gray Television, Inc., through Gray Hawkeye Stations, Inc. (Merger Sub).</t>
+          <t>Gray Television, Inc., through its subsidiary Gray Hawkeye Stations, Inc. (Merger Sub).</t>
         </is>
       </c>
     </row>
@@ -6713,7 +7100,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategic (television broadcast company).</t>
+          <t>Strategic (television broadcaster).</t>
         </is>
       </c>
     </row>
@@ -6725,7 +7112,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$16.99 per share in cash (amendment of 06/02/2021; $14.51 per share in cash at signing on 05/03/2021). Enterprise value $2.825 billion. Shareholders also receive NMG SpinCo shares in the spin-off, which Gray does not pay for.</t>
+          <t>$16.99 per share in cash (amendment of 06/02/2021; EV $2.825B). The original price was $14.51 per share in cash (05/03/2021; EV $2.7B, of which $725M was cash to shareholders after $1.975B net debt stayed with LMG RemainCo). Shareholders also receive one NMG SpinCo share per Meredith share in the spin-off. Under the 10/06/2021 Dotdash (IAC) agreement those shares are to be sold for $42.18 cash each; that deal is not a condition of the Gray merger.</t>
         </is>
       </c>
     </row>
@@ -6737,7 +7124,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/03/2021 (amended 06/02/2021; further amended by the Consent Agreement of 10/06/2021).</t>
+          <t>05/03/2021 (amended 06/02/2021 and 10/06/2021)</t>
         </is>
       </c>
     </row>
@@ -6749,7 +7136,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/03/2021 (amendment announced 06/03/2021).</t>
+          <t>05/03/2021, before market open (amendment announced 06/03/2021)</t>
         </is>
       </c>
     </row>
@@ -6809,7 +7196,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Fall 2019: preliminary talks with a few private equity firms (including Party B) about possible strategic transactions; none went beyond preliminary talks (p. 58). No month is given, so there are no rows.</t>
+          <t>Fall 2019: preliminary talks with a few private equity firms, including Party B, about possible strategic transactions. None went beyond preliminary talks and no transaction resulted (p.58, p.60).</t>
         </is>
       </c>
     </row>
@@ -6821,7 +7208,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Met (process 1): 17 parties</t>
+          <t>Met (process 1): 17 parties (confidentiality agreements with 17 parties including Gray, p.60)</t>
         </is>
       </c>
     </row>
@@ -6833,7 +7220,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Yes: LMG RemainCo proposals (the whole of Meredith after the NMG spin-off to its shareholders) are recorded as Bids (Q3). The select-station proposals of 12/2020–01/2021 are Other-scope.</t>
+          <t>Yes. Proposals for LMG RemainCo (Meredith after the NMG spin-off) are treated as whole-company bids. Bids for the four select stations (Nov 2020–Jan 2021) are Other-scope.</t>
         </is>
       </c>
     </row>
@@ -6845,7 +7232,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>US dollars. LMG bids were stated as enterprise values in billions until May 2021, and station bids as total dollars; per-share prices appear only in Gray's post-signing offers. Party D offered cash plus stock of a new combined company, with per-share figures for its cash dividend only (Q3).</t>
+          <t>US dollars. LMG bids before signing are stated as enterprise values or EV ranges ($ billions). Party D's bids are cash consideration plus a percentage of a new combined company, with implied cash dividends per share given from 04/29/2021. Per-share cash prices appear only from signing ($14.51) and in Gray's post-signing offers. Station bids are aggregate dollar amounts. Mixed bases: see Q4.</t>
         </is>
       </c>
     </row>
@@ -6869,7 +7256,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Cooley LLP (Deloitte Tax LLP was the tax adviser)</t>
+          <t>Cooley LLP (Deloitte Tax LLP was tax adviser; regulatory advisers not named)</t>
         </is>
       </c>
     </row>
@@ -6881,7 +7268,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Meredith hired Moelis in 2020 to sell four select TV stations. The November 2020 outreach to 20 parties (17 NDAs) also drew LMG indications from Gray, Party A and Party B. After final station bids in January 2021, the board paused the station sale and ran a final LMG round with Gray and Party B. Party D joined unsolicited with a Morris Trust proposal. Gray was preferred on value and certainty and signed at $14.51 per share on 05/03/2021. Party D's post-signing proposals pushed Gray to an amendment at $16.99 per share on 06/02/2021; the filing also says media reports about the process drew no superior proposal (p. 53).</t>
+          <t>Meredith first tried to sell four TV stations, and Moelis contacted 20 parties from 11/16/2020, of which 17 signed NDAs. Gray, Party A and Party B also indicated interest in buying all of the LMG station group after a spin-off of NMG. After final station bids in January 2021, the board paused the station sale and ran a final LMG round with Gray and Party B from 03/17/2021, while Party D pressed uninvited Morris Trust proposals. The board judged Gray strongest on 04/23/2021, dropped Party B and signed with Gray on 05/03/2021 at EV $2.7B ($14.51 per share cash plus NMG SpinCo shares). Party D's post-signing proposals led Gray to raise its price through an amendment signed 06/02/2021, at $16.99 per share with a $113M break fee.</t>
         </is>
       </c>
     </row>
